--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -35,226 +35,868 @@
     <x:t>TL</x:t>
   </x:si>
   <x:si>
+    <x:t>ADEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASUZU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACSEL</x:t>
   </x:si>
   <x:si>
-    <x:t>ADEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
   </x:si>
   <x:si>
     <x:t>AKHAN</x:t>
   </x:si>
   <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
     <x:t>AKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
   </x:si>
   <x:si>
     <x:t>ALGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALVES</x:t>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
   </x:si>
   <x:si>
     <x:t>ANELE</x:t>
   </x:si>
   <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
   </x:si>
   <x:si>
     <x:t>ARFYE</x:t>
   </x:si>
   <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASUZU</x:t>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
   </x:si>
   <x:si>
     <x:t>ATATR</x:t>
   </x:si>
   <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>AVTUR</x:t>
   </x:si>
   <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
   </x:si>
   <x:si>
     <x:t>BLCYT</x:t>
   </x:si>
   <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
   </x:si>
   <x:si>
     <x:t>BURVA</x:t>
   </x:si>
   <x:si>
-    <x:t>BYDNR</x:t>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
   </x:si>
   <x:si>
     <x:t>CATES</x:t>
   </x:si>
   <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIMSA</x:t>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
   </x:si>
   <x:si>
     <x:t>CLEBI</x:t>
   </x:si>
   <x:si>
-    <x:t>CONSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
   </x:si>
   <x:si>
     <x:t>CUSAN</x:t>
   </x:si>
   <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
   </x:si>
   <x:si>
     <x:t>DCTTR</x:t>
   </x:si>
   <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
     <x:t>DERHL</x:t>
   </x:si>
   <x:si>
-    <x:t>DESA</x:t>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
   </x:si>
   <x:si>
     <x:t>DIRIT</x:t>
   </x:si>
   <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
   </x:si>
   <x:si>
     <x:t>DURDO</x:t>
   </x:si>
   <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
   </x:si>
   <x:si>
     <x:t>ECOGR</x:t>
   </x:si>
   <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
   </x:si>
   <x:si>
     <x:t>EMPAE</x:t>
@@ -263,55 +905,79 @@
     <x:t>ENDAE</x:t>
   </x:si>
   <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
   </x:si>
   <x:si>
     <x:t>ESCAR</x:t>
   </x:si>
   <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
   </x:si>
   <x:si>
     <x:t>FONET</x:t>
   </x:si>
   <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
     <x:t>FORTE</x:t>
   </x:si>
   <x:si>
     <x:t>FRIGO</x:t>
   </x:si>
   <x:si>
-    <x:t>FZLGY</x:t>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
   </x:si>
   <x:si>
     <x:t>GENIL</x:t>
@@ -320,19 +986,22 @@
     <x:t>GENKM</x:t>
   </x:si>
   <x:si>
-    <x:t>GEREL</x:t>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
   </x:si>
   <x:si>
     <x:t>GIPTA</x:t>
   </x:si>
   <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
   </x:si>
   <x:si>
     <x:t>GOKNR</x:t>
@@ -341,19 +1010,67 @@
     <x:t>GOLTS</x:t>
   </x:si>
   <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
   </x:si>
   <x:si>
     <x:t>HKTM</x:t>
   </x:si>
   <x:si>
-    <x:t>HLGYO</x:t>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
   </x:si>
   <x:si>
     <x:t>HURGZ</x:t>
@@ -368,58 +1085,130 @@
     <x:t>IDGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
   </x:si>
   <x:si>
     <x:t>ISGSY</x:t>
   </x:si>
   <x:si>
-    <x:t>ISKPL</x:t>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
   </x:si>
   <x:si>
     <x:t>ISSEN</x:t>
   </x:si>
   <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>IZINV</x:t>
   </x:si>
   <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
   </x:si>
   <x:si>
     <x:t>KCAER</x:t>
   </x:si>
   <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
   </x:si>
   <x:si>
     <x:t>KIMMR</x:t>
   </x:si>
   <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>KLMSN</x:t>
   </x:si>
   <x:si>
-    <x:t>KLSYN</x:t>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
   </x:si>
   <x:si>
     <x:t>KLYPV</x:t>
@@ -428,103 +1217,175 @@
     <x:t>KMPUR</x:t>
   </x:si>
   <x:si>
-    <x:t>KONKA</x:t>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
   </x:si>
   <x:si>
     <x:t>KORDS</x:t>
   </x:si>
   <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
     <x:t>KRDMA</x:t>
   </x:si>
   <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
   </x:si>
   <x:si>
     <x:t>KUVVA</x:t>
   </x:si>
   <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
   </x:si>
   <x:si>
     <x:t>LXGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>MAALT</x:t>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
   </x:si>
   <x:si>
     <x:t>MACKO</x:t>
   </x:si>
   <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
     <x:t>MAKIM</x:t>
   </x:si>
   <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
     <x:t>MANAS</x:t>
   </x:si>
   <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARKA</x:t>
   </x:si>
   <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
     <x:t>MARTI</x:t>
   </x:si>
   <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
     <x:t>MCARD</x:t>
   </x:si>
   <x:si>
-    <x:t>MEGMT</x:t>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
   </x:si>
   <x:si>
     <x:t>MEKAG</x:t>
   </x:si>
   <x:si>
-    <x:t>METRO</x:t>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
   </x:si>
   <x:si>
     <x:t>MEYSU</x:t>
   </x:si>
   <x:si>
-    <x:t>MGROS</x:t>
+    <x:t>MHRGY</x:t>
   </x:si>
   <x:si>
     <x:t>MIATK</x:t>
   </x:si>
   <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
   </x:si>
   <x:si>
     <x:t>NETCD</x:t>
@@ -533,28 +1394,94 @@
     <x:t>NIBAS</x:t>
   </x:si>
   <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
     <x:t>OBAMS</x:t>
   </x:si>
   <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ODAS</x:t>
   </x:si>
   <x:si>
-    <x:t>ODINE</x:t>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
   </x:si>
   <x:si>
     <x:t>ORGE</x:t>
   </x:si>
   <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
   </x:si>
   <x:si>
     <x:t>PCILT</x:t>
@@ -563,124 +1490,259 @@
     <x:t>PEKGY</x:t>
   </x:si>
   <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
   </x:si>
   <x:si>
     <x:t>PINSU</x:t>
   </x:si>
   <x:si>
-    <x:t>PKART</x:t>
+    <x:t>PKENT</x:t>
   </x:si>
   <x:si>
     <x:t>PLTUR</x:t>
   </x:si>
   <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
     <x:t>PNSUT</x:t>
   </x:si>
   <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
   </x:si>
   <x:si>
     <x:t>QNBFK</x:t>
   </x:si>
   <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
     <x:t>QUAGR</x:t>
   </x:si>
   <x:si>
-    <x:t>RALYH</x:t>
+    <x:t>RAYSG</x:t>
   </x:si>
   <x:si>
     <x:t>REEDR</x:t>
   </x:si>
   <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
   </x:si>
   <x:si>
     <x:t>RUBNS</x:t>
   </x:si>
   <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
   </x:si>
   <x:si>
     <x:t>SANFM</x:t>
   </x:si>
   <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
   </x:si>
   <x:si>
     <x:t>SERNT</x:t>
   </x:si>
   <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
   </x:si>
   <x:si>
     <x:t>SKYMD</x:t>
   </x:si>
   <x:si>
-    <x:t>SOKE</x:t>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
   </x:si>
   <x:si>
     <x:t>SVGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
     <x:t>TATEN</x:t>
   </x:si>
   <x:si>
-    <x:t>TAVHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TBORG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TDGYO</x:t>
   </x:si>
   <x:si>
     <x:t>TEHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TERA</x:t>
+    <x:t>TEKTU</x:t>
   </x:si>
   <x:si>
     <x:t>TEZOL</x:t>
   </x:si>
   <x:si>
-    <x:t>THYAO</x:t>
+    <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
     <x:t>TKFEN</x:t>
   </x:si>
   <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
+    <x:t>TKNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSPOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTRAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
   </x:si>
   <x:si>
     <x:t>TUREX</x:t>
@@ -689,45 +1751,102 @@
     <x:t>TURGG</x:t>
   </x:si>
   <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
     <x:t>UCAYM</x:t>
   </x:si>
   <x:si>
     <x:t>UFUK</x:t>
   </x:si>
   <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UMPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
   </x:si>
   <x:si>
     <x:t>VAKFA</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
+    <x:t>VAKFN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESBE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKFYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VSNMD</x:t>
   </x:si>
   <x:si>
     <x:t>YAPRK</x:t>
   </x:si>
   <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAYLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YBTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YESIL</x:t>
   </x:si>
   <x:si>
     <x:t>YIGIT</x:t>
   </x:si>
   <x:si>
+    <x:t>YKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKSLN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YONGA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYAPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYLGD</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZEDUR</x:t>
   </x:si>
   <x:si>
@@ -735,1125 +1854,6 @@
   </x:si>
   <x:si>
     <x:t>ZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TBORG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSPOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTRAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UMPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VESBE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VESTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKFYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VSNMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAYLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YBTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YESIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKSLN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YONGA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YYAPI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YYLGD</x:t>
   </x:si>
   <x:si>
     <x:t>ZOREN</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C236"/>
+  <x:dimension ref="A1:C149"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -3849,963 +3849,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" spans="1:3">
-      <x:c r="A150" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C150" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151" spans="1:3">
-      <x:c r="A151" s="0" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="B151" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C151" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152" spans="1:3">
-      <x:c r="A152" s="0" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C152" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153" spans="1:3">
-      <x:c r="A153" s="0" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C153" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154" spans="1:3">
-      <x:c r="A154" s="0" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="B154" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C154" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155" spans="1:3">
-      <x:c r="A155" s="0" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C155" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156" spans="1:3">
-      <x:c r="A156" s="0" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="B156" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C156" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" spans="1:3">
-      <x:c r="A157" s="0" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C157" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" spans="1:3">
-      <x:c r="A158" s="0" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C158" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" spans="1:3">
-      <x:c r="A159" s="0" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C159" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" spans="1:3">
-      <x:c r="A160" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C160" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" spans="1:3">
-      <x:c r="A161" s="0" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C161" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" spans="1:3">
-      <x:c r="A162" s="0" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C162" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" spans="1:3">
-      <x:c r="A163" s="0" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="B163" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C163" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" spans="1:3">
-      <x:c r="A164" s="0" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C164" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" spans="1:3">
-      <x:c r="A165" s="0" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C165" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" spans="1:3">
-      <x:c r="A166" s="0" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C166" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" spans="1:3">
-      <x:c r="A167" s="0" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C167" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" spans="1:3">
-      <x:c r="A168" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C168" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:3">
-      <x:c r="A169" s="0" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C169" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:3">
-      <x:c r="A170" s="0" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C170" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:3">
-      <x:c r="A171" s="0" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C171" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:3">
-      <x:c r="A172" s="0" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="B172" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C172" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" spans="1:3">
-      <x:c r="A173" s="0" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="B173" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C173" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" spans="1:3">
-      <x:c r="A174" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="B174" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C174" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" spans="1:3">
-      <x:c r="A175" s="0" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="B175" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C175" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" spans="1:3">
-      <x:c r="A176" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="B176" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C176" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" spans="1:3">
-      <x:c r="A177" s="0" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="B177" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C177" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" spans="1:3">
-      <x:c r="A178" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="B178" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C178" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" spans="1:3">
-      <x:c r="A179" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="B179" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C179" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180" spans="1:3">
-      <x:c r="A180" s="0" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="B180" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C180" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181" spans="1:3">
-      <x:c r="A181" s="0" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="B181" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C181" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182" spans="1:3">
-      <x:c r="A182" s="0" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="B182" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C182" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="183" spans="1:3">
-      <x:c r="A183" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="B183" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C183" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184" spans="1:3">
-      <x:c r="A184" s="0" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="B184" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C184" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="185" spans="1:3">
-      <x:c r="A185" s="0" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="B185" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C185" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186" spans="1:3">
-      <x:c r="A186" s="0" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="B186" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C186" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187" spans="1:3">
-      <x:c r="A187" s="0" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="B187" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C187" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188" spans="1:3">
-      <x:c r="A188" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="B188" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C188" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189" spans="1:3">
-      <x:c r="A189" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="B189" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C189" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190" spans="1:3">
-      <x:c r="A190" s="0" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="B190" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C190" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191" spans="1:3">
-      <x:c r="A191" s="0" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="B191" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C191" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192" spans="1:3">
-      <x:c r="A192" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="B192" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C192" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193" spans="1:3">
-      <x:c r="A193" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="B193" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C193" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194" spans="1:3">
-      <x:c r="A194" s="0" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="B194" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C194" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195" spans="1:3">
-      <x:c r="A195" s="0" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="B195" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C195" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196" spans="1:3">
-      <x:c r="A196" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="B196" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C196" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197" spans="1:3">
-      <x:c r="A197" s="0" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="B197" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C197" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198" spans="1:3">
-      <x:c r="A198" s="0" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="B198" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C198" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199" spans="1:3">
-      <x:c r="A199" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="B199" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C199" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200" spans="1:3">
-      <x:c r="A200" s="0" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="B200" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C200" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201" spans="1:3">
-      <x:c r="A201" s="0" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="B201" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C201" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202" spans="1:3">
-      <x:c r="A202" s="0" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="B202" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C202" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203" spans="1:3">
-      <x:c r="A203" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="B203" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C203" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" spans="1:3">
-      <x:c r="A204" s="0" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="B204" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C204" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" spans="1:3">
-      <x:c r="A205" s="0" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="B205" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C205" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" spans="1:3">
-      <x:c r="A206" s="0" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="B206" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C206" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="207" spans="1:3">
-      <x:c r="A207" s="0" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="B207" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C207" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="208" spans="1:3">
-      <x:c r="A208" s="0" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="B208" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C208" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="209" spans="1:3">
-      <x:c r="A209" s="0" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="B209" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C209" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="210" spans="1:3">
-      <x:c r="A210" s="0" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="B210" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C210" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="211" spans="1:3">
-      <x:c r="A211" s="0" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="B211" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C211" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="212" spans="1:3">
-      <x:c r="A212" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="B212" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C212" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="213" spans="1:3">
-      <x:c r="A213" s="0" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="B213" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C213" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214" spans="1:3">
-      <x:c r="A214" s="0" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="B214" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C214" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="215" spans="1:3">
-      <x:c r="A215" s="0" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="B215" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C215" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="216" spans="1:3">
-      <x:c r="A216" s="0" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="B216" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C216" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="217" spans="1:3">
-      <x:c r="A217" s="0" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="B217" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C217" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="218" spans="1:3">
-      <x:c r="A218" s="0" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="B218" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C218" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="219" spans="1:3">
-      <x:c r="A219" s="0" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="B219" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C219" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220" spans="1:3">
-      <x:c r="A220" s="0" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="B220" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C220" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221" spans="1:3">
-      <x:c r="A221" s="0" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="B221" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C221" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="222" spans="1:3">
-      <x:c r="A222" s="0" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="B222" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C222" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223" spans="1:3">
-      <x:c r="A223" s="0" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="B223" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C223" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224" spans="1:3">
-      <x:c r="A224" s="0" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="B224" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C224" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="225" spans="1:3">
-      <x:c r="A225" s="0" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="B225" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C225" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226" spans="1:3">
-      <x:c r="A226" s="0" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="B226" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C226" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="227" spans="1:3">
-      <x:c r="A227" s="0" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="B227" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C227" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="228" spans="1:3">
-      <x:c r="A228" s="0" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="B228" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C228" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="229" spans="1:3">
-      <x:c r="A229" s="0" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="B229" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C229" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="230" spans="1:3">
-      <x:c r="A230" s="0" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="B230" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C230" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="231" spans="1:3">
-      <x:c r="A231" s="0" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="B231" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C231" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="232" spans="1:3">
-      <x:c r="A232" s="0" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="B232" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C232" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="233" spans="1:3">
-      <x:c r="A233" s="0" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="B233" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C233" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="234" spans="1:3">
-      <x:c r="A234" s="0" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="B234" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C234" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="235" spans="1:3">
-      <x:c r="A235" s="0" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="B235" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C235" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="236" spans="1:3">
-      <x:c r="A236" s="0" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="B236" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C236" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4823,7 +3866,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C376"/>
+  <x:dimension ref="A1:C463"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4839,7 +3882,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +3893,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +3904,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +3915,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +3926,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +3937,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +3948,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +3959,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +3970,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +3981,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +3992,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +4003,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +4014,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +4025,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +4036,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +4047,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +4058,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +4069,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +4080,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +4091,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +4102,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +4113,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +4124,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +4135,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +4146,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +4157,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +4168,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +4179,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +4190,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +4201,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +4212,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +4223,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +4234,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +4245,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +4256,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +4267,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +4278,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +4289,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +4300,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +4311,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +4322,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +4333,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +4344,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +4355,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +4366,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +4377,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +4388,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +4399,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +4410,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +4421,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +4432,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +4443,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +4454,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +4465,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +4476,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +4487,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +4498,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +4509,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +4520,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +4531,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +4542,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +4553,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +4564,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +4575,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +4586,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +4597,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +4608,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +4619,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +4630,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +4641,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +4652,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +4663,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +4674,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +4685,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +4696,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +4707,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +4718,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +4729,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +4740,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +4751,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +4762,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +4773,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +4784,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +4795,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +4806,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +4817,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +4828,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +4839,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +4850,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +4861,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +4872,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +4883,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +4894,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +4905,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +4916,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +4927,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +4938,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +4949,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +4960,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +4971,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +4982,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +4993,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +5004,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +5015,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +5026,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +5037,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +5048,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +5059,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +5070,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +5081,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +5092,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +5103,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +5114,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +5125,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +5136,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +5147,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +5158,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +5169,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +5180,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +5191,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +5202,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +5213,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +5224,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +5235,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +5246,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +5257,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +5268,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +5279,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +5290,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +5301,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +5312,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +5323,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +5334,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +5345,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +5356,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +5367,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +5378,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +5389,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +5400,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +5411,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +5422,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +5433,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +5444,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +5455,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +5466,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +5477,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +5488,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +5499,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +5510,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +5521,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +5532,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +5543,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +5554,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +5565,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +5576,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +5587,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +5598,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +5609,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +5620,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +5631,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +5642,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +5653,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +5664,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +5675,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +5686,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +5697,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +5708,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +5719,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +5730,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +5741,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +5752,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +5763,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +5774,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +5785,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +5796,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +5807,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +5818,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +5829,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +5840,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +5851,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +5862,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +5873,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +5884,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +5895,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +5906,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +5917,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +5928,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +5939,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +5950,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +5961,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +5972,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +5983,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +5994,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +6005,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +6016,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +6027,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +6038,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +6049,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +6060,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +6071,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +6082,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +6093,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +6104,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +6115,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +6126,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +6137,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +6148,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +6159,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +6170,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +6181,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +6192,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +6203,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +6214,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +6225,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +6236,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +6247,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +6258,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +6269,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +6280,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +6291,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +6302,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +6313,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +6324,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +6335,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +6346,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +6357,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +6368,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +6379,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +6390,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +6401,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +6412,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +6423,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +6434,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +6445,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +6456,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +6467,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +6478,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +6489,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +6500,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +6511,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +6522,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +6533,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +6544,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +6555,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +6566,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +6577,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +6588,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +6599,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +6610,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +6621,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +6632,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +6643,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +6654,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +6665,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +6676,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +6687,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +6698,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +6709,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +6720,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +6731,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +6742,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +6753,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +6764,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +6775,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +6786,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +6797,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +6808,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +6819,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +6830,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +6841,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +6852,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +6863,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +6874,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +6885,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +6896,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +6907,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +6918,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +6929,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +6940,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +6951,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +6962,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +6973,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +6984,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +6995,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +7006,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +7017,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +7028,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +7039,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +7050,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +7061,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +7072,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +7083,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +7094,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +7105,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +7116,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +7127,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +7138,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +7149,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +7160,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +7171,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +7182,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +7193,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +7204,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +7215,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +7226,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +7237,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +7248,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +7259,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +7270,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +7281,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +7292,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +7303,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +7314,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +7325,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +7336,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +7347,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +7358,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +7369,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +7380,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +7391,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +7402,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +7413,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +7424,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +7435,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +7446,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +7457,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +7468,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +7479,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +7490,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +7501,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +7512,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +7523,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +7534,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +7545,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +7556,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +7567,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +7578,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +7589,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +7600,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +7611,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +7622,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +7633,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +7644,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +7655,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +7666,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +7677,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +7688,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +7699,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +7710,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +7721,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +7732,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +7743,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +7754,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +7765,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +7776,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +7787,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +7798,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +7809,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +7820,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +7831,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +7842,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +7853,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +7864,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +7875,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +7886,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +7897,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +7908,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +7919,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,7 +7930,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8898,7 +7941,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8909,7 +7952,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8920,7 +7963,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8931,7 +7974,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>612</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8942,7 +7985,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>613</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8953,12 +7996,969 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="B376" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C376" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" spans="1:3">
+      <x:c r="A377" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="B377" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C377" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" spans="1:3">
+      <x:c r="A378" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B378" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C378" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" spans="1:3">
+      <x:c r="A379" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="B379" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C379" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" spans="1:3">
+      <x:c r="A380" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="B380" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C380" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" spans="1:3">
+      <x:c r="A381" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="B381" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C381" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" spans="1:3">
+      <x:c r="A382" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="B382" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C382" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" spans="1:3">
+      <x:c r="A383" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B383" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C383" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" spans="1:3">
+      <x:c r="A384" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="B384" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C384" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" spans="1:3">
+      <x:c r="A385" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B385" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C385" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" spans="1:3">
+      <x:c r="A386" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="B386" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C386" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" spans="1:3">
+      <x:c r="A387" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="B387" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C387" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" spans="1:3">
+      <x:c r="A388" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="B388" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C388" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" spans="1:3">
+      <x:c r="A389" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B389" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C389" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" spans="1:3">
+      <x:c r="A390" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B390" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C390" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" spans="1:3">
+      <x:c r="A391" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B391" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C391" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" spans="1:3">
+      <x:c r="A392" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="B392" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C392" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" spans="1:3">
+      <x:c r="A393" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B393" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C393" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" spans="1:3">
+      <x:c r="A394" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="B394" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C394" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" spans="1:3">
+      <x:c r="A395" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="B395" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C395" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" spans="1:3">
+      <x:c r="A396" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B396" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C396" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" spans="1:3">
+      <x:c r="A397" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="B397" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C397" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" spans="1:3">
+      <x:c r="A398" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="B398" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C398" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" spans="1:3">
+      <x:c r="A399" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B399" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C399" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" spans="1:3">
+      <x:c r="A400" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="B400" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C400" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" spans="1:3">
+      <x:c r="A401" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="B401" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C401" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" spans="1:3">
+      <x:c r="A402" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B402" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C402" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" spans="1:3">
+      <x:c r="A403" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="B403" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C403" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" spans="1:3">
+      <x:c r="A404" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="B404" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C404" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" spans="1:3">
+      <x:c r="A405" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B405" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C405" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" spans="1:3">
+      <x:c r="A406" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="B406" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C406" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" spans="1:3">
+      <x:c r="A407" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="B407" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C407" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" spans="1:3">
+      <x:c r="A408" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="B408" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C408" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" spans="1:3">
+      <x:c r="A409" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B409" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C409" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" spans="1:3">
+      <x:c r="A410" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="B410" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C410" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" spans="1:3">
+      <x:c r="A411" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="B411" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C411" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" spans="1:3">
+      <x:c r="A412" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="B412" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C412" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" spans="1:3">
+      <x:c r="A413" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="B413" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C413" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" spans="1:3">
+      <x:c r="A414" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="B414" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C414" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" spans="1:3">
+      <x:c r="A415" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B415" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C415" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" spans="1:3">
+      <x:c r="A416" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B416" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C416" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" spans="1:3">
+      <x:c r="A417" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="B417" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C417" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" spans="1:3">
+      <x:c r="A418" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B418" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C418" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" spans="1:3">
+      <x:c r="A419" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B419" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C419" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" spans="1:3">
+      <x:c r="A420" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="B420" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C420" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" spans="1:3">
+      <x:c r="A421" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B421" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C421" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" spans="1:3">
+      <x:c r="A422" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B422" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C422" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" spans="1:3">
+      <x:c r="A423" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="B423" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C423" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" spans="1:3">
+      <x:c r="A424" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="B424" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C424" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" spans="1:3">
+      <x:c r="A425" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B425" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C425" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" spans="1:3">
+      <x:c r="A426" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="B426" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C426" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" spans="1:3">
+      <x:c r="A427" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="B427" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C427" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" spans="1:3">
+      <x:c r="A428" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="B428" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C428" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" spans="1:3">
+      <x:c r="A429" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="B429" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C429" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" spans="1:3">
+      <x:c r="A430" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="B430" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C430" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" spans="1:3">
+      <x:c r="A431" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="B431" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C431" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" spans="1:3">
+      <x:c r="A432" s="0" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B432" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C432" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" spans="1:3">
+      <x:c r="A433" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="B433" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C433" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" spans="1:3">
+      <x:c r="A434" s="0" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B434" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C434" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" spans="1:3">
+      <x:c r="A435" s="0" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="B435" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C435" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" spans="1:3">
+      <x:c r="A436" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="B436" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C436" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" spans="1:3">
+      <x:c r="A437" s="0" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B437" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C437" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" spans="1:3">
+      <x:c r="A438" s="0" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="B438" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C438" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" spans="1:3">
+      <x:c r="A439" s="0" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="B439" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C439" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" spans="1:3">
+      <x:c r="A440" s="0" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B440" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C440" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" spans="1:3">
+      <x:c r="A441" s="0" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B441" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C441" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" spans="1:3">
+      <x:c r="A442" s="0" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="B442" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C442" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" spans="1:3">
+      <x:c r="A443" s="0" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B443" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C443" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" spans="1:3">
+      <x:c r="A444" s="0" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B444" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C444" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" spans="1:3">
+      <x:c r="A445" s="0" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="B445" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C445" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" spans="1:3">
+      <x:c r="A446" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B446" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C446" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" spans="1:3">
+      <x:c r="A447" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="B447" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C447" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" spans="1:3">
+      <x:c r="A448" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="B448" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C448" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" spans="1:3">
+      <x:c r="A449" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B449" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C449" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" spans="1:3">
+      <x:c r="A450" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="B450" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C450" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" spans="1:3">
+      <x:c r="A451" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="B451" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C451" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" spans="1:3">
+      <x:c r="A452" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B452" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C452" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" spans="1:3">
+      <x:c r="A453" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B453" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C453" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" spans="1:3">
+      <x:c r="A454" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="B454" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C454" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" spans="1:3">
+      <x:c r="A455" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B455" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C455" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" spans="1:3">
+      <x:c r="A456" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="B456" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C456" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" spans="1:3">
+      <x:c r="A457" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B457" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C457" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" spans="1:3">
+      <x:c r="A458" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B458" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C458" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" spans="1:3">
+      <x:c r="A459" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="B459" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C459" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" spans="1:3">
+      <x:c r="A460" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B460" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C460" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" spans="1:3">
+      <x:c r="A461" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B461" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C461" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" spans="1:3">
+      <x:c r="A462" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B462" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C462" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" spans="1:3">
+      <x:c r="A463" s="0" t="s">
         <x:v>614</x:v>
       </x:c>
-      <x:c r="B376" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C376" s="0" t="s">
+      <x:c r="B463" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C463" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -26,36 +26,201 @@
     <x:t>Birim</x:t>
   </x:si>
   <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gün</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESBE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YBTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YESIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKSLN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YONGA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1YEN</x:t>
   </x:si>
   <x:si>
-    <x:t>Gün</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TL</x:t>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
   </x:si>
   <x:si>
     <x:t>ADEL</x:t>
   </x:si>
   <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ADGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGESA</x:t>
   </x:si>
   <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
     <x:t>AKFYE</x:t>
   </x:si>
   <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKMGY</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSEN</x:t>
   </x:si>
   <x:si>
@@ -65,15 +230,48 @@
     <x:t>AKSUE</x:t>
   </x:si>
   <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALVES</x:t>
   </x:si>
   <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ANHYT</x:t>
   </x:si>
   <x:si>
@@ -83,9 +281,24 @@
     <x:t>ARASE</x:t>
   </x:si>
   <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARTMS</x:t>
   </x:si>
   <x:si>
@@ -95,12 +308,51 @@
     <x:t>ASELS</x:t>
   </x:si>
   <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ASTOR</x:t>
   </x:si>
   <x:si>
     <x:t>ASUZU</x:t>
   </x:si>
   <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYCES</x:t>
   </x:si>
   <x:si>
@@ -116,81 +368,318 @@
     <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
     <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
     <x:t>BAKAB</x:t>
   </x:si>
   <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
     <x:t>BARMA</x:t>
   </x:si>
   <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
     <x:t>BASGZ</x:t>
   </x:si>
   <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
     <x:t>BORSK</x:t>
   </x:si>
   <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>BSOKE</x:t>
   </x:si>
   <x:si>
     <x:t>BTCIM</x:t>
   </x:si>
   <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>BYDNR</x:t>
   </x:si>
   <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
     <x:t>CEMZY</x:t>
   </x:si>
   <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
     <x:t>CIMSA</x:t>
   </x:si>
   <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
     <x:t>CONSE</x:t>
   </x:si>
   <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
     <x:t>CRDFA</x:t>
   </x:si>
   <x:si>
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>CVKMD</x:t>
   </x:si>
   <x:si>
     <x:t>CWENE</x:t>
   </x:si>
   <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>DESA</x:t>
   </x:si>
   <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>DMRGD</x:t>
   </x:si>
   <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
     <x:t>DOFRB</x:t>
   </x:si>
   <x:si>
     <x:t>DOGUB</x:t>
   </x:si>
   <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
     <x:t>DSTKF</x:t>
   </x:si>
   <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
     <x:t>DURKN</x:t>
   </x:si>
   <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>EBEBK</x:t>
   </x:si>
   <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
     <x:t>ECZYT</x:t>
   </x:si>
   <x:si>
     <x:t>EDATA</x:t>
   </x:si>
   <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
     <x:t>EGEGY</x:t>
   </x:si>
   <x:si>
@@ -203,93 +692,384 @@
     <x:t>EGPRO</x:t>
   </x:si>
   <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
     <x:t>ENJSA</x:t>
   </x:si>
   <x:si>
     <x:t>ENKAI</x:t>
   </x:si>
   <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ENSRI</x:t>
   </x:si>
   <x:si>
     <x:t>ENTRA</x:t>
   </x:si>
   <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>ERBOS</x:t>
   </x:si>
   <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
     <x:t>EREGL</x:t>
   </x:si>
   <x:si>
     <x:t>ERSU</x:t>
   </x:si>
   <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
     <x:t>EUPWR</x:t>
   </x:si>
   <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
     <x:t>EUYO</x:t>
   </x:si>
   <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>FADE</x:t>
   </x:si>
   <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
     <x:t>FLAP</x:t>
   </x:si>
   <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
     <x:t>FZLGY</x:t>
   </x:si>
   <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEREL</x:t>
   </x:si>
   <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLRMK</x:t>
   </x:si>
   <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
     <x:t>GMTAS</x:t>
   </x:si>
   <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
     <x:t>GUNDG</x:t>
   </x:si>
   <x:si>
     <x:t>GWIND</x:t>
   </x:si>
   <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
     <x:t>HLGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>IEYHO</x:t>
   </x:si>
   <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
     <x:t>INDES</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
     <x:t>INVES</x:t>
   </x:si>
   <x:si>
     <x:t>ISATR</x:t>
   </x:si>
   <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
     <x:t>ISDMR</x:t>
   </x:si>
   <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ISKPL</x:t>
   </x:si>
   <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
     <x:t>KAPLM</x:t>
   </x:si>
   <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>KBORU</x:t>
   </x:si>
   <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
     <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
@@ -299,33 +1079,105 @@
     <x:t>KGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
     <x:t>KLSYN</x:t>
   </x:si>
   <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
     <x:t>KONKA</x:t>
   </x:si>
   <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
     <x:t>KRDMB</x:t>
   </x:si>
   <x:si>
     <x:t>KRDMD</x:t>
   </x:si>
   <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>KRONT</x:t>
   </x:si>
   <x:si>
     <x:t>KRPLS</x:t>
   </x:si>
   <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
     <x:t>KTLEV</x:t>
   </x:si>
   <x:si>
     <x:t>KTSKR</x:t>
   </x:si>
   <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUYAS</x:t>
   </x:si>
   <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>LIDER</x:t>
   </x:si>
   <x:si>
@@ -335,81 +1187,384 @@
     <x:t>LILAK</x:t>
   </x:si>
   <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
     <x:t>MAALT</x:t>
   </x:si>
   <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
     <x:t>MAGEN</x:t>
   </x:si>
   <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARMR</x:t>
   </x:si>
   <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEGMT</x:t>
   </x:si>
   <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
     <x:t>METRO</x:t>
   </x:si>
   <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
     <x:t>MGROS</x:t>
   </x:si>
   <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
     <x:t>MOBTL</x:t>
   </x:si>
   <x:si>
     <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
     <x:t>MSGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>ODINE</x:t>
   </x:si>
   <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>OZATD</x:t>
   </x:si>
   <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>OZRDN</x:t>
   </x:si>
   <x:si>
     <x:t>OZSUB</x:t>
   </x:si>
   <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
     <x:t>PAGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>PENGD</x:t>
   </x:si>
   <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
     <x:t>PETKM</x:t>
   </x:si>
   <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
     <x:t>PKART</x:t>
   </x:si>
   <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
     <x:t>POLHO</x:t>
   </x:si>
   <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
     <x:t>PRDGS</x:t>
   </x:si>
   <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
     <x:t>RALYH</x:t>
   </x:si>
   <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
     <x:t>RGYAS</x:t>
   </x:si>
   <x:si>
     <x:t>RNPOL</x:t>
   </x:si>
   <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>RYSAS</x:t>
   </x:si>
   <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
     <x:t>SEGMN</x:t>
   </x:si>
   <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
     <x:t>SEKFK</x:t>
   </x:si>
   <x:si>
@@ -419,1423 +1574,268 @@
     <x:t>SELEC</x:t>
   </x:si>
   <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
     <x:t>SISE</x:t>
   </x:si>
   <x:si>
     <x:t>SKBNK</x:t>
   </x:si>
   <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
     <x:t>SOKE</x:t>
   </x:si>
   <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
     <x:t>TAVHL</x:t>
   </x:si>
   <x:si>
+    <x:t>TBORG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
     <x:t>TCKRC</x:t>
   </x:si>
   <x:si>
+    <x:t>TDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>THYAO</x:t>
   </x:si>
   <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>TMPOL</x:t>
   </x:si>
   <x:si>
+    <x:t>TMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRGYO</x:t>
   </x:si>
   <x:si>
     <x:t>TRHOL</x:t>
   </x:si>
   <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSPOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTRAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>TUPRS</x:t>
   </x:si>
   <x:si>
+    <x:t>TUREX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
     <x:t>TURSG</x:t>
   </x:si>
   <x:si>
+    <x:t>UCAYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
     <x:t>ULUFA</x:t>
   </x:si>
   <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>ULUUN</x:t>
   </x:si>
   <x:si>
+    <x:t>UMPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFN</x:t>
+  </x:si>
+  <x:si>
     <x:t>VAKKO</x:t>
   </x:si>
   <x:si>
     <x:t>VANGD</x:t>
   </x:si>
   <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
     <x:t>VERUS</x:t>
   </x:si>
   <x:si>
+    <x:t>VKFYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VSNMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAYLA</x:t>
+  </x:si>
+  <x:si>
     <x:t>YEOTK</x:t>
   </x:si>
   <x:si>
     <x:t>YGGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SERNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TBORG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSPOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTRAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUREX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURGG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UCAYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UMPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VESBE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VESTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKFYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VSNMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAYLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YBTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YESIL</x:t>
-  </x:si>
-  <x:si>
     <x:t>YIGIT</x:t>
   </x:si>
   <x:si>
     <x:t>YKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKSLN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YONGA</x:t>
   </x:si>
   <x:si>
     <x:t>YUNSA</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C149"/>
+  <x:dimension ref="A1:C39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -2639,1216 +2639,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:3">
-      <x:c r="A40" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:3">
-      <x:c r="A41" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:3">
-      <x:c r="A42" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:3">
-      <x:c r="A43" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:3">
-      <x:c r="A44" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:3">
-      <x:c r="A45" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:3">
-      <x:c r="A46" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:3">
-      <x:c r="A47" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:3">
-      <x:c r="A48" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:3">
-      <x:c r="A49" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:3">
-      <x:c r="A50" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:3">
-      <x:c r="A51" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:3">
-      <x:c r="A52" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:3">
-      <x:c r="A53" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C53" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:3">
-      <x:c r="A54" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:3">
-      <x:c r="A55" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C55" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:3">
-      <x:c r="A56" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C56" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:3">
-      <x:c r="A57" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C57" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:3">
-      <x:c r="A58" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:3">
-      <x:c r="A59" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C59" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:3">
-      <x:c r="A60" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:3">
-      <x:c r="A61" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C61" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:3">
-      <x:c r="A62" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C62" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:3">
-      <x:c r="A63" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C63" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:3">
-      <x:c r="A64" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C64" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:3">
-      <x:c r="A65" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C65" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:3">
-      <x:c r="A66" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:3">
-      <x:c r="A67" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:3">
-      <x:c r="A68" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C68" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:3">
-      <x:c r="A69" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C69" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:3">
-      <x:c r="A70" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C70" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:3">
-      <x:c r="A71" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C71" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:3">
-      <x:c r="A72" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C72" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:3">
-      <x:c r="A73" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C73" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:3">
-      <x:c r="A74" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C74" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:3">
-      <x:c r="A75" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C75" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:3">
-      <x:c r="A76" s="0" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C76" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:3">
-      <x:c r="A77" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C77" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:3">
-      <x:c r="A78" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C78" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:3">
-      <x:c r="A79" s="0" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C79" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:3">
-      <x:c r="A80" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C80" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:3">
-      <x:c r="A81" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C81" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:3">
-      <x:c r="A82" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C82" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:3">
-      <x:c r="A83" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C83" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:3">
-      <x:c r="A84" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C84" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:3">
-      <x:c r="A85" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C85" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:3">
-      <x:c r="A86" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C86" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:3">
-      <x:c r="A87" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C87" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:3">
-      <x:c r="A88" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C88" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:3">
-      <x:c r="A89" s="0" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C89" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:3">
-      <x:c r="A90" s="0" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C90" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:3">
-      <x:c r="A91" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C91" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:3">
-      <x:c r="A92" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C92" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:3">
-      <x:c r="A93" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C93" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:3">
-      <x:c r="A94" s="0" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B94" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C94" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:3">
-      <x:c r="A95" s="0" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C95" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:3">
-      <x:c r="A96" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C96" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:3">
-      <x:c r="A97" s="0" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C97" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:3">
-      <x:c r="A98" s="0" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C98" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:3">
-      <x:c r="A99" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C99" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:3">
-      <x:c r="A100" s="0" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C100" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:3">
-      <x:c r="A101" s="0" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C101" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:3">
-      <x:c r="A102" s="0" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C102" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:3">
-      <x:c r="A103" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C103" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:3">
-      <x:c r="A104" s="0" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="B104" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C104" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:3">
-      <x:c r="A105" s="0" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C105" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:3">
-      <x:c r="A106" s="0" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="B106" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C106" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:3">
-      <x:c r="A107" s="0" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C107" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:3">
-      <x:c r="A108" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C108" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:3">
-      <x:c r="A109" s="0" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C109" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:3">
-      <x:c r="A110" s="0" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C110" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:3">
-      <x:c r="A111" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C111" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:3">
-      <x:c r="A112" s="0" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C112" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:3">
-      <x:c r="A113" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C113" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:3">
-      <x:c r="A114" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C114" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:3">
-      <x:c r="A115" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C115" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:3">
-      <x:c r="A116" s="0" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C116" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:3">
-      <x:c r="A117" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C117" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:3">
-      <x:c r="A118" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C118" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:3">
-      <x:c r="A119" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C119" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:3">
-      <x:c r="A120" s="0" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C120" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:3">
-      <x:c r="A121" s="0" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C121" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:3">
-      <x:c r="A122" s="0" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C122" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:3">
-      <x:c r="A123" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C123" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:3">
-      <x:c r="A124" s="0" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C124" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:3">
-      <x:c r="A125" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C125" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:3">
-      <x:c r="A126" s="0" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C126" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" spans="1:3">
-      <x:c r="A127" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C127" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" spans="1:3">
-      <x:c r="A128" s="0" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C128" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" spans="1:3">
-      <x:c r="A129" s="0" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C129" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" spans="1:3">
-      <x:c r="A130" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C130" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" spans="1:3">
-      <x:c r="A131" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C131" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" spans="1:3">
-      <x:c r="A132" s="0" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C132" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" spans="1:3">
-      <x:c r="A133" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="B133" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C133" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" spans="1:3">
-      <x:c r="A134" s="0" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C134" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" spans="1:3">
-      <x:c r="A135" s="0" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C135" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" spans="1:3">
-      <x:c r="A136" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="B136" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C136" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" spans="1:3">
-      <x:c r="A137" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C137" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="138" spans="1:3">
-      <x:c r="A138" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="B138" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C138" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139" spans="1:3">
-      <x:c r="A139" s="0" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C139" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="140" spans="1:3">
-      <x:c r="A140" s="0" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C140" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="141" spans="1:3">
-      <x:c r="A141" s="0" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C141" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="142" spans="1:3">
-      <x:c r="A142" s="0" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C142" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="143" spans="1:3">
-      <x:c r="A143" s="0" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C143" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" spans="1:3">
-      <x:c r="A144" s="0" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C144" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" spans="1:3">
-      <x:c r="A145" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C145" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" spans="1:3">
-      <x:c r="A146" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C146" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" spans="1:3">
-      <x:c r="A147" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="B147" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C147" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" spans="1:3">
-      <x:c r="A148" s="0" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C148" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" spans="1:3">
-      <x:c r="A149" s="0" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C149" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -3866,7 +2656,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C463"/>
+  <x:dimension ref="A1:C573"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -3882,7 +2672,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -3893,7 +2683,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -3904,7 +2694,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -3915,7 +2705,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -3926,7 +2716,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -3937,7 +2727,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -3948,7 +2738,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -3959,7 +2749,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -3970,7 +2760,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -3981,7 +2771,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -3992,7 +2782,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4003,7 +2793,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4014,7 +2804,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4025,7 +2815,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4036,7 +2826,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4047,7 +2837,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4058,7 +2848,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4069,7 +2859,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4080,7 +2870,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4091,7 +2881,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4102,7 +2892,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4113,7 +2903,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4124,7 +2914,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4135,7 +2925,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4146,7 +2936,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4157,7 +2947,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4168,7 +2958,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4179,7 +2969,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4190,7 +2980,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4201,7 +2991,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4212,7 +3002,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4223,7 +3013,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4234,7 +3024,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4245,7 +3035,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4256,7 +3046,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4267,7 +3057,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4278,7 +3068,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4289,7 +3079,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4300,7 +3090,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4311,7 +3101,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4322,7 +3112,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4333,7 +3123,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4344,7 +3134,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4355,7 +3145,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4366,7 +3156,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4377,7 +3167,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4388,7 +3178,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4399,7 +3189,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -4410,7 +3200,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -4421,7 +3211,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -4432,7 +3222,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -4443,7 +3233,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -4454,7 +3244,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -4465,7 +3255,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -4476,7 +3266,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +3277,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +3288,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +3299,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +3310,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +3321,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +3332,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +3343,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +3354,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +3365,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +3376,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +3387,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +3398,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +3409,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +3420,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +3431,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +3442,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +3453,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +3464,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +3475,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +3486,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +3497,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +3508,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +3519,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +3530,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +3541,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +3552,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +3563,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +3574,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +3585,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +3596,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +3607,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +3618,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +3629,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +3640,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +3651,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +3662,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +3673,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +3684,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +3695,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +3706,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +3717,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +3728,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +3739,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +3750,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +3761,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +3772,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +3783,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +3794,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +3805,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +3816,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +3827,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +3838,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +3849,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +3860,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +3871,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +3882,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +3893,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +3904,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +3915,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +3926,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +3937,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +3948,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +3959,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +3970,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +3981,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +3992,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +4003,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +4014,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +4025,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +4036,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +4047,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +4058,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +4069,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +4080,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +4091,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +4102,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +4113,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +4124,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +4135,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +4146,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +4157,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +4168,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +4179,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +4190,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +4201,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +4212,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +4223,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +4234,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +4245,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +4256,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +4267,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +4278,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +4289,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +4300,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +4311,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +4322,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +4333,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +4344,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +4355,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +4366,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +4377,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +4388,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +4399,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +4410,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +4421,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +4432,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +4443,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +4454,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +4465,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +4476,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +4487,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +4498,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +4509,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +4520,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +4531,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +4542,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +4553,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +4564,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +4575,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +4586,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +4597,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +4608,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +4619,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +4630,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +4641,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +4652,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +4663,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +4674,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +4685,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +4696,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +4707,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +4718,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +4729,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +4740,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +4751,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +4762,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +4773,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +4784,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +4795,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +4806,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +4817,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +4828,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +4839,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +4850,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +4861,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +4872,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +4883,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +4894,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +4905,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +4916,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +4927,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +4938,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +4949,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +4960,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +4971,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +4982,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +4993,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +5004,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +5015,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +5026,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +5037,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +5048,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +5059,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +5070,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +5081,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +5092,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +5103,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +5114,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +5125,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +5136,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +5147,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +5158,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +5169,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +5180,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +5191,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +5202,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +5213,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +5224,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +5235,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +5246,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +5257,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +5268,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +5279,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +5290,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +5301,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +5312,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +5323,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +5334,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +5345,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +5356,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +5367,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +5378,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +5389,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +5400,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +5411,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +5422,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +5433,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +5444,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +5455,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +5466,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +5477,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +5488,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +5499,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +5510,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +5521,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +5532,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +5543,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +5554,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +5565,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +5576,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +5587,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +5598,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +5609,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +5620,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +5631,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +5642,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +5653,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +5664,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +5675,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +5686,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +5697,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +5708,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +5719,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +5730,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +5741,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +5752,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +5763,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +5774,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +5785,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +5796,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +5807,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +5818,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +5829,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +5840,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +5851,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +5862,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +5873,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +5884,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +5895,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +5906,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +5917,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +5928,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +5939,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +5950,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +5961,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +5972,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +5983,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +5994,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +6005,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +6016,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +6027,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +6038,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +6049,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +6060,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +6071,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +6082,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +6093,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +6104,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +6115,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +6126,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +6137,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +6148,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +6159,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +6170,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +6181,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +6192,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +6203,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +6214,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +6225,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +6236,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +6247,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +6258,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +6269,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +6280,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +6291,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +6302,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +6313,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +6324,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +6335,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +6346,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +6357,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +6368,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +6379,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +6390,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +6401,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +6412,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +6423,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +6434,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +6445,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +6456,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +6467,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +6478,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +6489,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +6500,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +6511,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +6522,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +6533,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +6544,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +6555,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +6566,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +6577,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +6588,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +6599,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +6610,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +6621,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +6632,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +6643,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +6654,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +6665,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +6676,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +6687,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +6698,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +6709,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +6720,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +6731,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +6742,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +6753,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +6764,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +6775,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +6786,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +6797,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +6808,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +6819,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +6830,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +6841,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +6852,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +6863,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +6874,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +6885,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +6896,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +6907,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +6918,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +6929,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +6940,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +6951,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +6962,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +6973,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +6984,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +6995,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +7006,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +7017,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +7028,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +7039,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +7050,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +7061,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +7072,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +7083,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +7094,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +7105,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +7116,7 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +7127,7 @@
     </x:row>
     <x:row r="407" spans="1:3">
       <x:c r="A407" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +7138,7 @@
     </x:row>
     <x:row r="408" spans="1:3">
       <x:c r="A408" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B408" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +7149,7 @@
     </x:row>
     <x:row r="409" spans="1:3">
       <x:c r="A409" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B409" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +7160,7 @@
     </x:row>
     <x:row r="410" spans="1:3">
       <x:c r="A410" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B410" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +7171,7 @@
     </x:row>
     <x:row r="411" spans="1:3">
       <x:c r="A411" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B411" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +7182,7 @@
     </x:row>
     <x:row r="412" spans="1:3">
       <x:c r="A412" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B412" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +7193,7 @@
     </x:row>
     <x:row r="413" spans="1:3">
       <x:c r="A413" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B413" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +7204,7 @@
     </x:row>
     <x:row r="414" spans="1:3">
       <x:c r="A414" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B414" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +7215,7 @@
     </x:row>
     <x:row r="415" spans="1:3">
       <x:c r="A415" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B415" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +7226,7 @@
     </x:row>
     <x:row r="416" spans="1:3">
       <x:c r="A416" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B416" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +7237,7 @@
     </x:row>
     <x:row r="417" spans="1:3">
       <x:c r="A417" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B417" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +7248,7 @@
     </x:row>
     <x:row r="418" spans="1:3">
       <x:c r="A418" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B418" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +7259,7 @@
     </x:row>
     <x:row r="419" spans="1:3">
       <x:c r="A419" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B419" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +7270,7 @@
     </x:row>
     <x:row r="420" spans="1:3">
       <x:c r="A420" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B420" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +7281,7 @@
     </x:row>
     <x:row r="421" spans="1:3">
       <x:c r="A421" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B421" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +7292,7 @@
     </x:row>
     <x:row r="422" spans="1:3">
       <x:c r="A422" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B422" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +7303,7 @@
     </x:row>
     <x:row r="423" spans="1:3">
       <x:c r="A423" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B423" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +7314,7 @@
     </x:row>
     <x:row r="424" spans="1:3">
       <x:c r="A424" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B424" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +7325,7 @@
     </x:row>
     <x:row r="425" spans="1:3">
       <x:c r="A425" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B425" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +7336,7 @@
     </x:row>
     <x:row r="426" spans="1:3">
       <x:c r="A426" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B426" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +7347,7 @@
     </x:row>
     <x:row r="427" spans="1:3">
       <x:c r="A427" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B427" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +7358,7 @@
     </x:row>
     <x:row r="428" spans="1:3">
       <x:c r="A428" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B428" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +7369,7 @@
     </x:row>
     <x:row r="429" spans="1:3">
       <x:c r="A429" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B429" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +7380,7 @@
     </x:row>
     <x:row r="430" spans="1:3">
       <x:c r="A430" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B430" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +7391,7 @@
     </x:row>
     <x:row r="431" spans="1:3">
       <x:c r="A431" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B431" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +7402,7 @@
     </x:row>
     <x:row r="432" spans="1:3">
       <x:c r="A432" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B432" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +7413,7 @@
     </x:row>
     <x:row r="433" spans="1:3">
       <x:c r="A433" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B433" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +7424,7 @@
     </x:row>
     <x:row r="434" spans="1:3">
       <x:c r="A434" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B434" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +7435,7 @@
     </x:row>
     <x:row r="435" spans="1:3">
       <x:c r="A435" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B435" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +7446,7 @@
     </x:row>
     <x:row r="436" spans="1:3">
       <x:c r="A436" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B436" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +7457,7 @@
     </x:row>
     <x:row r="437" spans="1:3">
       <x:c r="A437" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B437" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +7468,7 @@
     </x:row>
     <x:row r="438" spans="1:3">
       <x:c r="A438" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B438" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +7479,7 @@
     </x:row>
     <x:row r="439" spans="1:3">
       <x:c r="A439" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B439" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +7490,7 @@
     </x:row>
     <x:row r="440" spans="1:3">
       <x:c r="A440" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B440" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +7501,7 @@
     </x:row>
     <x:row r="441" spans="1:3">
       <x:c r="A441" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B441" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +7512,7 @@
     </x:row>
     <x:row r="442" spans="1:3">
       <x:c r="A442" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B442" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +7523,7 @@
     </x:row>
     <x:row r="443" spans="1:3">
       <x:c r="A443" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B443" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +7534,7 @@
     </x:row>
     <x:row r="444" spans="1:3">
       <x:c r="A444" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B444" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +7545,7 @@
     </x:row>
     <x:row r="445" spans="1:3">
       <x:c r="A445" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B445" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +7556,7 @@
     </x:row>
     <x:row r="446" spans="1:3">
       <x:c r="A446" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B446" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +7567,7 @@
     </x:row>
     <x:row r="447" spans="1:3">
       <x:c r="A447" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B447" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +7578,7 @@
     </x:row>
     <x:row r="448" spans="1:3">
       <x:c r="A448" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B448" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +7589,7 @@
     </x:row>
     <x:row r="449" spans="1:3">
       <x:c r="A449" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B449" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +7600,7 @@
     </x:row>
     <x:row r="450" spans="1:3">
       <x:c r="A450" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B450" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +7611,7 @@
     </x:row>
     <x:row r="451" spans="1:3">
       <x:c r="A451" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B451" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +7622,7 @@
     </x:row>
     <x:row r="452" spans="1:3">
       <x:c r="A452" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B452" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +7633,7 @@
     </x:row>
     <x:row r="453" spans="1:3">
       <x:c r="A453" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B453" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +7644,7 @@
     </x:row>
     <x:row r="454" spans="1:3">
       <x:c r="A454" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B454" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +7655,7 @@
     </x:row>
     <x:row r="455" spans="1:3">
       <x:c r="A455" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B455" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +7666,7 @@
     </x:row>
     <x:row r="456" spans="1:3">
       <x:c r="A456" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B456" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,7 +7677,7 @@
     </x:row>
     <x:row r="457" spans="1:3">
       <x:c r="A457" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B457" s="0" t="s">
         <x:v>4</x:v>
@@ -8898,7 +7688,7 @@
     </x:row>
     <x:row r="458" spans="1:3">
       <x:c r="A458" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B458" s="0" t="s">
         <x:v>4</x:v>
@@ -8909,7 +7699,7 @@
     </x:row>
     <x:row r="459" spans="1:3">
       <x:c r="A459" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B459" s="0" t="s">
         <x:v>4</x:v>
@@ -8920,7 +7710,7 @@
     </x:row>
     <x:row r="460" spans="1:3">
       <x:c r="A460" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B460" s="0" t="s">
         <x:v>4</x:v>
@@ -8931,7 +7721,7 @@
     </x:row>
     <x:row r="461" spans="1:3">
       <x:c r="A461" s="0" t="s">
-        <x:v>612</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B461" s="0" t="s">
         <x:v>4</x:v>
@@ -8942,7 +7732,7 @@
     </x:row>
     <x:row r="462" spans="1:3">
       <x:c r="A462" s="0" t="s">
-        <x:v>613</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B462" s="0" t="s">
         <x:v>4</x:v>
@@ -8953,12 +7743,1222 @@
     </x:row>
     <x:row r="463" spans="1:3">
       <x:c r="A463" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="B463" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C463" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" spans="1:3">
+      <x:c r="A464" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B464" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C464" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" spans="1:3">
+      <x:c r="A465" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="B465" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C465" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" spans="1:3">
+      <x:c r="A466" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="B466" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C466" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" spans="1:3">
+      <x:c r="A467" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B467" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C467" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" spans="1:3">
+      <x:c r="A468" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="B468" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C468" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" spans="1:3">
+      <x:c r="A469" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="B469" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C469" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" spans="1:3">
+      <x:c r="A470" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="B470" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C470" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" spans="1:3">
+      <x:c r="A471" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="B471" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C471" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472" spans="1:3">
+      <x:c r="A472" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="B472" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C472" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" spans="1:3">
+      <x:c r="A473" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B473" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C473" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" spans="1:3">
+      <x:c r="A474" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="B474" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C474" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" spans="1:3">
+      <x:c r="A475" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="B475" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C475" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" spans="1:3">
+      <x:c r="A476" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B476" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C476" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" spans="1:3">
+      <x:c r="A477" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="B477" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C477" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" spans="1:3">
+      <x:c r="A478" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B478" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C478" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" spans="1:3">
+      <x:c r="A479" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="B479" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C479" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" spans="1:3">
+      <x:c r="A480" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="B480" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C480" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" spans="1:3">
+      <x:c r="A481" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="B481" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C481" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" spans="1:3">
+      <x:c r="A482" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="B482" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C482" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" spans="1:3">
+      <x:c r="A483" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="B483" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C483" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" spans="1:3">
+      <x:c r="A484" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="B484" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C484" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" spans="1:3">
+      <x:c r="A485" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B485" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C485" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" spans="1:3">
+      <x:c r="A486" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="B486" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C486" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" spans="1:3">
+      <x:c r="A487" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="B487" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C487" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" spans="1:3">
+      <x:c r="A488" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B488" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C488" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" spans="1:3">
+      <x:c r="A489" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="B489" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C489" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" spans="1:3">
+      <x:c r="A490" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="B490" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C490" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" spans="1:3">
+      <x:c r="A491" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="B491" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C491" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" spans="1:3">
+      <x:c r="A492" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="B492" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C492" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" spans="1:3">
+      <x:c r="A493" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B493" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C493" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" spans="1:3">
+      <x:c r="A494" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="B494" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C494" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" spans="1:3">
+      <x:c r="A495" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B495" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C495" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" spans="1:3">
+      <x:c r="A496" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="B496" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C496" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" spans="1:3">
+      <x:c r="A497" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="B497" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C497" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" spans="1:3">
+      <x:c r="A498" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="B498" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C498" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" spans="1:3">
+      <x:c r="A499" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B499" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C499" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" spans="1:3">
+      <x:c r="A500" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B500" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C500" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" spans="1:3">
+      <x:c r="A501" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B501" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C501" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" spans="1:3">
+      <x:c r="A502" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="B502" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C502" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" spans="1:3">
+      <x:c r="A503" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B503" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C503" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" spans="1:3">
+      <x:c r="A504" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="B504" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C504" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" spans="1:3">
+      <x:c r="A505" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="B505" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C505" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" spans="1:3">
+      <x:c r="A506" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B506" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C506" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" spans="1:3">
+      <x:c r="A507" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="B507" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C507" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" spans="1:3">
+      <x:c r="A508" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="B508" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C508" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" spans="1:3">
+      <x:c r="A509" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B509" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C509" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" spans="1:3">
+      <x:c r="A510" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="B510" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C510" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" spans="1:3">
+      <x:c r="A511" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="B511" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C511" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" spans="1:3">
+      <x:c r="A512" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B512" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C512" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" spans="1:3">
+      <x:c r="A513" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="B513" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C513" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" spans="1:3">
+      <x:c r="A514" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="B514" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C514" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" spans="1:3">
+      <x:c r="A515" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B515" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C515" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" spans="1:3">
+      <x:c r="A516" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="B516" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C516" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" spans="1:3">
+      <x:c r="A517" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="B517" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C517" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" spans="1:3">
+      <x:c r="A518" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="B518" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C518" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" spans="1:3">
+      <x:c r="A519" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B519" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C519" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" spans="1:3">
+      <x:c r="A520" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="B520" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C520" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" spans="1:3">
+      <x:c r="A521" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="B521" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C521" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" spans="1:3">
+      <x:c r="A522" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="B522" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C522" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" spans="1:3">
+      <x:c r="A523" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="B523" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C523" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" spans="1:3">
+      <x:c r="A524" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="B524" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C524" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" spans="1:3">
+      <x:c r="A525" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B525" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C525" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" spans="1:3">
+      <x:c r="A526" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B526" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C526" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" spans="1:3">
+      <x:c r="A527" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="B527" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C527" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528" spans="1:3">
+      <x:c r="A528" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B528" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C528" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" spans="1:3">
+      <x:c r="A529" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B529" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C529" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" spans="1:3">
+      <x:c r="A530" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="B530" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C530" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" spans="1:3">
+      <x:c r="A531" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B531" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C531" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" spans="1:3">
+      <x:c r="A532" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B532" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C532" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" spans="1:3">
+      <x:c r="A533" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="B533" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C533" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" spans="1:3">
+      <x:c r="A534" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="B534" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C534" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" spans="1:3">
+      <x:c r="A535" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B535" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C535" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536" spans="1:3">
+      <x:c r="A536" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="B536" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C536" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" spans="1:3">
+      <x:c r="A537" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="B537" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C537" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538" spans="1:3">
+      <x:c r="A538" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="B538" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C538" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" spans="1:3">
+      <x:c r="A539" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="B539" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C539" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" spans="1:3">
+      <x:c r="A540" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="B540" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C540" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" spans="1:3">
+      <x:c r="A541" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="B541" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C541" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" spans="1:3">
+      <x:c r="A542" s="0" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B542" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C542" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" spans="1:3">
+      <x:c r="A543" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="B543" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C543" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" spans="1:3">
+      <x:c r="A544" s="0" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B544" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C544" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" spans="1:3">
+      <x:c r="A545" s="0" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="B545" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C545" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546" spans="1:3">
+      <x:c r="A546" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="B546" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C546" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" spans="1:3">
+      <x:c r="A547" s="0" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B547" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C547" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" spans="1:3">
+      <x:c r="A548" s="0" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="B548" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C548" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" spans="1:3">
+      <x:c r="A549" s="0" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="B549" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C549" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550" spans="1:3">
+      <x:c r="A550" s="0" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B550" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C550" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" spans="1:3">
+      <x:c r="A551" s="0" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B551" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C551" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552" spans="1:3">
+      <x:c r="A552" s="0" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="B552" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C552" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" spans="1:3">
+      <x:c r="A553" s="0" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B553" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C553" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" spans="1:3">
+      <x:c r="A554" s="0" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B554" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C554" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" spans="1:3">
+      <x:c r="A555" s="0" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="B555" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C555" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556" spans="1:3">
+      <x:c r="A556" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B556" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C556" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" spans="1:3">
+      <x:c r="A557" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="B557" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C557" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" spans="1:3">
+      <x:c r="A558" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="B558" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C558" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" spans="1:3">
+      <x:c r="A559" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B559" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C559" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560" spans="1:3">
+      <x:c r="A560" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="B560" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C560" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" spans="1:3">
+      <x:c r="A561" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="B561" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C561" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562" spans="1:3">
+      <x:c r="A562" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B562" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C562" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" spans="1:3">
+      <x:c r="A563" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B563" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C563" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564" spans="1:3">
+      <x:c r="A564" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="B564" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C564" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" spans="1:3">
+      <x:c r="A565" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B565" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C565" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566" spans="1:3">
+      <x:c r="A566" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="B566" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C566" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" spans="1:3">
+      <x:c r="A567" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B567" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C567" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568" spans="1:3">
+      <x:c r="A568" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B568" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C568" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" spans="1:3">
+      <x:c r="A569" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="B569" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C569" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570" spans="1:3">
+      <x:c r="A570" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B570" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C570" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" spans="1:3">
+      <x:c r="A571" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B571" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C571" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572" spans="1:3">
+      <x:c r="A572" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B572" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C572" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" spans="1:3">
+      <x:c r="A573" s="0" t="s">
         <x:v>614</x:v>
       </x:c>
-      <x:c r="B463" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C463" s="0" t="s">
+      <x:c r="B573" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C573" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -113,6 +113,9 @@
     <x:t>AYEN</x:t>
   </x:si>
   <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYGAZ</x:t>
   </x:si>
   <x:si>
@@ -125,6 +128,9 @@
     <x:t>BASGZ</x:t>
   </x:si>
   <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
@@ -140,6 +146,9 @@
     <x:t>BTCIM</x:t>
   </x:si>
   <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>BYDNR</x:t>
   </x:si>
   <x:si>
@@ -164,1513 +173,1504 @@
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
     <x:t>CUSAN</x:t>
   </x:si>
   <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
     <x:t>CWENE</x:t>
   </x:si>
   <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
   </x:si>
   <x:si>
     <x:t>ENSRI</x:t>
   </x:si>
   <x:si>
-    <x:t>ENTRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
   </x:si>
   <x:si>
     <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAVHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SERNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
   </x:si>
   <x:si>
     <x:t>TBORG</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C162"/>
+  <x:dimension ref="A1:C165"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -3992,6 +3992,39 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:3">
+      <x:c r="A163" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:3">
+      <x:c r="A164" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:3">
+      <x:c r="A165" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4009,7 +4042,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C450"/>
+  <x:dimension ref="A1:C447"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4025,7 +4058,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4036,7 +4069,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4047,7 +4080,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4058,7 +4091,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4069,7 +4102,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4080,7 +4113,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4091,7 +4124,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4102,7 +4135,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4113,7 +4146,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4124,7 +4157,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4135,7 +4168,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4146,7 +4179,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4157,7 +4190,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4168,7 +4201,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4179,7 +4212,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4190,7 +4223,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4201,7 +4234,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4212,7 +4245,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4223,7 +4256,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4234,7 +4267,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4245,7 +4278,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4256,7 +4289,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4267,7 +4300,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4278,7 +4311,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4289,7 +4322,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4300,7 +4333,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4311,7 +4344,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4322,7 +4355,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4333,7 +4366,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4344,7 +4377,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4355,7 +4388,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4366,7 +4399,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4377,7 +4410,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4388,7 +4421,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4399,7 +4432,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4410,7 +4443,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4421,7 +4454,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4432,7 +4465,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4443,7 +4476,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4454,7 +4487,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4465,7 +4498,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4476,7 +4509,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +4520,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4531,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4542,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4553,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4564,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4575,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4586,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4597,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4608,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4619,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4630,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4641,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4652,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4663,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4674,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4685,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4696,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4707,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4718,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4729,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4740,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4751,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4762,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4773,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4784,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4795,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4806,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4817,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4828,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4839,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4850,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4861,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4872,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4883,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4894,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4905,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4916,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4927,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4938,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4949,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +4960,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +4971,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +4982,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +4993,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +5004,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +5015,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +5026,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +5037,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +5048,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +5059,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +5070,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +5081,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +5092,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +5103,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +5114,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +5125,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +5136,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +5147,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +5158,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +5169,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +5180,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +5191,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +5202,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +5213,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5224,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5235,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5246,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5257,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5268,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5279,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5290,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5301,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5312,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5323,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5334,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5345,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5356,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5367,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5378,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5389,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5400,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5411,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5422,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5433,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5444,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5455,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5466,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5477,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5488,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5499,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5510,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5521,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5532,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5543,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5554,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5565,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5576,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5587,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5598,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5609,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5620,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5631,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5642,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5653,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5664,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5675,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5686,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5697,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5708,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5719,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5730,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5741,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5752,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5763,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5774,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5785,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5796,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5807,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5818,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5829,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5840,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5851,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5862,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +5873,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +5884,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +5895,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +5906,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +5917,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +5928,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +5939,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +5950,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +5961,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +5972,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +5983,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +5994,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +6005,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +6016,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +6027,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +6038,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +6049,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +6060,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +6071,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +6082,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +6093,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +6104,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +6115,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +6126,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +6137,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +6148,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +6159,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +6170,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +6181,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +6192,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +6203,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +6214,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6225,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6236,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6247,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6258,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6269,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6280,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6291,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6302,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6313,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6324,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6335,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6346,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6357,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6368,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6379,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6390,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6401,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6412,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6423,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6434,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6445,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6456,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6467,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6478,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6489,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6500,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6511,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6522,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6533,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6544,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6555,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6566,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6577,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6588,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6599,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6610,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6621,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6632,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6643,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6654,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6665,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6676,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6687,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6698,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6709,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6720,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6731,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6742,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6753,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6764,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6775,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6786,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6797,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6808,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6819,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6830,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6841,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6852,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6863,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +6874,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +6885,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +6896,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +6907,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +6918,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +6929,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +6940,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +6951,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +6962,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +6973,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +6984,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +6995,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +7006,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +7017,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +7028,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +7039,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +7050,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +7061,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +7072,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +7083,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +7094,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +7105,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +7116,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +7127,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +7138,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +7149,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +7160,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +7171,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +7182,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +7193,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +7204,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +7215,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7226,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7237,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7248,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7259,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7270,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7281,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7292,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7303,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7314,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7325,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7336,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7347,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7358,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7369,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7380,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7391,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7402,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7413,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7424,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7435,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7446,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7457,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7468,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7479,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7490,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7501,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7512,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7523,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7534,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7545,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7556,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7567,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7578,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7589,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7600,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7611,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7622,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7633,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7644,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7655,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7666,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7677,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7688,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7699,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7710,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7721,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7732,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7743,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7754,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7765,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7776,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7787,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7798,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7809,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7820,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7831,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7842,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7853,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7864,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +7875,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +7886,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +7897,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +7908,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +7919,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +7930,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +7941,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +7952,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +7963,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +7974,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +7985,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +7996,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +8007,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +8018,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +8029,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +8040,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +8051,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +8062,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +8073,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +8084,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +8095,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +8106,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +8117,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +8128,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +8139,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +8150,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +8161,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +8172,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +8183,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +8194,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +8205,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +8216,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8227,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8238,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8249,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8260,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8271,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8282,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8293,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8304,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8315,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8326,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8337,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8348,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8359,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8370,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8381,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8392,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8403,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8414,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8425,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8436,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8447,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8458,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8469,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8480,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8491,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8502,7 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8513,7 @@
     </x:row>
     <x:row r="407" spans="1:3">
       <x:c r="A407" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8524,7 @@
     </x:row>
     <x:row r="408" spans="1:3">
       <x:c r="A408" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B408" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8535,7 @@
     </x:row>
     <x:row r="409" spans="1:3">
       <x:c r="A409" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B409" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8546,7 @@
     </x:row>
     <x:row r="410" spans="1:3">
       <x:c r="A410" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B410" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8557,7 @@
     </x:row>
     <x:row r="411" spans="1:3">
       <x:c r="A411" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B411" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8568,7 @@
     </x:row>
     <x:row r="412" spans="1:3">
       <x:c r="A412" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B412" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8579,7 @@
     </x:row>
     <x:row r="413" spans="1:3">
       <x:c r="A413" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B413" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8590,7 @@
     </x:row>
     <x:row r="414" spans="1:3">
       <x:c r="A414" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B414" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8601,7 @@
     </x:row>
     <x:row r="415" spans="1:3">
       <x:c r="A415" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B415" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8612,7 @@
     </x:row>
     <x:row r="416" spans="1:3">
       <x:c r="A416" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B416" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8623,7 @@
     </x:row>
     <x:row r="417" spans="1:3">
       <x:c r="A417" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B417" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8634,7 @@
     </x:row>
     <x:row r="418" spans="1:3">
       <x:c r="A418" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B418" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8645,7 @@
     </x:row>
     <x:row r="419" spans="1:3">
       <x:c r="A419" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B419" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8656,7 @@
     </x:row>
     <x:row r="420" spans="1:3">
       <x:c r="A420" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B420" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8667,7 @@
     </x:row>
     <x:row r="421" spans="1:3">
       <x:c r="A421" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B421" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8678,7 @@
     </x:row>
     <x:row r="422" spans="1:3">
       <x:c r="A422" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B422" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8689,7 @@
     </x:row>
     <x:row r="423" spans="1:3">
       <x:c r="A423" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B423" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8700,7 @@
     </x:row>
     <x:row r="424" spans="1:3">
       <x:c r="A424" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B424" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8711,7 @@
     </x:row>
     <x:row r="425" spans="1:3">
       <x:c r="A425" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B425" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8722,7 @@
     </x:row>
     <x:row r="426" spans="1:3">
       <x:c r="A426" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B426" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8733,7 @@
     </x:row>
     <x:row r="427" spans="1:3">
       <x:c r="A427" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B427" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8744,7 @@
     </x:row>
     <x:row r="428" spans="1:3">
       <x:c r="A428" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B428" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8755,7 @@
     </x:row>
     <x:row r="429" spans="1:3">
       <x:c r="A429" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B429" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8766,7 @@
     </x:row>
     <x:row r="430" spans="1:3">
       <x:c r="A430" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B430" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8777,7 @@
     </x:row>
     <x:row r="431" spans="1:3">
       <x:c r="A431" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B431" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8788,7 @@
     </x:row>
     <x:row r="432" spans="1:3">
       <x:c r="A432" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B432" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8799,7 @@
     </x:row>
     <x:row r="433" spans="1:3">
       <x:c r="A433" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B433" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8810,7 @@
     </x:row>
     <x:row r="434" spans="1:3">
       <x:c r="A434" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B434" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +8821,7 @@
     </x:row>
     <x:row r="435" spans="1:3">
       <x:c r="A435" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B435" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +8832,7 @@
     </x:row>
     <x:row r="436" spans="1:3">
       <x:c r="A436" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B436" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +8843,7 @@
     </x:row>
     <x:row r="437" spans="1:3">
       <x:c r="A437" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B437" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +8854,7 @@
     </x:row>
     <x:row r="438" spans="1:3">
       <x:c r="A438" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B438" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +8865,7 @@
     </x:row>
     <x:row r="439" spans="1:3">
       <x:c r="A439" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B439" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +8876,7 @@
     </x:row>
     <x:row r="440" spans="1:3">
       <x:c r="A440" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B440" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +8887,7 @@
     </x:row>
     <x:row r="441" spans="1:3">
       <x:c r="A441" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B441" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +8898,7 @@
     </x:row>
     <x:row r="442" spans="1:3">
       <x:c r="A442" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B442" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +8909,7 @@
     </x:row>
     <x:row r="443" spans="1:3">
       <x:c r="A443" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B443" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,7 +8920,7 @@
     </x:row>
     <x:row r="444" spans="1:3">
       <x:c r="A444" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B444" s="0" t="s">
         <x:v>4</x:v>
@@ -8898,7 +8931,7 @@
     </x:row>
     <x:row r="445" spans="1:3">
       <x:c r="A445" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B445" s="0" t="s">
         <x:v>4</x:v>
@@ -8909,7 +8942,7 @@
     </x:row>
     <x:row r="446" spans="1:3">
       <x:c r="A446" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B446" s="0" t="s">
         <x:v>4</x:v>
@@ -8920,45 +8953,12 @@
     </x:row>
     <x:row r="447" spans="1:3">
       <x:c r="A447" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B447" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C447" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="448" spans="1:3">
-      <x:c r="A448" s="0" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="B448" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C448" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="449" spans="1:3">
-      <x:c r="A449" s="0" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="B449" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C449" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="450" spans="1:3">
-      <x:c r="A450" s="0" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B450" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C450" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -44,1750 +44,1750 @@
     <x:t>AGESA</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASUZU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>AKFIS</x:t>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
   </x:si>
   <x:si>
     <x:t>AKFYE</x:t>
   </x:si>
   <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
   </x:si>
   <x:si>
     <x:t>ASTOR</x:t>
   </x:si>
   <x:si>
-    <x:t>ASUZU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIMSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAVHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TBORG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSPOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTRAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUREX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UCAYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UMPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SERNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TBORG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSPOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTRAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUREX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURGG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UCAYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UMPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
   </x:si>
   <x:si>
     <x:t>VESBE</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C165"/>
+  <x:dimension ref="A1:C180"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4025,6 +4025,171 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:3">
+      <x:c r="A166" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:3">
+      <x:c r="A167" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:3">
+      <x:c r="A168" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:3">
+      <x:c r="A169" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:3">
+      <x:c r="A170" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:3">
+      <x:c r="A171" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:3">
+      <x:c r="A172" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:3">
+      <x:c r="A173" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:3">
+      <x:c r="A174" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:3">
+      <x:c r="A175" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:3">
+      <x:c r="A176" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:3">
+      <x:c r="A177" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:3">
+      <x:c r="A178" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C178" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:3">
+      <x:c r="A179" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:3">
+      <x:c r="A180" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4042,7 +4207,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C447"/>
+  <x:dimension ref="A1:C432"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4058,7 +4223,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4069,7 +4234,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4080,7 +4245,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4091,7 +4256,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4102,7 +4267,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4113,7 +4278,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4124,7 +4289,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4135,7 +4300,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4146,7 +4311,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4157,7 +4322,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4168,7 +4333,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4179,7 +4344,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4190,7 +4355,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4201,7 +4366,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4212,7 +4377,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4223,7 +4388,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4234,7 +4399,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4245,7 +4410,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4256,7 +4421,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4267,7 +4432,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4278,7 +4443,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4289,7 +4454,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4300,7 +4465,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4311,7 +4476,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4322,7 +4487,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4333,7 +4498,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4344,7 +4509,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4355,7 +4520,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4366,7 +4531,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4377,7 +4542,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4388,7 +4553,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4399,7 +4564,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4410,7 +4575,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4421,7 +4586,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4432,7 +4597,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4443,7 +4608,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4454,7 +4619,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4465,7 +4630,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4476,7 +4641,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +4652,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4663,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4674,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4685,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4696,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4707,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4718,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4729,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4740,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4751,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4762,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4773,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4784,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4795,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4806,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4817,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4828,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4839,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4850,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4861,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4872,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4883,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4894,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4905,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4916,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4927,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4938,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4949,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4960,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4971,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4982,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4993,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +5004,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +5015,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +5026,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +5037,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +5048,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +5059,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +5070,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +5081,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +5092,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +5103,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +5114,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +5125,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +5136,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +5147,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +5158,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +5169,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +5180,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +5191,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +5202,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +5213,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +5224,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +5235,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +5246,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +5257,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +5268,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +5279,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +5290,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +5301,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +5312,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +5323,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +5334,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +5345,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5356,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5367,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5378,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5389,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5400,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5411,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5422,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5433,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5444,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5455,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5466,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5477,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5488,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5499,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5510,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5521,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5532,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5543,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5554,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5565,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5576,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5587,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5598,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5609,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5620,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5631,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5642,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5653,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5664,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5675,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5686,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5697,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5708,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5719,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5730,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5741,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5752,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5763,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5774,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5785,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5796,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5807,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5818,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5829,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5840,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5851,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5862,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5873,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5884,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5895,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5906,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5917,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5928,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5939,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5950,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5961,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5972,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5983,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5994,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +6005,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +6016,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +6027,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +6038,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +6049,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +6060,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +6071,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +6082,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +6093,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +6104,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +6115,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +6126,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +6137,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +6148,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +6159,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +6170,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +6181,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +6192,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +6203,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +6214,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +6225,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +6236,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +6247,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +6258,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +6269,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +6280,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +6291,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +6302,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +6313,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +6324,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +6335,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +6346,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6357,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6368,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6379,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6390,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6401,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6412,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6423,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6434,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6445,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6456,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6467,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6478,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6489,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6500,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6511,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6522,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6533,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6544,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6555,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6566,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6577,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6588,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6599,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6610,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6621,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6632,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6643,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6654,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6665,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6676,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6687,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6698,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6709,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6720,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6731,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6742,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6753,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6764,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6775,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6786,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6797,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6808,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6819,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6830,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6841,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6852,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6863,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6874,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6885,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6896,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6907,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6918,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6929,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6940,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6951,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6962,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6973,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6984,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6995,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +7006,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +7017,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +7028,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +7039,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +7050,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +7061,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +7072,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +7083,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +7094,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +7105,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +7116,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +7127,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +7138,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +7149,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +7160,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +7171,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +7182,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +7193,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +7204,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +7215,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +7226,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +7237,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +7248,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +7259,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +7270,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +7281,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +7292,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +7303,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +7314,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +7325,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +7336,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +7347,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7358,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7369,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7380,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7391,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7402,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7413,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7424,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7435,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7446,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7457,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7468,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7479,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7490,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7501,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7512,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7523,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7534,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7545,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7556,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7567,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7578,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7589,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7600,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7611,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7622,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7633,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7644,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7655,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7666,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7677,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7688,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7699,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7710,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7721,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7732,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7743,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7754,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7765,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7776,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7787,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7798,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7809,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7820,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7831,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7842,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7853,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7864,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7875,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7886,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7897,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7908,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7919,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7930,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7941,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7952,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7963,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7974,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7985,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7996,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +8007,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +8018,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +8029,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +8040,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +8051,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +8062,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +8073,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +8084,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +8095,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +8106,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +8117,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +8128,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +8139,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +8150,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +8161,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +8172,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +8183,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +8194,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +8205,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +8216,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +8227,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +8238,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +8249,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +8260,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +8271,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +8282,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +8293,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +8304,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +8315,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +8326,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +8337,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +8348,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8359,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8370,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8381,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8392,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8403,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8414,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8425,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8436,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8447,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8458,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8469,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8480,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8491,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8502,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8513,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8524,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8535,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8546,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8557,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8568,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8579,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8590,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8601,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8612,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8623,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8634,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8645,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8656,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8667,7 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8678,7 @@
     </x:row>
     <x:row r="407" spans="1:3">
       <x:c r="A407" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8689,7 @@
     </x:row>
     <x:row r="408" spans="1:3">
       <x:c r="A408" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B408" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8700,7 @@
     </x:row>
     <x:row r="409" spans="1:3">
       <x:c r="A409" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B409" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8711,7 @@
     </x:row>
     <x:row r="410" spans="1:3">
       <x:c r="A410" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B410" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8722,7 @@
     </x:row>
     <x:row r="411" spans="1:3">
       <x:c r="A411" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B411" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8733,7 @@
     </x:row>
     <x:row r="412" spans="1:3">
       <x:c r="A412" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B412" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8744,7 @@
     </x:row>
     <x:row r="413" spans="1:3">
       <x:c r="A413" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B413" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8755,7 @@
     </x:row>
     <x:row r="414" spans="1:3">
       <x:c r="A414" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B414" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8766,7 @@
     </x:row>
     <x:row r="415" spans="1:3">
       <x:c r="A415" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B415" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8777,7 @@
     </x:row>
     <x:row r="416" spans="1:3">
       <x:c r="A416" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B416" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8788,7 @@
     </x:row>
     <x:row r="417" spans="1:3">
       <x:c r="A417" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B417" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8799,7 @@
     </x:row>
     <x:row r="418" spans="1:3">
       <x:c r="A418" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B418" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8810,7 @@
     </x:row>
     <x:row r="419" spans="1:3">
       <x:c r="A419" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B419" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8821,7 @@
     </x:row>
     <x:row r="420" spans="1:3">
       <x:c r="A420" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B420" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8832,7 @@
     </x:row>
     <x:row r="421" spans="1:3">
       <x:c r="A421" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B421" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8843,7 @@
     </x:row>
     <x:row r="422" spans="1:3">
       <x:c r="A422" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B422" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8854,7 @@
     </x:row>
     <x:row r="423" spans="1:3">
       <x:c r="A423" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B423" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8865,7 @@
     </x:row>
     <x:row r="424" spans="1:3">
       <x:c r="A424" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B424" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8876,7 @@
     </x:row>
     <x:row r="425" spans="1:3">
       <x:c r="A425" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B425" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8887,7 @@
     </x:row>
     <x:row r="426" spans="1:3">
       <x:c r="A426" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B426" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8898,7 @@
     </x:row>
     <x:row r="427" spans="1:3">
       <x:c r="A427" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B427" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8909,7 @@
     </x:row>
     <x:row r="428" spans="1:3">
       <x:c r="A428" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B428" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8920,7 @@
     </x:row>
     <x:row r="429" spans="1:3">
       <x:c r="A429" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B429" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8931,7 @@
     </x:row>
     <x:row r="430" spans="1:3">
       <x:c r="A430" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B430" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8942,7 @@
     </x:row>
     <x:row r="431" spans="1:3">
       <x:c r="A431" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B431" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,177 +8953,12 @@
     </x:row>
     <x:row r="432" spans="1:3">
       <x:c r="A432" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B432" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C432" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="433" spans="1:3">
-      <x:c r="A433" s="0" t="s">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="B433" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C433" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="434" spans="1:3">
-      <x:c r="A434" s="0" t="s">
-        <x:v>601</x:v>
-      </x:c>
-      <x:c r="B434" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C434" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="435" spans="1:3">
-      <x:c r="A435" s="0" t="s">
-        <x:v>602</x:v>
-      </x:c>
-      <x:c r="B435" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C435" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="436" spans="1:3">
-      <x:c r="A436" s="0" t="s">
-        <x:v>603</x:v>
-      </x:c>
-      <x:c r="B436" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C436" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="437" spans="1:3">
-      <x:c r="A437" s="0" t="s">
-        <x:v>604</x:v>
-      </x:c>
-      <x:c r="B437" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C437" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="438" spans="1:3">
-      <x:c r="A438" s="0" t="s">
-        <x:v>605</x:v>
-      </x:c>
-      <x:c r="B438" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C438" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="439" spans="1:3">
-      <x:c r="A439" s="0" t="s">
-        <x:v>606</x:v>
-      </x:c>
-      <x:c r="B439" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C439" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="440" spans="1:3">
-      <x:c r="A440" s="0" t="s">
-        <x:v>607</x:v>
-      </x:c>
-      <x:c r="B440" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C440" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="441" spans="1:3">
-      <x:c r="A441" s="0" t="s">
-        <x:v>608</x:v>
-      </x:c>
-      <x:c r="B441" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C441" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="442" spans="1:3">
-      <x:c r="A442" s="0" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="B442" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C442" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="443" spans="1:3">
-      <x:c r="A443" s="0" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="B443" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C443" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="444" spans="1:3">
-      <x:c r="A444" s="0" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="B444" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C444" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="445" spans="1:3">
-      <x:c r="A445" s="0" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="B445" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C445" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="446" spans="1:3">
-      <x:c r="A446" s="0" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="B446" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C446" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="447" spans="1:3">
-      <x:c r="A447" s="0" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B447" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C447" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -41,6 +41,9 @@
     <x:t>ADGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>AEFES</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGESA</x:t>
   </x:si>
   <x:si>
@@ -113,1389 +116,1395 @@
     <x:t>AYCES</x:t>
   </x:si>
   <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYDEM</x:t>
   </x:si>
   <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
   </x:si>
   <x:si>
     <x:t>BASGZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
   </x:si>
   <x:si>
     <x:t>BRMEN</x:t>
   </x:si>
   <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
   </x:si>
   <x:si>
     <x:t>BYDNR</x:t>
   </x:si>
   <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIMSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
   </x:si>
   <x:si>
     <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
   </x:si>
   <x:si>
     <x:t>OZRDN</x:t>
   </x:si>
   <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAVHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AEFES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
     <x:t>OZYSR</x:t>
   </x:si>
   <x:si>
@@ -1547,9 +1556,6 @@
     <x:t>PRKME</x:t>
   </x:si>
   <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
     <x:t>PSDTC</x:t>
   </x:si>
   <x:si>
@@ -1670,9 +1676,6 @@
     <x:t>SVGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
     <x:t>TARKM</x:t>
   </x:si>
   <x:si>
@@ -1785,9 +1788,6 @@
   </x:si>
   <x:si>
     <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
   </x:si>
   <x:si>
     <x:t>VESBE</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C180"/>
+  <x:dimension ref="A1:C183"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4190,6 +4190,39 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C180" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:3">
+      <x:c r="A181" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C181" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:3">
+      <x:c r="A182" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:3">
+      <x:c r="A183" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4207,7 +4240,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C432"/>
+  <x:dimension ref="A1:C429"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4223,7 +4256,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4234,7 +4267,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4245,7 +4278,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4256,7 +4289,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4267,7 +4300,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4278,7 +4311,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4289,7 +4322,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4300,7 +4333,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4311,7 +4344,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4322,7 +4355,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4333,7 +4366,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4344,7 +4377,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4355,7 +4388,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4366,7 +4399,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4377,7 +4410,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4388,7 +4421,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4399,7 +4432,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4410,7 +4443,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4421,7 +4454,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4432,7 +4465,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4443,7 +4476,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4454,7 +4487,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4465,7 +4498,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4476,7 +4509,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +4520,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4531,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4542,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4553,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4564,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4575,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4586,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4597,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4608,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4619,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4630,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4641,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4652,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4663,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4674,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4685,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4696,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4707,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4718,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4729,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4740,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4751,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4762,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4773,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4784,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4795,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4806,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4817,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4828,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4839,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4850,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4861,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4872,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4883,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4894,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4905,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4916,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4927,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4938,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4949,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +4960,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +4971,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +4982,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +4993,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +5004,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +5015,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +5026,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +5037,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +5048,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +5059,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +5070,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +5081,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +5092,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +5103,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +5114,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +5125,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +5136,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +5147,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +5158,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +5169,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +5180,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +5191,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +5202,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +5213,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5224,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5235,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5246,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5257,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5268,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5279,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5290,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5301,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5312,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5323,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5334,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5345,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5356,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5367,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5378,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5389,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5400,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5411,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5422,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5433,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5444,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5455,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5466,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5477,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5488,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5499,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5510,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5521,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5532,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5543,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5554,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5565,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5576,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5587,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5598,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5609,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5620,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5631,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5642,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5653,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5664,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5675,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5686,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5697,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5708,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5719,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5730,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5741,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5752,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5763,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5774,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5785,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5796,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5807,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5818,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5829,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5840,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5851,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5862,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +5873,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +5884,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +5895,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +5906,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +5917,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +5928,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +5939,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +5950,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +5961,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +5972,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +5983,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +5994,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +6005,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +6016,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +6027,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +6038,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +6049,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +6060,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +6071,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +6082,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +6093,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +6104,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +6115,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +6126,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +6137,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +6148,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +6159,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +6170,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +6181,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +6192,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +6203,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +6214,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6225,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6236,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6247,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6258,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6269,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6280,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6291,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6302,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6313,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6324,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6335,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6346,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6357,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6368,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6379,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6390,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6401,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6412,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6423,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6434,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6445,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6456,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6467,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6478,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6489,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6500,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6511,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6522,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6533,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6544,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6555,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6566,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6577,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6588,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6599,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6610,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6621,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6632,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6643,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6654,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6665,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6676,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6687,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6698,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6709,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6720,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6731,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6742,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6753,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6764,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6775,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6786,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6797,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6808,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6819,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6830,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6841,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6852,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6863,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +6874,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +6885,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +6896,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +6907,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +6918,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +6929,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +6940,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +6951,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +6962,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +6973,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +6984,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +6995,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +7006,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +7017,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +7028,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +7039,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +7050,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +7061,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +7072,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +7083,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +7094,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +7105,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +7116,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +7127,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +7138,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +7149,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +7160,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +7171,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +7182,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +7193,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +7204,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +7215,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7226,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7237,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7248,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7259,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7270,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7281,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7292,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7303,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7314,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7325,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7336,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7347,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7358,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7369,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7380,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7391,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7402,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7413,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7424,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7435,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7446,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7457,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7468,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7479,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7490,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7501,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7512,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7523,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7534,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7545,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7556,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7567,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7578,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7589,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7600,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7611,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7622,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7633,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7644,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7655,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7666,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7677,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7688,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7699,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7710,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7721,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7732,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7743,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7754,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7765,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7776,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7787,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7798,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7809,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7820,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7831,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7842,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7853,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7864,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +7875,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +7886,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +7897,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +7908,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +7919,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +7930,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +7941,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +7952,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +7963,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +7974,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +7985,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +7996,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +8007,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +8018,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +8029,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +8040,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +8051,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +8062,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +8073,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +8084,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +8095,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +8106,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +8117,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +8128,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +8139,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +8150,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +8161,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +8172,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +8183,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +8194,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +8205,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +8216,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8227,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8238,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8249,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8260,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8271,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8282,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8293,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8304,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8315,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8326,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8337,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8348,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8359,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8370,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8381,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8392,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8403,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8414,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8425,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8436,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8447,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8458,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8469,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8480,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8491,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8502,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8513,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8524,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8535,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8546,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8557,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8568,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8579,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8590,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8601,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8612,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8623,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8634,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8645,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8656,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8667,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8678,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8689,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8700,7 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8711,7 @@
     </x:row>
     <x:row r="407" spans="1:3">
       <x:c r="A407" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8722,7 @@
     </x:row>
     <x:row r="408" spans="1:3">
       <x:c r="A408" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B408" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8733,7 @@
     </x:row>
     <x:row r="409" spans="1:3">
       <x:c r="A409" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B409" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8744,7 @@
     </x:row>
     <x:row r="410" spans="1:3">
       <x:c r="A410" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B410" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8755,7 @@
     </x:row>
     <x:row r="411" spans="1:3">
       <x:c r="A411" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B411" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8766,7 @@
     </x:row>
     <x:row r="412" spans="1:3">
       <x:c r="A412" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B412" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8777,7 @@
     </x:row>
     <x:row r="413" spans="1:3">
       <x:c r="A413" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B413" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8788,7 @@
     </x:row>
     <x:row r="414" spans="1:3">
       <x:c r="A414" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B414" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8799,7 @@
     </x:row>
     <x:row r="415" spans="1:3">
       <x:c r="A415" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B415" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8810,7 @@
     </x:row>
     <x:row r="416" spans="1:3">
       <x:c r="A416" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B416" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +8821,7 @@
     </x:row>
     <x:row r="417" spans="1:3">
       <x:c r="A417" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B417" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +8832,7 @@
     </x:row>
     <x:row r="418" spans="1:3">
       <x:c r="A418" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B418" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +8843,7 @@
     </x:row>
     <x:row r="419" spans="1:3">
       <x:c r="A419" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B419" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +8854,7 @@
     </x:row>
     <x:row r="420" spans="1:3">
       <x:c r="A420" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B420" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +8865,7 @@
     </x:row>
     <x:row r="421" spans="1:3">
       <x:c r="A421" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B421" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +8876,7 @@
     </x:row>
     <x:row r="422" spans="1:3">
       <x:c r="A422" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B422" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +8887,7 @@
     </x:row>
     <x:row r="423" spans="1:3">
       <x:c r="A423" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B423" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +8898,7 @@
     </x:row>
     <x:row r="424" spans="1:3">
       <x:c r="A424" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B424" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +8909,7 @@
     </x:row>
     <x:row r="425" spans="1:3">
       <x:c r="A425" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B425" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,7 +8920,7 @@
     </x:row>
     <x:row r="426" spans="1:3">
       <x:c r="A426" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B426" s="0" t="s">
         <x:v>4</x:v>
@@ -8898,7 +8931,7 @@
     </x:row>
     <x:row r="427" spans="1:3">
       <x:c r="A427" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B427" s="0" t="s">
         <x:v>4</x:v>
@@ -8909,7 +8942,7 @@
     </x:row>
     <x:row r="428" spans="1:3">
       <x:c r="A428" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B428" s="0" t="s">
         <x:v>4</x:v>
@@ -8920,45 +8953,12 @@
     </x:row>
     <x:row r="429" spans="1:3">
       <x:c r="A429" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B429" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C429" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="430" spans="1:3">
-      <x:c r="A430" s="0" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="B430" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C430" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="431" spans="1:3">
-      <x:c r="A431" s="0" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="B431" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C431" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="432" spans="1:3">
-      <x:c r="A432" s="0" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B432" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C432" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -47,6 +47,12 @@
     <x:t>AGESA</x:t>
   </x:si>
   <x:si>
+    <x:t>AGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
@@ -251,993 +257,999 @@
     <x:t>EUKYO</x:t>
   </x:si>
   <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
     <x:t>EUPWR</x:t>
   </x:si>
   <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
   </x:si>
   <x:si>
     <x:t>KERVN</x:t>
   </x:si>
   <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAVHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
     <x:t>KFEIN</x:t>
   </x:si>
   <x:si>
@@ -1316,9 +1328,6 @@
     <x:t>KZGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
     <x:t>LINK</x:t>
   </x:si>
   <x:si>
@@ -1460,9 +1469,6 @@
     <x:t>OFSYM</x:t>
   </x:si>
   <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
     <x:t>ONRYT</x:t>
   </x:si>
   <x:si>
@@ -1529,9 +1535,6 @@
     <x:t>PCILT</x:t>
   </x:si>
   <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
     <x:t>PENTA</x:t>
   </x:si>
   <x:si>
@@ -1611,9 +1614,6 @@
   </x:si>
   <x:si>
     <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
   </x:si>
   <x:si>
     <x:t>SEGYO</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C183"/>
+  <x:dimension ref="A1:C189"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4223,6 +4223,72 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C183" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:3">
+      <x:c r="A184" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:3">
+      <x:c r="A185" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:3">
+      <x:c r="A186" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:3">
+      <x:c r="A187" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C187" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:3">
+      <x:c r="A188" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:3">
+      <x:c r="A189" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C189" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4240,7 +4306,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C429"/>
+  <x:dimension ref="A1:C423"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4256,7 +4322,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4267,7 +4333,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4278,7 +4344,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4289,7 +4355,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4300,7 +4366,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4311,7 +4377,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4322,7 +4388,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4333,7 +4399,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4344,7 +4410,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4355,7 +4421,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4366,7 +4432,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4377,7 +4443,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4388,7 +4454,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4399,7 +4465,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4410,7 +4476,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4421,7 +4487,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4432,7 +4498,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4443,7 +4509,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4454,7 +4520,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4465,7 +4531,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4476,7 +4542,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +4553,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4564,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4575,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4586,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4597,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4608,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4619,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4630,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4641,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4652,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4663,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4674,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4685,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4696,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4707,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4718,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4729,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4740,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4751,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4762,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4773,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4784,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4795,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4806,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4817,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4828,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4839,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4850,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4861,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4872,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4883,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4894,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4905,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4916,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4927,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4938,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4949,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4960,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4971,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4982,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +4993,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +5004,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +5015,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +5026,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +5037,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +5048,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +5059,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +5070,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +5081,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +5092,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +5103,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +5114,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +5125,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +5136,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +5147,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +5158,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +5169,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +5180,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +5191,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +5202,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +5213,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +5224,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +5235,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +5246,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5257,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5268,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5279,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5290,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5301,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5312,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5323,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5334,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5345,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5356,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5367,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5378,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5389,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5400,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5411,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5422,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5433,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5444,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5455,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5466,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5477,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5488,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5499,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5510,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5521,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5532,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5543,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5554,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5565,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5576,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5587,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5598,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5609,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5620,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5631,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5642,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5653,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5664,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5675,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5686,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5697,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5708,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5719,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5730,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5741,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5752,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5763,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5774,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5785,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5796,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5807,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5818,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5829,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5840,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5851,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5862,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5873,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5884,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5895,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +5906,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +5917,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +5928,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +5939,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +5950,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +5961,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +5972,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +5983,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +5994,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +6005,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +6016,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +6027,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +6038,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +6049,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +6060,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +6071,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +6082,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +6093,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +6104,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +6115,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +6126,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +6137,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +6148,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +6159,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +6170,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +6181,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +6192,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +6203,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +6214,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +6225,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +6236,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +6247,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6258,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6269,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6280,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6291,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6302,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6313,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6324,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6335,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6346,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6357,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6368,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6379,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6390,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6401,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6412,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6423,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6434,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6445,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6456,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6467,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6478,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6489,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6500,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6511,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6522,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6533,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6544,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6555,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6566,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6577,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6588,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6599,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6610,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6621,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6632,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6643,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6654,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6665,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6676,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6687,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6698,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6709,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6720,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6731,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6742,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6753,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6764,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6775,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6786,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6797,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6808,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6819,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6830,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6841,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6852,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6863,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6874,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6885,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6896,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +6907,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +6918,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +6929,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +6940,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +6951,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +6962,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +6973,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +6984,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +6995,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +7006,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +7017,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +7028,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +7039,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +7050,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +7061,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +7072,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +7083,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +7094,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +7105,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +7116,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +7127,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +7138,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +7149,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +7160,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +7171,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +7182,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +7193,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +7204,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +7215,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +7226,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +7237,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +7248,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7259,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7270,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7281,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7292,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7303,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7314,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7325,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7336,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7347,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7358,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7369,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7380,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7391,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7402,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7413,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7424,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7435,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7446,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7457,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7468,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7479,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7490,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7501,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7512,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7523,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7534,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7545,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7556,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7567,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7578,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7589,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7600,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7611,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7622,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7633,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7644,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7655,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7666,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7677,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7688,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7699,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7710,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7721,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7732,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7743,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7754,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7765,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7776,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7787,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7798,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7809,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7820,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7831,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7842,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7853,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7864,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7875,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7886,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7897,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +7908,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +7919,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +7930,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +7941,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +7952,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +7963,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +7974,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +7985,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +7996,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +8007,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +8018,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +8029,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +8040,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +8051,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +8062,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +8073,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +8084,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +8095,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +8106,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +8117,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +8128,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +8139,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +8150,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +8161,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +8172,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +8183,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +8194,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +8205,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +8216,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +8227,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +8238,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +8249,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8260,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8271,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8282,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8293,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8304,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8315,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8326,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8337,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8348,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8359,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8370,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8381,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8392,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8403,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8414,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8425,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8436,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8447,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8458,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8469,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8480,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8491,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8502,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8513,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8524,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8535,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8546,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8557,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8568,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8579,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8590,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8601,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8612,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8623,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8634,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8645,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8656,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8667,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8678,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8689,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8700,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8711,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8722,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8733,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8744,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8755,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8766,7 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8777,7 @@
     </x:row>
     <x:row r="407" spans="1:3">
       <x:c r="A407" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8788,7 @@
     </x:row>
     <x:row r="408" spans="1:3">
       <x:c r="A408" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B408" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8799,7 @@
     </x:row>
     <x:row r="409" spans="1:3">
       <x:c r="A409" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B409" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8810,7 @@
     </x:row>
     <x:row r="410" spans="1:3">
       <x:c r="A410" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B410" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8821,7 @@
     </x:row>
     <x:row r="411" spans="1:3">
       <x:c r="A411" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B411" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8832,7 @@
     </x:row>
     <x:row r="412" spans="1:3">
       <x:c r="A412" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B412" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8843,7 @@
     </x:row>
     <x:row r="413" spans="1:3">
       <x:c r="A413" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B413" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +8854,7 @@
     </x:row>
     <x:row r="414" spans="1:3">
       <x:c r="A414" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B414" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +8865,7 @@
     </x:row>
     <x:row r="415" spans="1:3">
       <x:c r="A415" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B415" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +8876,7 @@
     </x:row>
     <x:row r="416" spans="1:3">
       <x:c r="A416" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B416" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +8887,7 @@
     </x:row>
     <x:row r="417" spans="1:3">
       <x:c r="A417" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B417" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +8898,7 @@
     </x:row>
     <x:row r="418" spans="1:3">
       <x:c r="A418" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B418" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +8909,7 @@
     </x:row>
     <x:row r="419" spans="1:3">
       <x:c r="A419" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B419" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +8920,7 @@
     </x:row>
     <x:row r="420" spans="1:3">
       <x:c r="A420" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B420" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +8931,7 @@
     </x:row>
     <x:row r="421" spans="1:3">
       <x:c r="A421" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B421" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +8942,7 @@
     </x:row>
     <x:row r="422" spans="1:3">
       <x:c r="A422" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B422" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,78 +8953,12 @@
     </x:row>
     <x:row r="423" spans="1:3">
       <x:c r="A423" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B423" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C423" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="424" spans="1:3">
-      <x:c r="A424" s="0" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="B424" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C424" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="425" spans="1:3">
-      <x:c r="A425" s="0" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="B425" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C425" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="426" spans="1:3">
-      <x:c r="A426" s="0" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="B426" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C426" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="427" spans="1:3">
-      <x:c r="A427" s="0" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="B427" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C427" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="428" spans="1:3">
-      <x:c r="A428" s="0" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="B428" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C428" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="429" spans="1:3">
-      <x:c r="A429" s="0" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B429" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C429" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -53,6 +53,9 @@
     <x:t>AKBNK</x:t>
   </x:si>
   <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
@@ -104,1584 +107,1587 @@
     <x:t>ARTMS</x:t>
   </x:si>
   <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASUZU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ARZUM</x:t>
   </x:si>
   <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASUZU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIMSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
   </x:si>
   <x:si>
     <x:t>FZLGY</x:t>
   </x:si>
   <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
   </x:si>
   <x:si>
     <x:t>HEDEF</x:t>
   </x:si>
   <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
   </x:si>
   <x:si>
     <x:t>TAVHL</x:t>
   </x:si>
   <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SERNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
     <x:t>TBORG</x:t>
   </x:si>
   <x:si>
@@ -1724,9 +1730,6 @@
     <x:t>TRILC</x:t>
   </x:si>
   <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
     <x:t>TSGYO</x:t>
   </x:si>
   <x:si>
@@ -1812,9 +1815,6 @@
   </x:si>
   <x:si>
     <x:t>YAPRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATAS</x:t>
   </x:si>
   <x:si>
     <x:t>YAYLA</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C189"/>
+  <x:dimension ref="A1:C196"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4289,6 +4289,83 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C189" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:3">
+      <x:c r="A190" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:3">
+      <x:c r="A191" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C191" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:3">
+      <x:c r="A192" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:3">
+      <x:c r="A193" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C193" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:3">
+      <x:c r="A194" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:3">
+      <x:c r="A195" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:3">
+      <x:c r="A196" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C196" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4306,7 +4383,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C423"/>
+  <x:dimension ref="A1:C416"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4322,7 +4399,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4333,7 +4410,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4344,7 +4421,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4355,7 +4432,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4366,7 +4443,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4377,7 +4454,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4388,7 +4465,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4399,7 +4476,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4410,7 +4487,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4421,7 +4498,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4432,7 +4509,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4443,7 +4520,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4454,7 +4531,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4465,7 +4542,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4476,7 +4553,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +4564,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4575,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4586,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4597,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4608,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4619,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4630,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4641,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4652,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4663,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4674,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4685,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4696,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4707,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4718,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4729,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4740,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4751,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4762,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4773,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4784,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4795,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4806,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4817,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4828,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4839,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4850,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4861,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4872,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4883,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4894,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4905,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4916,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4927,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4938,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4949,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4960,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4971,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4982,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4993,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +5004,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +5015,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +5026,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +5037,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +5048,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +5059,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +5070,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +5081,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +5092,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +5103,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +5114,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +5125,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +5136,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +5147,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +5158,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +5169,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +5180,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +5191,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +5202,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +5213,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +5224,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +5235,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +5246,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +5257,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5268,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5279,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5290,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5301,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5312,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5323,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5334,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5345,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5356,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5367,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5378,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5389,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5400,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5411,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5422,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5433,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5444,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5455,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5466,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5477,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5488,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5499,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5510,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5521,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5532,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5543,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5554,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5565,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5576,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5587,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5598,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5609,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5620,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5631,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5642,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5653,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5664,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5675,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5686,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5697,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5708,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5719,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5730,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5741,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5752,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5763,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5774,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5785,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5796,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5807,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5818,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5829,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5840,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5851,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5862,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5873,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5884,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5895,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5906,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +5917,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +5928,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +5939,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +5950,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +5961,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +5972,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +5983,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +5994,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +6005,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +6016,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +6027,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +6038,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +6049,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +6060,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +6071,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +6082,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +6093,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +6104,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +6115,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +6126,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +6137,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +6148,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +6159,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +6170,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +6181,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +6192,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +6203,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +6214,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +6225,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +6236,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +6247,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +6258,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6269,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6280,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6291,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6302,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6313,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6324,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6335,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6346,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6357,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6368,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6379,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6390,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6401,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6412,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6423,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6434,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6445,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6456,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6467,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6478,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6489,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6500,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6511,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6522,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6533,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6544,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6555,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6566,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6577,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6588,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6599,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6610,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6621,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6632,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6643,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6654,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6665,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6676,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6687,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6698,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6709,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6720,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6731,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6742,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6753,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6764,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6775,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6786,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6797,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6808,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6819,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6830,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6841,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6852,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6863,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6874,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6885,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6896,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6907,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +6918,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +6929,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +6940,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +6951,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +6962,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +6973,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +6984,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +6995,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +7006,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +7017,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +7028,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +7039,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +7050,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +7061,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +7072,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +7083,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +7094,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +7105,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +7116,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +7127,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +7138,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +7149,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +7160,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +7171,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +7182,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +7193,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +7204,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +7215,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +7226,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +7237,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +7248,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +7259,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7270,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7281,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7292,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7303,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7314,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7325,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7336,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7347,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7358,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7369,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7380,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7391,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7402,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7413,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7424,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7435,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7446,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7457,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7468,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7479,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7490,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7501,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7512,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7523,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7534,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7545,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7556,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7567,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7578,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7589,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7600,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7611,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7622,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7633,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7644,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7655,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7666,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7677,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7688,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7699,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7710,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7721,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7732,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7743,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7754,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7765,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7776,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7787,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7798,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7809,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7820,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7831,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7842,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7853,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7864,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7875,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7886,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7897,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7908,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +7919,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +7930,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +7941,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +7952,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +7963,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +7974,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +7985,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +7996,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +8007,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +8018,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +8029,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +8040,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +8051,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +8062,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +8073,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +8084,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +8095,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +8106,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +8117,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +8128,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +8139,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +8150,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +8161,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +8172,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +8183,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +8194,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +8205,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +8216,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +8227,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +8238,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +8249,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +8260,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8271,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8282,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8293,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8304,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8315,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8326,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8337,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8348,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8359,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8370,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8381,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8392,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8403,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8414,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8425,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8436,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8447,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8458,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8469,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8480,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8491,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8502,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8513,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8524,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8535,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8546,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8557,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8568,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8579,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8590,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8601,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8612,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8623,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8634,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8645,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8656,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8667,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8678,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8689,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8700,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8711,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8722,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8733,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8744,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8755,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8766,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8777,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8788,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8799,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8810,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8821,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8832,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8843,7 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8854,7 @@
     </x:row>
     <x:row r="407" spans="1:3">
       <x:c r="A407" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +8865,7 @@
     </x:row>
     <x:row r="408" spans="1:3">
       <x:c r="A408" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B408" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +8876,7 @@
     </x:row>
     <x:row r="409" spans="1:3">
       <x:c r="A409" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B409" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +8887,7 @@
     </x:row>
     <x:row r="410" spans="1:3">
       <x:c r="A410" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B410" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +8898,7 @@
     </x:row>
     <x:row r="411" spans="1:3">
       <x:c r="A411" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B411" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +8909,7 @@
     </x:row>
     <x:row r="412" spans="1:3">
       <x:c r="A412" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B412" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +8920,7 @@
     </x:row>
     <x:row r="413" spans="1:3">
       <x:c r="A413" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B413" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +8931,7 @@
     </x:row>
     <x:row r="414" spans="1:3">
       <x:c r="A414" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B414" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +8942,7 @@
     </x:row>
     <x:row r="415" spans="1:3">
       <x:c r="A415" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B415" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,89 +8953,12 @@
     </x:row>
     <x:row r="416" spans="1:3">
       <x:c r="A416" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B416" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C416" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="417" spans="1:3">
-      <x:c r="A417" s="0" t="s">
-        <x:v>608</x:v>
-      </x:c>
-      <x:c r="B417" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C417" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="418" spans="1:3">
-      <x:c r="A418" s="0" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="B418" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C418" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="419" spans="1:3">
-      <x:c r="A419" s="0" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="B419" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C419" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="420" spans="1:3">
-      <x:c r="A420" s="0" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="B420" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C420" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="421" spans="1:3">
-      <x:c r="A421" s="0" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="B421" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C421" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="422" spans="1:3">
-      <x:c r="A422" s="0" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="B422" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C422" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="423" spans="1:3">
-      <x:c r="A423" s="0" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B423" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C423" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -59,1734 +59,1737 @@
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASUZU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKMGY</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASUZU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
   </x:si>
   <x:si>
     <x:t>AYEN</x:t>
   </x:si>
   <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
   </x:si>
   <x:si>
     <x:t>BYDNR</x:t>
   </x:si>
   <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIMSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
   </x:si>
   <x:si>
     <x:t>MOGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TBORG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
   </x:si>
   <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSPOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTRAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
   </x:si>
   <x:si>
     <x:t>TUPRS</x:t>
   </x:si>
   <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
+    <x:t>TUREX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UCAYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UMPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFN</x:t>
   </x:si>
   <x:si>
     <x:t>VAKKO</x:t>
   </x:si>
   <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SERNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAVHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TBORG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSPOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTRAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUREX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURGG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UCAYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UMPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFN</x:t>
-  </x:si>
-  <x:si>
     <x:t>VBTYZ</x:t>
   </x:si>
   <x:si>
@@ -1836,9 +1839,6 @@
   </x:si>
   <x:si>
     <x:t>YONGA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
   </x:si>
   <x:si>
     <x:t>YYAPI</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C196"/>
+  <x:dimension ref="A1:C202"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4366,6 +4366,72 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C196" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:3">
+      <x:c r="A197" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C197" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:3">
+      <x:c r="A198" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C198" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:3">
+      <x:c r="A199" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C199" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:3">
+      <x:c r="A200" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C200" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:3">
+      <x:c r="A201" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C201" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:3">
+      <x:c r="A202" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B202" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C202" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4383,7 +4449,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C416"/>
+  <x:dimension ref="A1:C410"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4399,7 +4465,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4410,7 +4476,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4421,7 +4487,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4432,7 +4498,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4443,7 +4509,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4454,7 +4520,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4465,7 +4531,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4476,7 +4542,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +4553,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4564,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4575,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4586,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4597,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4608,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4619,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4630,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4641,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4652,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4663,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4674,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4685,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4696,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4707,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4718,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4729,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4740,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4751,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4762,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4773,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4784,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4795,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4806,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4817,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4828,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4839,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4850,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4861,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4872,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4883,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4894,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4905,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4916,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4927,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4938,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4949,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4960,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4971,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4982,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +4993,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +5004,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +5015,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +5026,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +5037,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +5048,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +5059,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +5070,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +5081,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +5092,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +5103,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +5114,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +5125,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +5136,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +5147,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +5158,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +5169,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +5180,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +5191,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +5202,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +5213,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +5224,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +5235,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +5246,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5257,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5268,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5279,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5290,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5301,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5312,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5323,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5334,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5345,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5356,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5367,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5378,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5389,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5400,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5411,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5422,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5433,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5444,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5455,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5466,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5477,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5488,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5499,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5510,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5521,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5532,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5543,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5554,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5565,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5576,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5587,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5598,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5609,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5620,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5631,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5642,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5653,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5664,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5675,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5686,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5697,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5708,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5719,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5730,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5741,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5752,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5763,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5774,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5785,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5796,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5807,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5818,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5829,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5840,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5851,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5862,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5873,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5884,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5895,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +5906,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +5917,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +5928,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +5939,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +5950,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +5961,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +5972,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +5983,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +5994,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +6005,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +6016,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +6027,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +6038,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +6049,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +6060,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +6071,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +6082,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +6093,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +6104,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +6115,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +6126,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +6137,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +6148,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +6159,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +6170,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +6181,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +6192,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +6203,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +6214,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +6225,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +6236,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +6247,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6258,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6269,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6280,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6291,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6302,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6313,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6324,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6335,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6346,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6357,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6368,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6379,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6390,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6401,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6412,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6423,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6434,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6445,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6456,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6467,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6478,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6489,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6500,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6511,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6522,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6533,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6544,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6555,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6566,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6577,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6588,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6599,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6610,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6621,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6632,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6643,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6654,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6665,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6676,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6687,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6698,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6709,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6720,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6731,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6742,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6753,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6764,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6775,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6786,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6797,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6808,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6819,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6830,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6841,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6852,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6863,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6874,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6885,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6896,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +6907,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +6918,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +6929,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +6940,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +6951,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +6962,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +6973,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +6984,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +6995,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +7006,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +7017,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +7028,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +7039,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +7050,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +7061,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +7072,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +7083,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +7094,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +7105,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +7116,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +7127,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +7138,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +7149,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +7160,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +7171,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +7182,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +7193,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +7204,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +7215,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +7226,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +7237,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +7248,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7259,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7270,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7281,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7292,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7303,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7314,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7325,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7336,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7347,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7358,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7369,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7380,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7391,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7402,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7413,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7424,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7435,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7446,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7457,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7468,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7479,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7490,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7501,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7512,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7523,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7534,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7545,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7556,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7567,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7578,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7589,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7600,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7611,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7622,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7633,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7644,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7655,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7666,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7677,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7688,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7699,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7710,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7721,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7732,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7743,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7754,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7765,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7776,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7787,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7798,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7809,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7820,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7831,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7842,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7853,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7864,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7875,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7886,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7897,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +7908,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +7919,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +7930,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +7941,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +7952,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +7963,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +7974,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +7985,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +7996,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +8007,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +8018,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +8029,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +8040,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +8051,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +8062,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +8073,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +8084,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +8095,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +8106,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +8117,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +8128,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +8139,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +8150,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +8161,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +8172,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +8183,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +8194,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +8205,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +8216,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +8227,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +8238,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +8249,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8260,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8271,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8282,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8293,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8304,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8315,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8326,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8337,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8348,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8359,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8370,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8381,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8392,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8403,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8414,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8425,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8436,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8447,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8458,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8469,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8480,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8491,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8502,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8513,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8524,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8535,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8546,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8557,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8568,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8579,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8590,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8601,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8612,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8623,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8634,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8645,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8656,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8667,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8678,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8689,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8700,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8711,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8722,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8733,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8744,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8755,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8766,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8777,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8788,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8799,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8810,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8821,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8832,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8843,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +8854,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +8865,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +8876,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +8887,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +8898,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +8909,7 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +8920,7 @@
     </x:row>
     <x:row r="407" spans="1:3">
       <x:c r="A407" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +8931,7 @@
     </x:row>
     <x:row r="408" spans="1:3">
       <x:c r="A408" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B408" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +8942,7 @@
     </x:row>
     <x:row r="409" spans="1:3">
       <x:c r="A409" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B409" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,78 +8953,12 @@
     </x:row>
     <x:row r="410" spans="1:3">
       <x:c r="A410" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B410" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C410" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="411" spans="1:3">
-      <x:c r="A411" s="0" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="B411" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C411" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="412" spans="1:3">
-      <x:c r="A412" s="0" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="B412" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C412" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="413" spans="1:3">
-      <x:c r="A413" s="0" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="B413" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C413" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="414" spans="1:3">
-      <x:c r="A414" s="0" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="B414" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C414" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="415" spans="1:3">
-      <x:c r="A415" s="0" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="B415" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C415" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="416" spans="1:3">
-      <x:c r="A416" s="0" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B416" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C416" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -62,136 +62,859 @@
     <x:t>AKSA</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASUZU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYLGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSEN</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
   </x:si>
   <x:si>
     <x:t>ALGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>ALKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASUZU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
   </x:si>
   <x:si>
     <x:t>AVTUR</x:t>
   </x:si>
   <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIMSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
   </x:si>
   <x:si>
     <x:t>CVKMD</x:t>
@@ -200,1398 +923,696 @@
     <x:t>CWENE</x:t>
   </x:si>
   <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
   </x:si>
   <x:si>
     <x:t>EGEGY</x:t>
   </x:si>
   <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
   </x:si>
   <x:si>
     <x:t>EUPWR</x:t>
   </x:si>
   <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
   </x:si>
   <x:si>
     <x:t>IHAAS</x:t>
   </x:si>
   <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
   </x:si>
   <x:si>
     <x:t>MANAS</x:t>
   </x:si>
   <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
   </x:si>
   <x:si>
     <x:t>NTGAZ</x:t>
   </x:si>
   <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
   </x:si>
   <x:si>
     <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
     <x:t>SAFKR</x:t>
   </x:si>
   <x:si>
@@ -1700,9 +1721,6 @@
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
     <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
@@ -1721,9 +1739,6 @@
     <x:t>TRALT</x:t>
   </x:si>
   <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRENJ</x:t>
   </x:si>
   <x:si>
@@ -1748,15 +1763,9 @@
     <x:t>TUKAS</x:t>
   </x:si>
   <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TUREX</x:t>
   </x:si>
   <x:si>
-    <x:t>TURGG</x:t>
-  </x:si>
-  <x:si>
     <x:t>UCAYM</x:t>
   </x:si>
   <x:si>
@@ -1805,9 +1814,6 @@
     <x:t>VKFYO</x:t>
   </x:si>
   <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
     <x:t>VKING</x:t>
   </x:si>
   <x:si>
@@ -1832,9 +1838,6 @@
     <x:t>YIGIT</x:t>
   </x:si>
   <x:si>
-    <x:t>YKBNK</x:t>
-  </x:si>
-  <x:si>
     <x:t>YKSLN</x:t>
   </x:si>
   <x:si>
@@ -1842,9 +1845,6 @@
   </x:si>
   <x:si>
     <x:t>YYAPI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YYLGD</x:t>
   </x:si>
   <x:si>
     <x:t>ZEDUR</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C202"/>
+  <x:dimension ref="A1:C204"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4432,6 +4432,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C202" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:3">
+      <x:c r="A203" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B203" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C203" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:3">
+      <x:c r="A204" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B204" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C204" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4449,7 +4471,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C410"/>
+  <x:dimension ref="A1:C408"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4465,7 +4487,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4476,7 +4498,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +4509,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4520,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4531,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4542,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4553,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4564,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4575,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4586,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4597,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4608,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4619,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4630,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4641,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4652,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4663,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4674,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4685,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4696,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4707,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4718,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4729,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4740,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4751,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4762,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4773,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4784,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4795,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4806,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4817,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4828,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4839,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4850,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4861,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4872,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4883,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4894,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4905,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4916,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4927,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4938,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +4949,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +4960,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +4971,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +4982,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +4993,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +5004,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +5015,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +5026,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +5037,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +5048,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +5059,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +5070,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +5081,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +5092,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +5103,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +5114,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +5125,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +5136,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +5147,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +5158,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +5169,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +5180,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +5191,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +5202,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5213,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5224,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5235,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5246,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5257,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5268,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5279,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5290,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5301,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5312,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5323,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5334,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5345,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5356,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5367,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5378,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5389,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5400,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5411,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5422,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5433,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5444,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5455,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5466,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5477,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5488,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5499,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5510,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5521,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5532,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5543,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5554,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5565,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5576,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5587,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5598,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5609,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5620,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5631,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5642,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5653,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5664,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5675,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5686,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5697,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5708,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5719,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5730,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5741,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5752,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5763,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5774,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5785,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5796,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5807,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5818,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5829,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5840,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5851,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +5862,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +5873,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +5884,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +5895,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +5906,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +5917,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +5928,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +5939,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +5950,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +5961,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +5972,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +5983,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +5994,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +6005,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +6016,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +6027,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +6038,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +6049,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +6060,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +6071,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +6082,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +6093,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +6104,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +6115,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +6126,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +6137,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +6148,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +6159,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +6170,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +6181,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +6192,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +6203,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6214,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6225,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6236,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6247,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6258,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6269,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6280,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6291,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6302,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6313,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6324,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6335,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6346,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6357,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6368,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6379,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6390,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6401,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6412,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6423,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6434,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6445,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6456,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6467,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6478,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6489,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6500,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6511,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6522,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6533,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6544,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6555,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6566,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6577,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6588,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6599,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6610,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6621,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6632,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6643,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6654,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6665,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6676,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6687,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6698,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6709,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6720,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6731,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6742,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6753,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6764,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6775,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6786,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6797,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6808,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6819,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6830,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6841,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6852,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +6863,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +6874,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +6885,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +6896,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +6907,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +6918,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +6929,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +6940,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +6951,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +6962,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +6973,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +6984,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +6995,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +7006,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +7017,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +7028,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +7039,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +7050,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +7061,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +7072,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +7083,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +7094,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +7105,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +7116,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +7127,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +7138,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +7149,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +7160,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +7171,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +7182,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +7193,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +7204,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7215,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7226,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7237,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7248,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7259,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7270,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7281,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7292,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7303,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7314,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7325,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7336,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7347,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7358,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7369,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7380,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7391,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7402,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7413,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7424,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7435,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7446,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7457,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7468,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7479,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7490,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7501,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7512,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7523,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7534,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7545,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7556,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7567,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7578,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7589,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7600,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7611,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7622,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7633,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7644,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7655,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7666,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7677,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7688,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7699,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7710,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7721,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7732,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7743,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7754,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7765,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7776,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7787,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7798,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7809,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7820,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7831,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7842,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7853,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +7864,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +7875,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +7886,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +7897,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +7908,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +7919,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +7930,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +7941,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +7952,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +7963,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +7974,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +7985,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +7996,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +8007,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +8018,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +8029,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +8040,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +8051,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +8062,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +8073,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +8084,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +8095,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +8106,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +8117,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +8128,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +8139,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +8150,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +8161,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +8172,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +8183,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +8194,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +8205,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8216,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8227,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8238,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8249,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8260,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8271,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8282,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8293,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8304,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8315,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8326,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8337,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8348,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8359,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8370,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8381,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8392,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8403,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8414,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8425,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8436,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8447,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8458,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8469,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8480,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8491,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8502,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8513,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8524,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8535,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8546,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8557,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8568,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8579,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8590,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8601,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8612,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8623,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8634,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8645,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8656,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8667,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8678,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8689,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8700,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8711,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8722,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8733,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8744,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8755,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8766,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8777,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8788,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8799,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +8810,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +8821,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +8832,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +8843,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +8854,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +8865,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +8876,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +8887,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +8898,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,7 +8909,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8898,7 +8920,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8909,7 +8931,7 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
@@ -8920,7 +8942,7 @@
     </x:row>
     <x:row r="407" spans="1:3">
       <x:c r="A407" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>4</x:v>
@@ -8931,34 +8953,12 @@
     </x:row>
     <x:row r="408" spans="1:3">
       <x:c r="A408" s="0" t="s">
-        <x:v>612</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B408" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C408" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="409" spans="1:3">
-      <x:c r="A409" s="0" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="B409" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C409" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="410" spans="1:3">
-      <x:c r="A410" s="0" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B410" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C410" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -59,9 +59,15 @@
     <x:t>AKFIS</x:t>
   </x:si>
   <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSA</x:t>
   </x:si>
   <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
     <x:t>AKSGY</x:t>
   </x:si>
   <x:si>
@@ -80,1629 +86,1626 @@
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASUZU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYLGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALVES</x:t>
   </x:si>
   <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASUZU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
   </x:si>
   <x:si>
     <x:t>BTCIM</x:t>
   </x:si>
   <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIMSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
   </x:si>
   <x:si>
     <x:t>CONSE</x:t>
   </x:si>
   <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
+    <x:t>COSMO</x:t>
   </x:si>
   <x:si>
     <x:t>CUSAN</x:t>
   </x:si>
   <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
   </x:si>
   <x:si>
     <x:t>GLRMK</x:t>
   </x:si>
   <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
   </x:si>
   <x:si>
     <x:t>IZINV</x:t>
   </x:si>
   <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
   </x:si>
   <x:si>
     <x:t>OYAKC</x:t>
   </x:si>
   <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
   </x:si>
   <x:si>
     <x:t>TATGD</x:t>
   </x:si>
   <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURGG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YYLGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SERNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
     <x:t>TAVHL</x:t>
   </x:si>
   <x:si>
@@ -1773,9 +1776,6 @@
   </x:si>
   <x:si>
     <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULKER</x:t>
   </x:si>
   <x:si>
     <x:t>UMPAS</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C204"/>
+  <x:dimension ref="A1:C203"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4443,17 +4443,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C203" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" spans="1:3">
-      <x:c r="A204" s="0" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="B204" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C204" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4471,7 +4460,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C408"/>
+  <x:dimension ref="A1:C409"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4487,7 +4476,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4487,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4498,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4509,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4520,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4531,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4542,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4553,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4564,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4575,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4586,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4597,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4608,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4619,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4630,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4641,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4652,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4663,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4674,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4685,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4696,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4707,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4718,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4729,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4740,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4751,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4762,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4773,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4784,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4795,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4806,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4817,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4828,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4839,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4850,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4861,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4872,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4883,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4894,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4905,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +4916,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +4927,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +4938,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +4949,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +4960,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +4971,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +4982,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +4993,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +5004,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +5015,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +5026,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +5037,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +5048,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +5059,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +5070,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +5081,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +5092,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +5103,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +5114,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +5125,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +5136,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +5147,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +5158,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +5169,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5180,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5191,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5202,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5213,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5224,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5235,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5246,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5257,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5268,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5279,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5290,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5301,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5312,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5323,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5334,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5345,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5356,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5367,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5378,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5389,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5400,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5411,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5422,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5433,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5444,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5455,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5466,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5477,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5488,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5499,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5510,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5521,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5532,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5543,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5554,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5565,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5576,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5587,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5598,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5609,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5620,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5631,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5642,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5653,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5664,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5675,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5686,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5697,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5708,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5719,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5730,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5741,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5752,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5763,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5774,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5785,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5796,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5807,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5818,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +5829,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +5840,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +5851,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +5862,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +5873,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +5884,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +5895,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +5906,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +5917,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +5928,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +5939,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +5950,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +5961,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +5972,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +5983,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +5994,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +6005,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +6016,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +6027,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +6038,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +6049,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +6060,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +6071,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +6082,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +6093,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +6104,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +6115,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +6126,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +6137,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +6148,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +6159,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +6170,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6181,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6192,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6203,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6214,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6225,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6236,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6247,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6258,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6269,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6280,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6291,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6302,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6313,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6324,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6335,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6346,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6357,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6368,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6379,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6390,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6401,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6412,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6423,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6434,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6445,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6456,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6467,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6478,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6489,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6500,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6511,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6522,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6533,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6544,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6555,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6566,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6577,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6588,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6599,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6610,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6621,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6632,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6643,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6654,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6665,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6676,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6687,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6698,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6709,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6720,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6731,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6742,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6753,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6764,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6775,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6786,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6797,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6808,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6819,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +6830,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +6841,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +6852,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +6863,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +6874,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +6885,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +6896,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +6907,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +6918,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +6929,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +6940,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +6951,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +6962,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +6973,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +6984,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +6995,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +7006,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +7017,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +7028,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +7039,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +7050,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +7061,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +7072,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +7083,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +7094,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +7105,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +7116,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +7127,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +7138,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +7149,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +7160,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +7171,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7182,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7193,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7204,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7215,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7226,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7237,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7248,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7259,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7270,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7281,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7292,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7303,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7314,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7325,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7336,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7347,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7358,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7369,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7380,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7391,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7402,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7413,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7424,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7435,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7446,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7457,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7468,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7479,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7490,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7501,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7512,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7523,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7534,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7545,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7556,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7567,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7578,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7589,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7600,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7611,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7622,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7633,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7644,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7655,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7666,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7677,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7688,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7699,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7710,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7721,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7732,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7743,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7754,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7765,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7776,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7787,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7798,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7809,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7820,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +7831,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +7842,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +7853,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +7864,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +7875,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +7886,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +7897,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +7908,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +7919,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +7930,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +7941,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +7952,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +7963,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +7974,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +7985,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +7996,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +8007,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +8018,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +8029,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +8040,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +8051,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +8062,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +8073,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +8084,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +8095,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +8106,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +8117,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +8128,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +8139,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +8150,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +8161,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +8172,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8183,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8194,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8205,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8216,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8227,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8238,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8249,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8260,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8271,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8282,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8293,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8304,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8315,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8326,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8337,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8348,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8359,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8370,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8381,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8392,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8403,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8414,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8425,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8436,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8447,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8458,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8469,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8480,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8491,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8502,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8513,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8524,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8535,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8546,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8557,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8568,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8579,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8590,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8601,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8612,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8623,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8634,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8645,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8656,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8667,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8678,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8689,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8700,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8711,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8722,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8733,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8744,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8755,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8766,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +8777,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +8788,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +8799,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +8810,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +8821,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +8832,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +8843,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +8854,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +8865,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,7 +8876,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8898,7 +8887,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8909,7 +8898,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8920,7 +8909,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8931,7 +8920,7 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>612</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
@@ -8942,7 +8931,7 @@
     </x:row>
     <x:row r="407" spans="1:3">
       <x:c r="A407" s="0" t="s">
-        <x:v>613</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>4</x:v>
@@ -8953,12 +8942,23 @@
     </x:row>
     <x:row r="408" spans="1:3">
       <x:c r="A408" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B408" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C408" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" spans="1:3">
+      <x:c r="A409" s="0" t="s">
         <x:v>614</x:v>
       </x:c>
-      <x:c r="B408" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C408" s="0" t="s">
+      <x:c r="B409" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C409" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -161,12 +161,18 @@
     <x:t>BULGS</x:t>
   </x:si>
   <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
     <x:t>BURVA</x:t>
   </x:si>
   <x:si>
     <x:t>BVSAN</x:t>
   </x:si>
   <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
     <x:t>CCOLA</x:t>
   </x:si>
   <x:si>
@@ -185,1567 +191,1561 @@
     <x:t>CRDFA</x:t>
   </x:si>
   <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYLGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
     <x:t>CRFSA</x:t>
   </x:si>
   <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>FADE</x:t>
   </x:si>
   <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
   </x:si>
   <x:si>
     <x:t>LIDFA</x:t>
   </x:si>
   <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
   </x:si>
   <x:si>
     <x:t>MAALT</x:t>
   </x:si>
   <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
   </x:si>
   <x:si>
     <x:t>PINSU</x:t>
   </x:si>
   <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
   </x:si>
   <x:si>
     <x:t>POLHO</x:t>
   </x:si>
   <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TBORG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
   </x:si>
   <x:si>
     <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURGG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YYLGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SERNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAVHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TBORG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
   </x:si>
   <x:si>
     <x:t>TSGYO</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C203"/>
+  <x:dimension ref="A1:C206"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4443,6 +4443,39 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C203" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:3">
+      <x:c r="A204" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B204" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C204" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:3">
+      <x:c r="A205" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B205" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C205" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:3">
+      <x:c r="A206" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B206" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C206" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4460,7 +4493,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C409"/>
+  <x:dimension ref="A1:C406"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4476,7 +4509,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +4520,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4531,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4542,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4553,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4564,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4575,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4586,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4597,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4608,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4619,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4630,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4641,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4652,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4663,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4674,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4685,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4696,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4707,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4718,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4729,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4740,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4751,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4762,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4773,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4784,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4795,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4806,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4817,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4828,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4839,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4850,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4861,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4872,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4883,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4894,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4905,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4916,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4927,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4938,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4949,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +4960,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +4971,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +4982,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +4993,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +5004,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +5015,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +5026,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +5037,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +5048,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +5059,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +5070,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +5081,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +5092,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +5103,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +5114,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +5125,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +5136,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +5147,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +5158,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +5169,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +5180,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +5191,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +5202,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +5213,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5224,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5235,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5246,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5257,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5268,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5279,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5290,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5301,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5312,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5323,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5334,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5345,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5356,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5367,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5378,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5389,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5400,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5411,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5422,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5433,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5444,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5455,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5466,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5477,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5488,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5499,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5510,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5521,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5532,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5543,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5554,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5565,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5576,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5587,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5598,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5609,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5620,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5631,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5642,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5653,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5664,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5675,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5686,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5697,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5708,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5719,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5730,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5741,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5752,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5763,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5774,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5785,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5796,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5807,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5818,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5829,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5840,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5851,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5862,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +5873,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +5884,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +5895,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +5906,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +5917,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +5928,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +5939,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +5950,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +5961,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +5972,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +5983,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +5994,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +6005,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +6016,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +6027,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +6038,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +6049,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +6060,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +6071,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +6082,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +6093,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +6104,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +6115,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +6126,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +6137,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +6148,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +6159,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +6170,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +6181,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +6192,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +6203,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +6214,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6225,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6236,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6247,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6258,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6269,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6280,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6291,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6302,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6313,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6324,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6335,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6346,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6357,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6368,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6379,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6390,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6401,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6412,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6423,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6434,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6445,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6456,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6467,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6478,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6489,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6500,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6511,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6522,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6533,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6544,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6555,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6566,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6577,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6588,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6599,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6610,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6621,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6632,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6643,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6654,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6665,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6676,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6687,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6698,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6709,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6720,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6731,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6742,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6753,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6764,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6775,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6786,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6797,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6808,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6819,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6830,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6841,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6852,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6863,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +6874,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +6885,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +6896,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +6907,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +6918,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +6929,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +6940,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +6951,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +6962,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +6973,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +6984,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +6995,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +7006,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +7017,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +7028,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +7039,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +7050,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +7061,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +7072,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +7083,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +7094,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +7105,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +7116,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +7127,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +7138,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +7149,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +7160,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +7171,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +7182,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +7193,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +7204,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +7215,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7226,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7237,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7248,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7259,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7270,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7281,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7292,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7303,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7314,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7325,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7336,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7347,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7358,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7369,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7380,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7391,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7402,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7413,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7424,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7435,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7446,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7457,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7468,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7479,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7490,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7501,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7512,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7523,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7534,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7545,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7556,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7567,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7578,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7589,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7600,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7611,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7622,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7633,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7644,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7655,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7666,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7677,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7688,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7699,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7710,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7721,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7732,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7743,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7754,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7765,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7776,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7787,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7798,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7809,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7820,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7831,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7842,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7853,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7864,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +7875,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +7886,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +7897,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +7908,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +7919,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +7930,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +7941,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +7952,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +7963,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +7974,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +7985,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +7996,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +8007,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +8018,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +8029,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +8040,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +8051,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +8062,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +8073,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +8084,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +8095,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +8106,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +8117,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +8128,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +8139,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +8150,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +8161,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +8172,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +8183,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +8194,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +8205,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +8216,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8227,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8238,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8249,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8260,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8271,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8282,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8293,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8304,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8315,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8326,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8337,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8348,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8359,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8370,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8381,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8392,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8403,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8414,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8425,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8436,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8447,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8458,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8469,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8480,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8491,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8502,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8513,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8524,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8535,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8546,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8557,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8568,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8579,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8590,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8601,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8612,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8623,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8634,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8645,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8656,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8667,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8678,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8689,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8700,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8711,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8722,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8733,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8744,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8755,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8766,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8777,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8788,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8799,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8810,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +8821,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +8832,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +8843,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +8854,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +8865,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +8876,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +8887,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +8898,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +8909,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,7 +8920,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8898,7 +8931,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8909,7 +8942,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8920,45 +8953,12 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C406" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="407" spans="1:3">
-      <x:c r="A407" s="0" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="B407" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C407" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="408" spans="1:3">
-      <x:c r="A408" s="0" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="B408" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C408" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="409" spans="1:3">
-      <x:c r="A409" s="0" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="B409" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C409" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -74,1777 +74,1777 @@
     <x:t>AKSUE</x:t>
   </x:si>
   <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASUZU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALBRK</x:t>
   </x:si>
   <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALCTL</x:t>
   </x:si>
   <x:si>
-    <x:t>ALKIM</x:t>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
   </x:si>
   <x:si>
     <x:t>ALKLC</x:t>
   </x:si>
   <x:si>
-    <x:t>ANELE</x:t>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
   </x:si>
   <x:si>
     <x:t>ANHYT</x:t>
   </x:si>
   <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
   </x:si>
   <x:si>
     <x:t>ARTMS</x:t>
   </x:si>
   <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASUZU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
   </x:si>
   <x:si>
     <x:t>AYES</x:t>
   </x:si>
   <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIMSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
   </x:si>
   <x:si>
     <x:t>DIRIT</x:t>
   </x:si>
   <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
   </x:si>
   <x:si>
     <x:t>DURKN</x:t>
   </x:si>
   <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
   </x:si>
   <x:si>
     <x:t>EDATA</x:t>
   </x:si>
   <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTRA</x:t>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
   </x:si>
   <x:si>
     <x:t>ERBOS</x:t>
   </x:si>
   <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
   </x:si>
   <x:si>
     <x:t>EUYO</x:t>
   </x:si>
   <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
   </x:si>
   <x:si>
     <x:t>GLYHO</x:t>
   </x:si>
   <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
   </x:si>
   <x:si>
     <x:t>ISMEN</x:t>
   </x:si>
   <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
   </x:si>
   <x:si>
     <x:t>KAYSE</x:t>
   </x:si>
   <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
   </x:si>
   <x:si>
     <x:t>KRONT</x:t>
   </x:si>
   <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
   </x:si>
   <x:si>
     <x:t>LIDER</x:t>
   </x:si>
   <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
   </x:si>
   <x:si>
     <x:t>MARMR</x:t>
   </x:si>
   <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
   </x:si>
   <x:si>
     <x:t>MGROS</x:t>
   </x:si>
   <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
   </x:si>
   <x:si>
     <x:t>MPARK</x:t>
   </x:si>
   <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TBORG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
   </x:si>
   <x:si>
     <x:t>TMPOL</x:t>
   </x:si>
   <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURGG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULKER</x:t>
+    <x:t>TMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSPOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTRAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUREX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UCAYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
   </x:si>
   <x:si>
     <x:t>ULUFA</x:t>
   </x:si>
   <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
+    <x:t>UMPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
   </x:si>
   <x:si>
     <x:t>VERUS</x:t>
   </x:si>
   <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
+    <x:t>VESBE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKFYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VSNMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAYLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YBTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YESIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YKSLN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YONGA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YYAPI</x:t>
   </x:si>
   <x:si>
     <x:t>YYLGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SERNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAVHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TBORG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSPOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTRAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUREX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UCAYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UMPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VESBE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VESTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKFYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VSNMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAYLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YBTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YESIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YKSLN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YONGA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YYAPI</x:t>
   </x:si>
   <x:si>
     <x:t>ZEDUR</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C206"/>
+  <x:dimension ref="A1:C189"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4289,193 +4289,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C189" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190" spans="1:3">
-      <x:c r="A190" s="0" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="B190" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C190" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191" spans="1:3">
-      <x:c r="A191" s="0" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="B191" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C191" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192" spans="1:3">
-      <x:c r="A192" s="0" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="B192" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C192" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193" spans="1:3">
-      <x:c r="A193" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="B193" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C193" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194" spans="1:3">
-      <x:c r="A194" s="0" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="B194" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C194" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195" spans="1:3">
-      <x:c r="A195" s="0" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="B195" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C195" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196" spans="1:3">
-      <x:c r="A196" s="0" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="B196" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C196" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197" spans="1:3">
-      <x:c r="A197" s="0" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="B197" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C197" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198" spans="1:3">
-      <x:c r="A198" s="0" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="B198" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C198" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199" spans="1:3">
-      <x:c r="A199" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="B199" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C199" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200" spans="1:3">
-      <x:c r="A200" s="0" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="B200" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C200" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201" spans="1:3">
-      <x:c r="A201" s="0" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="B201" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C201" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202" spans="1:3">
-      <x:c r="A202" s="0" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="B202" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C202" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203" spans="1:3">
-      <x:c r="A203" s="0" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="B203" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C203" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" spans="1:3">
-      <x:c r="A204" s="0" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="B204" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C204" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" spans="1:3">
-      <x:c r="A205" s="0" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="B205" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C205" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" spans="1:3">
-      <x:c r="A206" s="0" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="B206" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C206" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4493,7 +4306,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C406"/>
+  <x:dimension ref="A1:C423"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4509,7 +4322,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4333,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4344,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4355,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4366,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4377,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4388,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4399,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4410,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4421,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4432,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4443,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4454,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4465,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4476,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4487,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4498,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4509,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4520,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4531,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4542,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4553,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4564,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4575,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4586,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4597,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4608,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4619,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4630,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4641,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4652,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4663,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4674,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4685,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4696,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4707,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4718,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4729,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +4740,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +4751,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +4762,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +4773,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +4784,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +4795,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +4806,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +4817,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +4828,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +4839,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +4850,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +4861,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +4872,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +4883,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +4894,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +4905,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +4916,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +4927,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +4938,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +4949,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +4960,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +4971,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +4982,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +4993,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5004,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5015,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5026,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5037,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5048,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5059,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5070,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5081,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5092,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5103,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5114,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5125,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5136,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5147,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5158,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5169,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5180,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5191,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5202,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5213,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5224,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5235,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5246,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5257,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5268,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5279,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5290,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5301,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5312,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5323,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5334,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5345,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5356,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5367,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5378,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5389,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5400,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5411,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5422,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5433,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5444,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5455,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5466,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5477,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5488,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5499,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5510,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5521,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5532,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5543,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5554,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5565,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5576,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5587,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5598,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5609,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5620,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5631,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5642,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +5653,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +5664,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +5675,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +5686,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +5697,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +5708,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +5719,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +5730,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +5741,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +5752,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +5763,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +5774,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +5785,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +5796,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +5807,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +5818,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +5829,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +5840,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +5851,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +5862,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +5873,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +5884,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +5895,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +5906,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +5917,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +5928,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +5939,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +5950,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +5961,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +5972,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +5983,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +5994,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6005,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6016,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6027,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6038,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6049,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6060,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6071,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6082,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6093,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6104,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6115,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6126,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6137,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6148,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6159,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6170,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6181,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6192,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6203,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6214,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6225,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6236,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6247,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6258,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6269,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6280,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6291,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6302,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6313,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6324,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6335,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6346,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6357,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6368,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6379,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6390,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6401,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6412,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6423,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6434,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6445,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6456,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6467,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6478,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6489,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6500,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6511,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6522,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6533,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6544,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6555,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6566,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6577,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6588,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6599,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6610,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6621,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6632,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6643,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +6654,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +6665,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +6676,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +6687,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +6698,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +6709,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +6720,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +6731,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +6742,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +6753,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +6764,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +6775,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +6786,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +6797,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +6808,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +6819,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +6830,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +6841,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +6852,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +6863,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +6874,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +6885,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +6896,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +6907,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +6918,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +6929,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +6940,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +6951,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +6962,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +6973,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +6984,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +6995,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7006,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7017,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7028,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7039,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7050,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7061,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7072,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7083,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7094,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7105,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7116,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7127,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7138,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7149,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7160,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7171,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7182,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7193,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7204,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7215,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7226,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7237,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7248,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7259,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7270,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7281,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7292,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7303,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7314,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7325,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7336,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7347,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7358,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7369,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7380,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7391,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7402,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7413,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7424,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7435,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7446,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7457,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7468,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7479,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7490,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7501,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7512,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7523,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7534,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7545,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7556,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7567,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7578,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7589,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7600,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7611,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7622,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7633,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7644,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +7655,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +7666,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +7677,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +7688,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +7699,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +7710,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +7721,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +7732,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +7743,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +7754,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +7765,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +7776,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +7787,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +7798,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +7809,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +7820,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +7831,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +7842,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +7853,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +7864,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +7875,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +7886,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +7897,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +7908,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +7919,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +7930,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +7941,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +7952,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +7963,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +7974,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +7985,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +7996,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8007,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8018,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8029,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8040,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8051,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8062,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8073,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8084,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8095,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8106,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8117,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8128,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8139,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8150,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8161,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8172,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8183,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8194,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8205,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8216,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8227,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8238,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8249,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8260,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8271,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8282,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8293,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8304,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8315,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8326,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8337,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8348,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8359,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8370,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8381,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8392,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8403,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8414,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8425,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8436,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8447,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8458,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8469,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8480,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8491,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8502,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8513,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8524,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8535,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8546,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8557,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8568,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8579,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8590,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +8601,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +8612,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +8623,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +8634,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +8645,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +8656,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +8667,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +8678,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +8689,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,7 +8700,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8898,7 +8711,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8909,7 +8722,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8920,7 +8733,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8931,7 +8744,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>612</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8942,7 +8755,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>613</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8953,12 +8766,199 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B406" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C406" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" spans="1:3">
+      <x:c r="A407" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="B407" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C407" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" spans="1:3">
+      <x:c r="A408" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="B408" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C408" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" spans="1:3">
+      <x:c r="A409" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B409" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C409" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" spans="1:3">
+      <x:c r="A410" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="B410" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C410" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" spans="1:3">
+      <x:c r="A411" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="B411" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C411" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" spans="1:3">
+      <x:c r="A412" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B412" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C412" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" spans="1:3">
+      <x:c r="A413" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B413" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C413" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" spans="1:3">
+      <x:c r="A414" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="B414" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C414" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" spans="1:3">
+      <x:c r="A415" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B415" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C415" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" spans="1:3">
+      <x:c r="A416" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="B416" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C416" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" spans="1:3">
+      <x:c r="A417" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B417" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C417" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" spans="1:3">
+      <x:c r="A418" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B418" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C418" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" spans="1:3">
+      <x:c r="A419" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="B419" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C419" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" spans="1:3">
+      <x:c r="A420" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B420" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C420" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" spans="1:3">
+      <x:c r="A421" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B421" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C421" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" spans="1:3">
+      <x:c r="A422" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B422" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C422" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" spans="1:3">
+      <x:c r="A423" s="0" t="s">
         <x:v>614</x:v>
       </x:c>
-      <x:c r="B406" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C406" s="0" t="s">
+      <x:c r="B423" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C423" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -44,1797 +44,1800 @@
     <x:t>AEFES</x:t>
   </x:si>
   <x:si>
+    <x:t>AGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKCNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSUE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANELE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANSGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARDYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASTOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASUZU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYCES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GATEG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISFIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZYSR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RNPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THYAO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTKOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZEDUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGESA</x:t>
   </x:si>
   <x:si>
-    <x:t>AGYO</x:t>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
   </x:si>
   <x:si>
     <x:t>AKBNK</x:t>
   </x:si>
   <x:si>
-    <x:t>AKCNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFYE</x:t>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
   </x:si>
   <x:si>
     <x:t>AKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>AKSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSUE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANELE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANSGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARDYZ</x:t>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
   </x:si>
   <x:si>
     <x:t>ARMGD</x:t>
   </x:si>
   <x:si>
-    <x:t>ASELS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASUZU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYCES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
   </x:si>
   <x:si>
     <x:t>BIMAS</x:t>
   </x:si>
   <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BSOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIMSA</x:t>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
   </x:si>
   <x:si>
     <x:t>CLEBI</x:t>
   </x:si>
   <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
   </x:si>
   <x:si>
     <x:t>ENTRA</x:t>
   </x:si>
   <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GATEG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
   </x:si>
   <x:si>
     <x:t>ISCTR</x:t>
   </x:si>
   <x:si>
-    <x:t>ISDMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISFIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUYAS</x:t>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
   </x:si>
   <x:si>
     <x:t>LILAK</x:t>
   </x:si>
   <x:si>
-    <x:t>LMKDC</x:t>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
   </x:si>
   <x:si>
     <x:t>LYDHO</x:t>
   </x:si>
   <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
   </x:si>
   <x:si>
     <x:t>MOBTL</x:t>
   </x:si>
   <x:si>
-    <x:t>MOGAN</x:t>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
   </x:si>
   <x:si>
     <x:t>MSGYO</x:t>
   </x:si>
   <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZYSR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RNPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUZYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYSAS</x:t>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAFKR</x:t>
   </x:si>
   <x:si>
     <x:t>SAHOL</x:t>
   </x:si>
   <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>SDTTR</x:t>
   </x:si>
   <x:si>
     <x:t>SEGMN</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
   </x:si>
   <x:si>
     <x:t>SISE</x:t>
   </x:si>
   <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TBORG</x:t>
   </x:si>
   <x:si>
     <x:t>TCELL</x:t>
   </x:si>
   <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THYAO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURGG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
+    <x:t>TDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSPOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTRAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUREX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UCAYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UFUK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UMPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKFN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VBTYZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VERUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESBE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VESTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKFYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VSNMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAYLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YBTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YESIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YIGIT</x:t>
   </x:si>
   <x:si>
     <x:t>YKBNK</x:t>
   </x:si>
   <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SERNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAVHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TBORG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSPOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTRAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUREX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UCAYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UFUK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UMPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKFN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VBTYZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VERUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VESBE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VESTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKFYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VSNMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAYLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YBTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YESIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YIGIT</x:t>
-  </x:si>
-  <x:si>
     <x:t>YKSLN</x:t>
   </x:si>
   <x:si>
@@ -1845,9 +1848,6 @@
   </x:si>
   <x:si>
     <x:t>YYLGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZEDUR</x:t>
   </x:si>
   <x:si>
     <x:t>ZERGY</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C189"/>
+  <x:dimension ref="A1:C178"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4168,127 +4168,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C178" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" spans="1:3">
-      <x:c r="A179" s="0" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="B179" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C179" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180" spans="1:3">
-      <x:c r="A180" s="0" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="B180" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C180" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181" spans="1:3">
-      <x:c r="A181" s="0" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="B181" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C181" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182" spans="1:3">
-      <x:c r="A182" s="0" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="B182" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C182" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="183" spans="1:3">
-      <x:c r="A183" s="0" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="B183" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C183" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184" spans="1:3">
-      <x:c r="A184" s="0" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="B184" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C184" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="185" spans="1:3">
-      <x:c r="A185" s="0" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="B185" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C185" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186" spans="1:3">
-      <x:c r="A186" s="0" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="B186" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C186" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187" spans="1:3">
-      <x:c r="A187" s="0" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="B187" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C187" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188" spans="1:3">
-      <x:c r="A188" s="0" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="B188" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C188" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189" spans="1:3">
-      <x:c r="A189" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="B189" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C189" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4306,7 +4185,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C423"/>
+  <x:dimension ref="A1:C434"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4322,7 +4201,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4333,7 +4212,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4344,7 +4223,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4355,7 +4234,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4366,7 +4245,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4377,7 +4256,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4388,7 +4267,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4399,7 +4278,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4410,7 +4289,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4421,7 +4300,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4432,7 +4311,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4443,7 +4322,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4454,7 +4333,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4465,7 +4344,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4476,7 +4355,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +4366,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4377,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4388,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4399,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4410,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4421,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4432,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4443,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4454,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4465,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4476,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4487,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4498,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4509,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4520,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4531,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4542,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4553,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4564,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4575,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4586,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4597,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4608,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4619,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4630,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4641,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4652,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4663,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4674,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4685,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4696,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4707,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4718,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4729,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4740,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4751,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4762,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4773,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4784,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4795,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +4806,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +4817,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +4828,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +4839,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +4850,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +4861,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +4872,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +4883,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +4894,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +4905,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +4916,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +4927,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +4938,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +4949,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +4960,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -5092,7 +4971,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -5103,7 +4982,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -5114,7 +4993,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5125,7 +5004,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5136,7 +5015,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5147,7 +5026,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5158,7 +5037,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5169,7 +5048,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5180,7 +5059,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5191,7 +5070,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5202,7 +5081,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
         <x:v>4</x:v>
@@ -5213,7 +5092,7 @@
     </x:row>
     <x:row r="83" spans="1:3">
       <x:c r="A83" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
         <x:v>4</x:v>
@@ -5224,7 +5103,7 @@
     </x:row>
     <x:row r="84" spans="1:3">
       <x:c r="A84" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
         <x:v>4</x:v>
@@ -5235,7 +5114,7 @@
     </x:row>
     <x:row r="85" spans="1:3">
       <x:c r="A85" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
         <x:v>4</x:v>
@@ -5246,7 +5125,7 @@
     </x:row>
     <x:row r="86" spans="1:3">
       <x:c r="A86" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
         <x:v>4</x:v>
@@ -5257,7 +5136,7 @@
     </x:row>
     <x:row r="87" spans="1:3">
       <x:c r="A87" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
         <x:v>4</x:v>
@@ -5268,7 +5147,7 @@
     </x:row>
     <x:row r="88" spans="1:3">
       <x:c r="A88" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
         <x:v>4</x:v>
@@ -5279,7 +5158,7 @@
     </x:row>
     <x:row r="89" spans="1:3">
       <x:c r="A89" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
         <x:v>4</x:v>
@@ -5290,7 +5169,7 @@
     </x:row>
     <x:row r="90" spans="1:3">
       <x:c r="A90" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
         <x:v>4</x:v>
@@ -5301,7 +5180,7 @@
     </x:row>
     <x:row r="91" spans="1:3">
       <x:c r="A91" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
         <x:v>4</x:v>
@@ -5312,7 +5191,7 @@
     </x:row>
     <x:row r="92" spans="1:3">
       <x:c r="A92" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
         <x:v>4</x:v>
@@ -5323,7 +5202,7 @@
     </x:row>
     <x:row r="93" spans="1:3">
       <x:c r="A93" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
         <x:v>4</x:v>
@@ -5334,7 +5213,7 @@
     </x:row>
     <x:row r="94" spans="1:3">
       <x:c r="A94" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
         <x:v>4</x:v>
@@ -5345,7 +5224,7 @@
     </x:row>
     <x:row r="95" spans="1:3">
       <x:c r="A95" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
         <x:v>4</x:v>
@@ -5356,7 +5235,7 @@
     </x:row>
     <x:row r="96" spans="1:3">
       <x:c r="A96" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
         <x:v>4</x:v>
@@ -5367,7 +5246,7 @@
     </x:row>
     <x:row r="97" spans="1:3">
       <x:c r="A97" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
         <x:v>4</x:v>
@@ -5378,7 +5257,7 @@
     </x:row>
     <x:row r="98" spans="1:3">
       <x:c r="A98" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
         <x:v>4</x:v>
@@ -5389,7 +5268,7 @@
     </x:row>
     <x:row r="99" spans="1:3">
       <x:c r="A99" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
         <x:v>4</x:v>
@@ -5400,7 +5279,7 @@
     </x:row>
     <x:row r="100" spans="1:3">
       <x:c r="A100" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
         <x:v>4</x:v>
@@ -5411,7 +5290,7 @@
     </x:row>
     <x:row r="101" spans="1:3">
       <x:c r="A101" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
         <x:v>4</x:v>
@@ -5422,7 +5301,7 @@
     </x:row>
     <x:row r="102" spans="1:3">
       <x:c r="A102" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
         <x:v>4</x:v>
@@ -5433,7 +5312,7 @@
     </x:row>
     <x:row r="103" spans="1:3">
       <x:c r="A103" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
         <x:v>4</x:v>
@@ -5444,7 +5323,7 @@
     </x:row>
     <x:row r="104" spans="1:3">
       <x:c r="A104" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
         <x:v>4</x:v>
@@ -5455,7 +5334,7 @@
     </x:row>
     <x:row r="105" spans="1:3">
       <x:c r="A105" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
         <x:v>4</x:v>
@@ -5466,7 +5345,7 @@
     </x:row>
     <x:row r="106" spans="1:3">
       <x:c r="A106" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
         <x:v>4</x:v>
@@ -5477,7 +5356,7 @@
     </x:row>
     <x:row r="107" spans="1:3">
       <x:c r="A107" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
         <x:v>4</x:v>
@@ -5488,7 +5367,7 @@
     </x:row>
     <x:row r="108" spans="1:3">
       <x:c r="A108" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
         <x:v>4</x:v>
@@ -5499,7 +5378,7 @@
     </x:row>
     <x:row r="109" spans="1:3">
       <x:c r="A109" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
         <x:v>4</x:v>
@@ -5510,7 +5389,7 @@
     </x:row>
     <x:row r="110" spans="1:3">
       <x:c r="A110" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
         <x:v>4</x:v>
@@ -5521,7 +5400,7 @@
     </x:row>
     <x:row r="111" spans="1:3">
       <x:c r="A111" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
         <x:v>4</x:v>
@@ -5532,7 +5411,7 @@
     </x:row>
     <x:row r="112" spans="1:3">
       <x:c r="A112" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
         <x:v>4</x:v>
@@ -5543,7 +5422,7 @@
     </x:row>
     <x:row r="113" spans="1:3">
       <x:c r="A113" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
         <x:v>4</x:v>
@@ -5554,7 +5433,7 @@
     </x:row>
     <x:row r="114" spans="1:3">
       <x:c r="A114" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
         <x:v>4</x:v>
@@ -5565,7 +5444,7 @@
     </x:row>
     <x:row r="115" spans="1:3">
       <x:c r="A115" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
         <x:v>4</x:v>
@@ -5576,7 +5455,7 @@
     </x:row>
     <x:row r="116" spans="1:3">
       <x:c r="A116" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
         <x:v>4</x:v>
@@ -5587,7 +5466,7 @@
     </x:row>
     <x:row r="117" spans="1:3">
       <x:c r="A117" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
         <x:v>4</x:v>
@@ -5598,7 +5477,7 @@
     </x:row>
     <x:row r="118" spans="1:3">
       <x:c r="A118" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
         <x:v>4</x:v>
@@ -5609,7 +5488,7 @@
     </x:row>
     <x:row r="119" spans="1:3">
       <x:c r="A119" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
         <x:v>4</x:v>
@@ -5620,7 +5499,7 @@
     </x:row>
     <x:row r="120" spans="1:3">
       <x:c r="A120" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
         <x:v>4</x:v>
@@ -5631,7 +5510,7 @@
     </x:row>
     <x:row r="121" spans="1:3">
       <x:c r="A121" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
         <x:v>4</x:v>
@@ -5642,7 +5521,7 @@
     </x:row>
     <x:row r="122" spans="1:3">
       <x:c r="A122" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
         <x:v>4</x:v>
@@ -5653,7 +5532,7 @@
     </x:row>
     <x:row r="123" spans="1:3">
       <x:c r="A123" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
         <x:v>4</x:v>
@@ -5664,7 +5543,7 @@
     </x:row>
     <x:row r="124" spans="1:3">
       <x:c r="A124" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
         <x:v>4</x:v>
@@ -5675,7 +5554,7 @@
     </x:row>
     <x:row r="125" spans="1:3">
       <x:c r="A125" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
         <x:v>4</x:v>
@@ -5686,7 +5565,7 @@
     </x:row>
     <x:row r="126" spans="1:3">
       <x:c r="A126" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
         <x:v>4</x:v>
@@ -5697,7 +5576,7 @@
     </x:row>
     <x:row r="127" spans="1:3">
       <x:c r="A127" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
         <x:v>4</x:v>
@@ -5708,7 +5587,7 @@
     </x:row>
     <x:row r="128" spans="1:3">
       <x:c r="A128" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
         <x:v>4</x:v>
@@ -5719,7 +5598,7 @@
     </x:row>
     <x:row r="129" spans="1:3">
       <x:c r="A129" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
         <x:v>4</x:v>
@@ -5730,7 +5609,7 @@
     </x:row>
     <x:row r="130" spans="1:3">
       <x:c r="A130" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
         <x:v>4</x:v>
@@ -5741,7 +5620,7 @@
     </x:row>
     <x:row r="131" spans="1:3">
       <x:c r="A131" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
         <x:v>4</x:v>
@@ -5752,7 +5631,7 @@
     </x:row>
     <x:row r="132" spans="1:3">
       <x:c r="A132" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
         <x:v>4</x:v>
@@ -5763,7 +5642,7 @@
     </x:row>
     <x:row r="133" spans="1:3">
       <x:c r="A133" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
         <x:v>4</x:v>
@@ -5774,7 +5653,7 @@
     </x:row>
     <x:row r="134" spans="1:3">
       <x:c r="A134" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
         <x:v>4</x:v>
@@ -5785,7 +5664,7 @@
     </x:row>
     <x:row r="135" spans="1:3">
       <x:c r="A135" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
         <x:v>4</x:v>
@@ -5796,7 +5675,7 @@
     </x:row>
     <x:row r="136" spans="1:3">
       <x:c r="A136" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
         <x:v>4</x:v>
@@ -5807,7 +5686,7 @@
     </x:row>
     <x:row r="137" spans="1:3">
       <x:c r="A137" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
         <x:v>4</x:v>
@@ -5818,7 +5697,7 @@
     </x:row>
     <x:row r="138" spans="1:3">
       <x:c r="A138" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
         <x:v>4</x:v>
@@ -5829,7 +5708,7 @@
     </x:row>
     <x:row r="139" spans="1:3">
       <x:c r="A139" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
         <x:v>4</x:v>
@@ -5840,7 +5719,7 @@
     </x:row>
     <x:row r="140" spans="1:3">
       <x:c r="A140" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
         <x:v>4</x:v>
@@ -5851,7 +5730,7 @@
     </x:row>
     <x:row r="141" spans="1:3">
       <x:c r="A141" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
         <x:v>4</x:v>
@@ -5862,7 +5741,7 @@
     </x:row>
     <x:row r="142" spans="1:3">
       <x:c r="A142" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
         <x:v>4</x:v>
@@ -5873,7 +5752,7 @@
     </x:row>
     <x:row r="143" spans="1:3">
       <x:c r="A143" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
         <x:v>4</x:v>
@@ -5884,7 +5763,7 @@
     </x:row>
     <x:row r="144" spans="1:3">
       <x:c r="A144" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
         <x:v>4</x:v>
@@ -5895,7 +5774,7 @@
     </x:row>
     <x:row r="145" spans="1:3">
       <x:c r="A145" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
         <x:v>4</x:v>
@@ -5906,7 +5785,7 @@
     </x:row>
     <x:row r="146" spans="1:3">
       <x:c r="A146" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
         <x:v>4</x:v>
@@ -5917,7 +5796,7 @@
     </x:row>
     <x:row r="147" spans="1:3">
       <x:c r="A147" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
         <x:v>4</x:v>
@@ -5928,7 +5807,7 @@
     </x:row>
     <x:row r="148" spans="1:3">
       <x:c r="A148" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
         <x:v>4</x:v>
@@ -5939,7 +5818,7 @@
     </x:row>
     <x:row r="149" spans="1:3">
       <x:c r="A149" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
         <x:v>4</x:v>
@@ -5950,7 +5829,7 @@
     </x:row>
     <x:row r="150" spans="1:3">
       <x:c r="A150" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
         <x:v>4</x:v>
@@ -5961,7 +5840,7 @@
     </x:row>
     <x:row r="151" spans="1:3">
       <x:c r="A151" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
         <x:v>4</x:v>
@@ -5972,7 +5851,7 @@
     </x:row>
     <x:row r="152" spans="1:3">
       <x:c r="A152" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
         <x:v>4</x:v>
@@ -5983,7 +5862,7 @@
     </x:row>
     <x:row r="153" spans="1:3">
       <x:c r="A153" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
         <x:v>4</x:v>
@@ -5994,7 +5873,7 @@
     </x:row>
     <x:row r="154" spans="1:3">
       <x:c r="A154" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
         <x:v>4</x:v>
@@ -6005,7 +5884,7 @@
     </x:row>
     <x:row r="155" spans="1:3">
       <x:c r="A155" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
         <x:v>4</x:v>
@@ -6016,7 +5895,7 @@
     </x:row>
     <x:row r="156" spans="1:3">
       <x:c r="A156" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
         <x:v>4</x:v>
@@ -6027,7 +5906,7 @@
     </x:row>
     <x:row r="157" spans="1:3">
       <x:c r="A157" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
         <x:v>4</x:v>
@@ -6038,7 +5917,7 @@
     </x:row>
     <x:row r="158" spans="1:3">
       <x:c r="A158" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
         <x:v>4</x:v>
@@ -6049,7 +5928,7 @@
     </x:row>
     <x:row r="159" spans="1:3">
       <x:c r="A159" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
         <x:v>4</x:v>
@@ -6060,7 +5939,7 @@
     </x:row>
     <x:row r="160" spans="1:3">
       <x:c r="A160" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
         <x:v>4</x:v>
@@ -6071,7 +5950,7 @@
     </x:row>
     <x:row r="161" spans="1:3">
       <x:c r="A161" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
         <x:v>4</x:v>
@@ -6082,7 +5961,7 @@
     </x:row>
     <x:row r="162" spans="1:3">
       <x:c r="A162" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
         <x:v>4</x:v>
@@ -6093,7 +5972,7 @@
     </x:row>
     <x:row r="163" spans="1:3">
       <x:c r="A163" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
         <x:v>4</x:v>
@@ -6104,7 +5983,7 @@
     </x:row>
     <x:row r="164" spans="1:3">
       <x:c r="A164" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
         <x:v>4</x:v>
@@ -6115,7 +5994,7 @@
     </x:row>
     <x:row r="165" spans="1:3">
       <x:c r="A165" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
         <x:v>4</x:v>
@@ -6126,7 +6005,7 @@
     </x:row>
     <x:row r="166" spans="1:3">
       <x:c r="A166" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
         <x:v>4</x:v>
@@ -6137,7 +6016,7 @@
     </x:row>
     <x:row r="167" spans="1:3">
       <x:c r="A167" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
         <x:v>4</x:v>
@@ -6148,7 +6027,7 @@
     </x:row>
     <x:row r="168" spans="1:3">
       <x:c r="A168" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
         <x:v>4</x:v>
@@ -6159,7 +6038,7 @@
     </x:row>
     <x:row r="169" spans="1:3">
       <x:c r="A169" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
         <x:v>4</x:v>
@@ -6170,7 +6049,7 @@
     </x:row>
     <x:row r="170" spans="1:3">
       <x:c r="A170" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
         <x:v>4</x:v>
@@ -6181,7 +6060,7 @@
     </x:row>
     <x:row r="171" spans="1:3">
       <x:c r="A171" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
         <x:v>4</x:v>
@@ -6192,7 +6071,7 @@
     </x:row>
     <x:row r="172" spans="1:3">
       <x:c r="A172" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
         <x:v>4</x:v>
@@ -6203,7 +6082,7 @@
     </x:row>
     <x:row r="173" spans="1:3">
       <x:c r="A173" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
         <x:v>4</x:v>
@@ -6214,7 +6093,7 @@
     </x:row>
     <x:row r="174" spans="1:3">
       <x:c r="A174" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
         <x:v>4</x:v>
@@ -6225,7 +6104,7 @@
     </x:row>
     <x:row r="175" spans="1:3">
       <x:c r="A175" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
         <x:v>4</x:v>
@@ -6236,7 +6115,7 @@
     </x:row>
     <x:row r="176" spans="1:3">
       <x:c r="A176" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
         <x:v>4</x:v>
@@ -6247,7 +6126,7 @@
     </x:row>
     <x:row r="177" spans="1:3">
       <x:c r="A177" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
         <x:v>4</x:v>
@@ -6258,7 +6137,7 @@
     </x:row>
     <x:row r="178" spans="1:3">
       <x:c r="A178" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
         <x:v>4</x:v>
@@ -6269,7 +6148,7 @@
     </x:row>
     <x:row r="179" spans="1:3">
       <x:c r="A179" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
         <x:v>4</x:v>
@@ -6280,7 +6159,7 @@
     </x:row>
     <x:row r="180" spans="1:3">
       <x:c r="A180" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
         <x:v>4</x:v>
@@ -6291,7 +6170,7 @@
     </x:row>
     <x:row r="181" spans="1:3">
       <x:c r="A181" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
         <x:v>4</x:v>
@@ -6302,7 +6181,7 @@
     </x:row>
     <x:row r="182" spans="1:3">
       <x:c r="A182" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
         <x:v>4</x:v>
@@ -6313,7 +6192,7 @@
     </x:row>
     <x:row r="183" spans="1:3">
       <x:c r="A183" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
         <x:v>4</x:v>
@@ -6324,7 +6203,7 @@
     </x:row>
     <x:row r="184" spans="1:3">
       <x:c r="A184" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
         <x:v>4</x:v>
@@ -6335,7 +6214,7 @@
     </x:row>
     <x:row r="185" spans="1:3">
       <x:c r="A185" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
         <x:v>4</x:v>
@@ -6346,7 +6225,7 @@
     </x:row>
     <x:row r="186" spans="1:3">
       <x:c r="A186" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
         <x:v>4</x:v>
@@ -6357,7 +6236,7 @@
     </x:row>
     <x:row r="187" spans="1:3">
       <x:c r="A187" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
         <x:v>4</x:v>
@@ -6368,7 +6247,7 @@
     </x:row>
     <x:row r="188" spans="1:3">
       <x:c r="A188" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
         <x:v>4</x:v>
@@ -6379,7 +6258,7 @@
     </x:row>
     <x:row r="189" spans="1:3">
       <x:c r="A189" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
         <x:v>4</x:v>
@@ -6390,7 +6269,7 @@
     </x:row>
     <x:row r="190" spans="1:3">
       <x:c r="A190" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
         <x:v>4</x:v>
@@ -6401,7 +6280,7 @@
     </x:row>
     <x:row r="191" spans="1:3">
       <x:c r="A191" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
         <x:v>4</x:v>
@@ -6412,7 +6291,7 @@
     </x:row>
     <x:row r="192" spans="1:3">
       <x:c r="A192" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
         <x:v>4</x:v>
@@ -6423,7 +6302,7 @@
     </x:row>
     <x:row r="193" spans="1:3">
       <x:c r="A193" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
         <x:v>4</x:v>
@@ -6434,7 +6313,7 @@
     </x:row>
     <x:row r="194" spans="1:3">
       <x:c r="A194" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
         <x:v>4</x:v>
@@ -6445,7 +6324,7 @@
     </x:row>
     <x:row r="195" spans="1:3">
       <x:c r="A195" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
         <x:v>4</x:v>
@@ -6456,7 +6335,7 @@
     </x:row>
     <x:row r="196" spans="1:3">
       <x:c r="A196" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
         <x:v>4</x:v>
@@ -6467,7 +6346,7 @@
     </x:row>
     <x:row r="197" spans="1:3">
       <x:c r="A197" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
         <x:v>4</x:v>
@@ -6478,7 +6357,7 @@
     </x:row>
     <x:row r="198" spans="1:3">
       <x:c r="A198" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
         <x:v>4</x:v>
@@ -6489,7 +6368,7 @@
     </x:row>
     <x:row r="199" spans="1:3">
       <x:c r="A199" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
         <x:v>4</x:v>
@@ -6500,7 +6379,7 @@
     </x:row>
     <x:row r="200" spans="1:3">
       <x:c r="A200" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
         <x:v>4</x:v>
@@ -6511,7 +6390,7 @@
     </x:row>
     <x:row r="201" spans="1:3">
       <x:c r="A201" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
         <x:v>4</x:v>
@@ -6522,7 +6401,7 @@
     </x:row>
     <x:row r="202" spans="1:3">
       <x:c r="A202" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
         <x:v>4</x:v>
@@ -6533,7 +6412,7 @@
     </x:row>
     <x:row r="203" spans="1:3">
       <x:c r="A203" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
         <x:v>4</x:v>
@@ -6544,7 +6423,7 @@
     </x:row>
     <x:row r="204" spans="1:3">
       <x:c r="A204" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
         <x:v>4</x:v>
@@ -6555,7 +6434,7 @@
     </x:row>
     <x:row r="205" spans="1:3">
       <x:c r="A205" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
         <x:v>4</x:v>
@@ -6566,7 +6445,7 @@
     </x:row>
     <x:row r="206" spans="1:3">
       <x:c r="A206" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
         <x:v>4</x:v>
@@ -6577,7 +6456,7 @@
     </x:row>
     <x:row r="207" spans="1:3">
       <x:c r="A207" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
         <x:v>4</x:v>
@@ -6588,7 +6467,7 @@
     </x:row>
     <x:row r="208" spans="1:3">
       <x:c r="A208" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
         <x:v>4</x:v>
@@ -6599,7 +6478,7 @@
     </x:row>
     <x:row r="209" spans="1:3">
       <x:c r="A209" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
         <x:v>4</x:v>
@@ -6610,7 +6489,7 @@
     </x:row>
     <x:row r="210" spans="1:3">
       <x:c r="A210" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
         <x:v>4</x:v>
@@ -6621,7 +6500,7 @@
     </x:row>
     <x:row r="211" spans="1:3">
       <x:c r="A211" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
         <x:v>4</x:v>
@@ -6632,7 +6511,7 @@
     </x:row>
     <x:row r="212" spans="1:3">
       <x:c r="A212" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
         <x:v>4</x:v>
@@ -6643,7 +6522,7 @@
     </x:row>
     <x:row r="213" spans="1:3">
       <x:c r="A213" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
         <x:v>4</x:v>
@@ -6654,7 +6533,7 @@
     </x:row>
     <x:row r="214" spans="1:3">
       <x:c r="A214" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
         <x:v>4</x:v>
@@ -6665,7 +6544,7 @@
     </x:row>
     <x:row r="215" spans="1:3">
       <x:c r="A215" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
         <x:v>4</x:v>
@@ -6676,7 +6555,7 @@
     </x:row>
     <x:row r="216" spans="1:3">
       <x:c r="A216" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
         <x:v>4</x:v>
@@ -6687,7 +6566,7 @@
     </x:row>
     <x:row r="217" spans="1:3">
       <x:c r="A217" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
         <x:v>4</x:v>
@@ -6698,7 +6577,7 @@
     </x:row>
     <x:row r="218" spans="1:3">
       <x:c r="A218" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
         <x:v>4</x:v>
@@ -6709,7 +6588,7 @@
     </x:row>
     <x:row r="219" spans="1:3">
       <x:c r="A219" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
         <x:v>4</x:v>
@@ -6720,7 +6599,7 @@
     </x:row>
     <x:row r="220" spans="1:3">
       <x:c r="A220" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
         <x:v>4</x:v>
@@ -6731,7 +6610,7 @@
     </x:row>
     <x:row r="221" spans="1:3">
       <x:c r="A221" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
         <x:v>4</x:v>
@@ -6742,7 +6621,7 @@
     </x:row>
     <x:row r="222" spans="1:3">
       <x:c r="A222" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
         <x:v>4</x:v>
@@ -6753,7 +6632,7 @@
     </x:row>
     <x:row r="223" spans="1:3">
       <x:c r="A223" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
         <x:v>4</x:v>
@@ -6764,7 +6643,7 @@
     </x:row>
     <x:row r="224" spans="1:3">
       <x:c r="A224" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
         <x:v>4</x:v>
@@ -6775,7 +6654,7 @@
     </x:row>
     <x:row r="225" spans="1:3">
       <x:c r="A225" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
         <x:v>4</x:v>
@@ -6786,7 +6665,7 @@
     </x:row>
     <x:row r="226" spans="1:3">
       <x:c r="A226" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
         <x:v>4</x:v>
@@ -6797,7 +6676,7 @@
     </x:row>
     <x:row r="227" spans="1:3">
       <x:c r="A227" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
         <x:v>4</x:v>
@@ -6808,7 +6687,7 @@
     </x:row>
     <x:row r="228" spans="1:3">
       <x:c r="A228" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
         <x:v>4</x:v>
@@ -6819,7 +6698,7 @@
     </x:row>
     <x:row r="229" spans="1:3">
       <x:c r="A229" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
         <x:v>4</x:v>
@@ -6830,7 +6709,7 @@
     </x:row>
     <x:row r="230" spans="1:3">
       <x:c r="A230" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
         <x:v>4</x:v>
@@ -6841,7 +6720,7 @@
     </x:row>
     <x:row r="231" spans="1:3">
       <x:c r="A231" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
         <x:v>4</x:v>
@@ -6852,7 +6731,7 @@
     </x:row>
     <x:row r="232" spans="1:3">
       <x:c r="A232" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
         <x:v>4</x:v>
@@ -6863,7 +6742,7 @@
     </x:row>
     <x:row r="233" spans="1:3">
       <x:c r="A233" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
         <x:v>4</x:v>
@@ -6874,7 +6753,7 @@
     </x:row>
     <x:row r="234" spans="1:3">
       <x:c r="A234" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
         <x:v>4</x:v>
@@ -6885,7 +6764,7 @@
     </x:row>
     <x:row r="235" spans="1:3">
       <x:c r="A235" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
         <x:v>4</x:v>
@@ -6896,7 +6775,7 @@
     </x:row>
     <x:row r="236" spans="1:3">
       <x:c r="A236" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
         <x:v>4</x:v>
@@ -6907,7 +6786,7 @@
     </x:row>
     <x:row r="237" spans="1:3">
       <x:c r="A237" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
         <x:v>4</x:v>
@@ -6918,7 +6797,7 @@
     </x:row>
     <x:row r="238" spans="1:3">
       <x:c r="A238" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
         <x:v>4</x:v>
@@ -6929,7 +6808,7 @@
     </x:row>
     <x:row r="239" spans="1:3">
       <x:c r="A239" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
         <x:v>4</x:v>
@@ -6940,7 +6819,7 @@
     </x:row>
     <x:row r="240" spans="1:3">
       <x:c r="A240" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
         <x:v>4</x:v>
@@ -6951,7 +6830,7 @@
     </x:row>
     <x:row r="241" spans="1:3">
       <x:c r="A241" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
         <x:v>4</x:v>
@@ -6962,7 +6841,7 @@
     </x:row>
     <x:row r="242" spans="1:3">
       <x:c r="A242" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
         <x:v>4</x:v>
@@ -6973,7 +6852,7 @@
     </x:row>
     <x:row r="243" spans="1:3">
       <x:c r="A243" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
         <x:v>4</x:v>
@@ -6984,7 +6863,7 @@
     </x:row>
     <x:row r="244" spans="1:3">
       <x:c r="A244" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
         <x:v>4</x:v>
@@ -6995,7 +6874,7 @@
     </x:row>
     <x:row r="245" spans="1:3">
       <x:c r="A245" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
         <x:v>4</x:v>
@@ -7006,7 +6885,7 @@
     </x:row>
     <x:row r="246" spans="1:3">
       <x:c r="A246" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
         <x:v>4</x:v>
@@ -7017,7 +6896,7 @@
     </x:row>
     <x:row r="247" spans="1:3">
       <x:c r="A247" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
         <x:v>4</x:v>
@@ -7028,7 +6907,7 @@
     </x:row>
     <x:row r="248" spans="1:3">
       <x:c r="A248" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
         <x:v>4</x:v>
@@ -7039,7 +6918,7 @@
     </x:row>
     <x:row r="249" spans="1:3">
       <x:c r="A249" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
         <x:v>4</x:v>
@@ -7050,7 +6929,7 @@
     </x:row>
     <x:row r="250" spans="1:3">
       <x:c r="A250" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
         <x:v>4</x:v>
@@ -7061,7 +6940,7 @@
     </x:row>
     <x:row r="251" spans="1:3">
       <x:c r="A251" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
         <x:v>4</x:v>
@@ -7072,7 +6951,7 @@
     </x:row>
     <x:row r="252" spans="1:3">
       <x:c r="A252" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
         <x:v>4</x:v>
@@ -7083,7 +6962,7 @@
     </x:row>
     <x:row r="253" spans="1:3">
       <x:c r="A253" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
         <x:v>4</x:v>
@@ -7094,7 +6973,7 @@
     </x:row>
     <x:row r="254" spans="1:3">
       <x:c r="A254" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
         <x:v>4</x:v>
@@ -7105,7 +6984,7 @@
     </x:row>
     <x:row r="255" spans="1:3">
       <x:c r="A255" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
         <x:v>4</x:v>
@@ -7116,7 +6995,7 @@
     </x:row>
     <x:row r="256" spans="1:3">
       <x:c r="A256" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
         <x:v>4</x:v>
@@ -7127,7 +7006,7 @@
     </x:row>
     <x:row r="257" spans="1:3">
       <x:c r="A257" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
         <x:v>4</x:v>
@@ -7138,7 +7017,7 @@
     </x:row>
     <x:row r="258" spans="1:3">
       <x:c r="A258" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
         <x:v>4</x:v>
@@ -7149,7 +7028,7 @@
     </x:row>
     <x:row r="259" spans="1:3">
       <x:c r="A259" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
         <x:v>4</x:v>
@@ -7160,7 +7039,7 @@
     </x:row>
     <x:row r="260" spans="1:3">
       <x:c r="A260" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
         <x:v>4</x:v>
@@ -7171,7 +7050,7 @@
     </x:row>
     <x:row r="261" spans="1:3">
       <x:c r="A261" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
         <x:v>4</x:v>
@@ -7182,7 +7061,7 @@
     </x:row>
     <x:row r="262" spans="1:3">
       <x:c r="A262" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
         <x:v>4</x:v>
@@ -7193,7 +7072,7 @@
     </x:row>
     <x:row r="263" spans="1:3">
       <x:c r="A263" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
         <x:v>4</x:v>
@@ -7204,7 +7083,7 @@
     </x:row>
     <x:row r="264" spans="1:3">
       <x:c r="A264" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
         <x:v>4</x:v>
@@ -7215,7 +7094,7 @@
     </x:row>
     <x:row r="265" spans="1:3">
       <x:c r="A265" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
         <x:v>4</x:v>
@@ -7226,7 +7105,7 @@
     </x:row>
     <x:row r="266" spans="1:3">
       <x:c r="A266" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
         <x:v>4</x:v>
@@ -7237,7 +7116,7 @@
     </x:row>
     <x:row r="267" spans="1:3">
       <x:c r="A267" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
         <x:v>4</x:v>
@@ -7248,7 +7127,7 @@
     </x:row>
     <x:row r="268" spans="1:3">
       <x:c r="A268" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
         <x:v>4</x:v>
@@ -7259,7 +7138,7 @@
     </x:row>
     <x:row r="269" spans="1:3">
       <x:c r="A269" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
         <x:v>4</x:v>
@@ -7270,7 +7149,7 @@
     </x:row>
     <x:row r="270" spans="1:3">
       <x:c r="A270" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
         <x:v>4</x:v>
@@ -7281,7 +7160,7 @@
     </x:row>
     <x:row r="271" spans="1:3">
       <x:c r="A271" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
         <x:v>4</x:v>
@@ -7292,7 +7171,7 @@
     </x:row>
     <x:row r="272" spans="1:3">
       <x:c r="A272" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
         <x:v>4</x:v>
@@ -7303,7 +7182,7 @@
     </x:row>
     <x:row r="273" spans="1:3">
       <x:c r="A273" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
         <x:v>4</x:v>
@@ -7314,7 +7193,7 @@
     </x:row>
     <x:row r="274" spans="1:3">
       <x:c r="A274" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
         <x:v>4</x:v>
@@ -7325,7 +7204,7 @@
     </x:row>
     <x:row r="275" spans="1:3">
       <x:c r="A275" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
         <x:v>4</x:v>
@@ -7336,7 +7215,7 @@
     </x:row>
     <x:row r="276" spans="1:3">
       <x:c r="A276" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
         <x:v>4</x:v>
@@ -7347,7 +7226,7 @@
     </x:row>
     <x:row r="277" spans="1:3">
       <x:c r="A277" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
         <x:v>4</x:v>
@@ -7358,7 +7237,7 @@
     </x:row>
     <x:row r="278" spans="1:3">
       <x:c r="A278" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
         <x:v>4</x:v>
@@ -7369,7 +7248,7 @@
     </x:row>
     <x:row r="279" spans="1:3">
       <x:c r="A279" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
         <x:v>4</x:v>
@@ -7380,7 +7259,7 @@
     </x:row>
     <x:row r="280" spans="1:3">
       <x:c r="A280" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
         <x:v>4</x:v>
@@ -7391,7 +7270,7 @@
     </x:row>
     <x:row r="281" spans="1:3">
       <x:c r="A281" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
         <x:v>4</x:v>
@@ -7402,7 +7281,7 @@
     </x:row>
     <x:row r="282" spans="1:3">
       <x:c r="A282" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
         <x:v>4</x:v>
@@ -7413,7 +7292,7 @@
     </x:row>
     <x:row r="283" spans="1:3">
       <x:c r="A283" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
         <x:v>4</x:v>
@@ -7424,7 +7303,7 @@
     </x:row>
     <x:row r="284" spans="1:3">
       <x:c r="A284" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
         <x:v>4</x:v>
@@ -7435,7 +7314,7 @@
     </x:row>
     <x:row r="285" spans="1:3">
       <x:c r="A285" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
         <x:v>4</x:v>
@@ -7446,7 +7325,7 @@
     </x:row>
     <x:row r="286" spans="1:3">
       <x:c r="A286" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B286" s="0" t="s">
         <x:v>4</x:v>
@@ -7457,7 +7336,7 @@
     </x:row>
     <x:row r="287" spans="1:3">
       <x:c r="A287" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B287" s="0" t="s">
         <x:v>4</x:v>
@@ -7468,7 +7347,7 @@
     </x:row>
     <x:row r="288" spans="1:3">
       <x:c r="A288" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B288" s="0" t="s">
         <x:v>4</x:v>
@@ -7479,7 +7358,7 @@
     </x:row>
     <x:row r="289" spans="1:3">
       <x:c r="A289" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="B289" s="0" t="s">
         <x:v>4</x:v>
@@ -7490,7 +7369,7 @@
     </x:row>
     <x:row r="290" spans="1:3">
       <x:c r="A290" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B290" s="0" t="s">
         <x:v>4</x:v>
@@ -7501,7 +7380,7 @@
     </x:row>
     <x:row r="291" spans="1:3">
       <x:c r="A291" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B291" s="0" t="s">
         <x:v>4</x:v>
@@ -7512,7 +7391,7 @@
     </x:row>
     <x:row r="292" spans="1:3">
       <x:c r="A292" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="B292" s="0" t="s">
         <x:v>4</x:v>
@@ -7523,7 +7402,7 @@
     </x:row>
     <x:row r="293" spans="1:3">
       <x:c r="A293" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="B293" s="0" t="s">
         <x:v>4</x:v>
@@ -7534,7 +7413,7 @@
     </x:row>
     <x:row r="294" spans="1:3">
       <x:c r="A294" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B294" s="0" t="s">
         <x:v>4</x:v>
@@ -7545,7 +7424,7 @@
     </x:row>
     <x:row r="295" spans="1:3">
       <x:c r="A295" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B295" s="0" t="s">
         <x:v>4</x:v>
@@ -7556,7 +7435,7 @@
     </x:row>
     <x:row r="296" spans="1:3">
       <x:c r="A296" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B296" s="0" t="s">
         <x:v>4</x:v>
@@ -7567,7 +7446,7 @@
     </x:row>
     <x:row r="297" spans="1:3">
       <x:c r="A297" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B297" s="0" t="s">
         <x:v>4</x:v>
@@ -7578,7 +7457,7 @@
     </x:row>
     <x:row r="298" spans="1:3">
       <x:c r="A298" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B298" s="0" t="s">
         <x:v>4</x:v>
@@ -7589,7 +7468,7 @@
     </x:row>
     <x:row r="299" spans="1:3">
       <x:c r="A299" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B299" s="0" t="s">
         <x:v>4</x:v>
@@ -7600,7 +7479,7 @@
     </x:row>
     <x:row r="300" spans="1:3">
       <x:c r="A300" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B300" s="0" t="s">
         <x:v>4</x:v>
@@ -7611,7 +7490,7 @@
     </x:row>
     <x:row r="301" spans="1:3">
       <x:c r="A301" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="B301" s="0" t="s">
         <x:v>4</x:v>
@@ -7622,7 +7501,7 @@
     </x:row>
     <x:row r="302" spans="1:3">
       <x:c r="A302" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B302" s="0" t="s">
         <x:v>4</x:v>
@@ -7633,7 +7512,7 @@
     </x:row>
     <x:row r="303" spans="1:3">
       <x:c r="A303" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="B303" s="0" t="s">
         <x:v>4</x:v>
@@ -7644,7 +7523,7 @@
     </x:row>
     <x:row r="304" spans="1:3">
       <x:c r="A304" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B304" s="0" t="s">
         <x:v>4</x:v>
@@ -7655,7 +7534,7 @@
     </x:row>
     <x:row r="305" spans="1:3">
       <x:c r="A305" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B305" s="0" t="s">
         <x:v>4</x:v>
@@ -7666,7 +7545,7 @@
     </x:row>
     <x:row r="306" spans="1:3">
       <x:c r="A306" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B306" s="0" t="s">
         <x:v>4</x:v>
@@ -7677,7 +7556,7 @@
     </x:row>
     <x:row r="307" spans="1:3">
       <x:c r="A307" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="B307" s="0" t="s">
         <x:v>4</x:v>
@@ -7688,7 +7567,7 @@
     </x:row>
     <x:row r="308" spans="1:3">
       <x:c r="A308" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="B308" s="0" t="s">
         <x:v>4</x:v>
@@ -7699,7 +7578,7 @@
     </x:row>
     <x:row r="309" spans="1:3">
       <x:c r="A309" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B309" s="0" t="s">
         <x:v>4</x:v>
@@ -7710,7 +7589,7 @@
     </x:row>
     <x:row r="310" spans="1:3">
       <x:c r="A310" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B310" s="0" t="s">
         <x:v>4</x:v>
@@ -7721,7 +7600,7 @@
     </x:row>
     <x:row r="311" spans="1:3">
       <x:c r="A311" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="B311" s="0" t="s">
         <x:v>4</x:v>
@@ -7732,7 +7611,7 @@
     </x:row>
     <x:row r="312" spans="1:3">
       <x:c r="A312" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B312" s="0" t="s">
         <x:v>4</x:v>
@@ -7743,7 +7622,7 @@
     </x:row>
     <x:row r="313" spans="1:3">
       <x:c r="A313" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B313" s="0" t="s">
         <x:v>4</x:v>
@@ -7754,7 +7633,7 @@
     </x:row>
     <x:row r="314" spans="1:3">
       <x:c r="A314" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="B314" s="0" t="s">
         <x:v>4</x:v>
@@ -7765,7 +7644,7 @@
     </x:row>
     <x:row r="315" spans="1:3">
       <x:c r="A315" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="B315" s="0" t="s">
         <x:v>4</x:v>
@@ -7776,7 +7655,7 @@
     </x:row>
     <x:row r="316" spans="1:3">
       <x:c r="A316" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B316" s="0" t="s">
         <x:v>4</x:v>
@@ -7787,7 +7666,7 @@
     </x:row>
     <x:row r="317" spans="1:3">
       <x:c r="A317" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="B317" s="0" t="s">
         <x:v>4</x:v>
@@ -7798,7 +7677,7 @@
     </x:row>
     <x:row r="318" spans="1:3">
       <x:c r="A318" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B318" s="0" t="s">
         <x:v>4</x:v>
@@ -7809,7 +7688,7 @@
     </x:row>
     <x:row r="319" spans="1:3">
       <x:c r="A319" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="B319" s="0" t="s">
         <x:v>4</x:v>
@@ -7820,7 +7699,7 @@
     </x:row>
     <x:row r="320" spans="1:3">
       <x:c r="A320" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B320" s="0" t="s">
         <x:v>4</x:v>
@@ -7831,7 +7710,7 @@
     </x:row>
     <x:row r="321" spans="1:3">
       <x:c r="A321" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="B321" s="0" t="s">
         <x:v>4</x:v>
@@ -7842,7 +7721,7 @@
     </x:row>
     <x:row r="322" spans="1:3">
       <x:c r="A322" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="B322" s="0" t="s">
         <x:v>4</x:v>
@@ -7853,7 +7732,7 @@
     </x:row>
     <x:row r="323" spans="1:3">
       <x:c r="A323" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="B323" s="0" t="s">
         <x:v>4</x:v>
@@ -7864,7 +7743,7 @@
     </x:row>
     <x:row r="324" spans="1:3">
       <x:c r="A324" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B324" s="0" t="s">
         <x:v>4</x:v>
@@ -7875,7 +7754,7 @@
     </x:row>
     <x:row r="325" spans="1:3">
       <x:c r="A325" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="B325" s="0" t="s">
         <x:v>4</x:v>
@@ -7886,7 +7765,7 @@
     </x:row>
     <x:row r="326" spans="1:3">
       <x:c r="A326" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="B326" s="0" t="s">
         <x:v>4</x:v>
@@ -7897,7 +7776,7 @@
     </x:row>
     <x:row r="327" spans="1:3">
       <x:c r="A327" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B327" s="0" t="s">
         <x:v>4</x:v>
@@ -7908,7 +7787,7 @@
     </x:row>
     <x:row r="328" spans="1:3">
       <x:c r="A328" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B328" s="0" t="s">
         <x:v>4</x:v>
@@ -7919,7 +7798,7 @@
     </x:row>
     <x:row r="329" spans="1:3">
       <x:c r="A329" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="B329" s="0" t="s">
         <x:v>4</x:v>
@@ -7930,7 +7809,7 @@
     </x:row>
     <x:row r="330" spans="1:3">
       <x:c r="A330" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="B330" s="0" t="s">
         <x:v>4</x:v>
@@ -7941,7 +7820,7 @@
     </x:row>
     <x:row r="331" spans="1:3">
       <x:c r="A331" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="B331" s="0" t="s">
         <x:v>4</x:v>
@@ -7952,7 +7831,7 @@
     </x:row>
     <x:row r="332" spans="1:3">
       <x:c r="A332" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B332" s="0" t="s">
         <x:v>4</x:v>
@@ -7963,7 +7842,7 @@
     </x:row>
     <x:row r="333" spans="1:3">
       <x:c r="A333" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="B333" s="0" t="s">
         <x:v>4</x:v>
@@ -7974,7 +7853,7 @@
     </x:row>
     <x:row r="334" spans="1:3">
       <x:c r="A334" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B334" s="0" t="s">
         <x:v>4</x:v>
@@ -7985,7 +7864,7 @@
     </x:row>
     <x:row r="335" spans="1:3">
       <x:c r="A335" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B335" s="0" t="s">
         <x:v>4</x:v>
@@ -7996,7 +7875,7 @@
     </x:row>
     <x:row r="336" spans="1:3">
       <x:c r="A336" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B336" s="0" t="s">
         <x:v>4</x:v>
@@ -8007,7 +7886,7 @@
     </x:row>
     <x:row r="337" spans="1:3">
       <x:c r="A337" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="B337" s="0" t="s">
         <x:v>4</x:v>
@@ -8018,7 +7897,7 @@
     </x:row>
     <x:row r="338" spans="1:3">
       <x:c r="A338" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B338" s="0" t="s">
         <x:v>4</x:v>
@@ -8029,7 +7908,7 @@
     </x:row>
     <x:row r="339" spans="1:3">
       <x:c r="A339" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B339" s="0" t="s">
         <x:v>4</x:v>
@@ -8040,7 +7919,7 @@
     </x:row>
     <x:row r="340" spans="1:3">
       <x:c r="A340" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B340" s="0" t="s">
         <x:v>4</x:v>
@@ -8051,7 +7930,7 @@
     </x:row>
     <x:row r="341" spans="1:3">
       <x:c r="A341" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="B341" s="0" t="s">
         <x:v>4</x:v>
@@ -8062,7 +7941,7 @@
     </x:row>
     <x:row r="342" spans="1:3">
       <x:c r="A342" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B342" s="0" t="s">
         <x:v>4</x:v>
@@ -8073,7 +7952,7 @@
     </x:row>
     <x:row r="343" spans="1:3">
       <x:c r="A343" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B343" s="0" t="s">
         <x:v>4</x:v>
@@ -8084,7 +7963,7 @@
     </x:row>
     <x:row r="344" spans="1:3">
       <x:c r="A344" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B344" s="0" t="s">
         <x:v>4</x:v>
@@ -8095,7 +7974,7 @@
     </x:row>
     <x:row r="345" spans="1:3">
       <x:c r="A345" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B345" s="0" t="s">
         <x:v>4</x:v>
@@ -8106,7 +7985,7 @@
     </x:row>
     <x:row r="346" spans="1:3">
       <x:c r="A346" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B346" s="0" t="s">
         <x:v>4</x:v>
@@ -8117,7 +7996,7 @@
     </x:row>
     <x:row r="347" spans="1:3">
       <x:c r="A347" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B347" s="0" t="s">
         <x:v>4</x:v>
@@ -8128,7 +8007,7 @@
     </x:row>
     <x:row r="348" spans="1:3">
       <x:c r="A348" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B348" s="0" t="s">
         <x:v>4</x:v>
@@ -8139,7 +8018,7 @@
     </x:row>
     <x:row r="349" spans="1:3">
       <x:c r="A349" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="B349" s="0" t="s">
         <x:v>4</x:v>
@@ -8150,7 +8029,7 @@
     </x:row>
     <x:row r="350" spans="1:3">
       <x:c r="A350" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="B350" s="0" t="s">
         <x:v>4</x:v>
@@ -8161,7 +8040,7 @@
     </x:row>
     <x:row r="351" spans="1:3">
       <x:c r="A351" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B351" s="0" t="s">
         <x:v>4</x:v>
@@ -8172,7 +8051,7 @@
     </x:row>
     <x:row r="352" spans="1:3">
       <x:c r="A352" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B352" s="0" t="s">
         <x:v>4</x:v>
@@ -8183,7 +8062,7 @@
     </x:row>
     <x:row r="353" spans="1:3">
       <x:c r="A353" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B353" s="0" t="s">
         <x:v>4</x:v>
@@ -8194,7 +8073,7 @@
     </x:row>
     <x:row r="354" spans="1:3">
       <x:c r="A354" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B354" s="0" t="s">
         <x:v>4</x:v>
@@ -8205,7 +8084,7 @@
     </x:row>
     <x:row r="355" spans="1:3">
       <x:c r="A355" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B355" s="0" t="s">
         <x:v>4</x:v>
@@ -8216,7 +8095,7 @@
     </x:row>
     <x:row r="356" spans="1:3">
       <x:c r="A356" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="B356" s="0" t="s">
         <x:v>4</x:v>
@@ -8227,7 +8106,7 @@
     </x:row>
     <x:row r="357" spans="1:3">
       <x:c r="A357" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="B357" s="0" t="s">
         <x:v>4</x:v>
@@ -8238,7 +8117,7 @@
     </x:row>
     <x:row r="358" spans="1:3">
       <x:c r="A358" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="B358" s="0" t="s">
         <x:v>4</x:v>
@@ -8249,7 +8128,7 @@
     </x:row>
     <x:row r="359" spans="1:3">
       <x:c r="A359" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B359" s="0" t="s">
         <x:v>4</x:v>
@@ -8260,7 +8139,7 @@
     </x:row>
     <x:row r="360" spans="1:3">
       <x:c r="A360" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="B360" s="0" t="s">
         <x:v>4</x:v>
@@ -8271,7 +8150,7 @@
     </x:row>
     <x:row r="361" spans="1:3">
       <x:c r="A361" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="B361" s="0" t="s">
         <x:v>4</x:v>
@@ -8282,7 +8161,7 @@
     </x:row>
     <x:row r="362" spans="1:3">
       <x:c r="A362" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B362" s="0" t="s">
         <x:v>4</x:v>
@@ -8293,7 +8172,7 @@
     </x:row>
     <x:row r="363" spans="1:3">
       <x:c r="A363" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B363" s="0" t="s">
         <x:v>4</x:v>
@@ -8304,7 +8183,7 @@
     </x:row>
     <x:row r="364" spans="1:3">
       <x:c r="A364" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="B364" s="0" t="s">
         <x:v>4</x:v>
@@ -8315,7 +8194,7 @@
     </x:row>
     <x:row r="365" spans="1:3">
       <x:c r="A365" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="B365" s="0" t="s">
         <x:v>4</x:v>
@@ -8326,7 +8205,7 @@
     </x:row>
     <x:row r="366" spans="1:3">
       <x:c r="A366" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B366" s="0" t="s">
         <x:v>4</x:v>
@@ -8337,7 +8216,7 @@
     </x:row>
     <x:row r="367" spans="1:3">
       <x:c r="A367" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B367" s="0" t="s">
         <x:v>4</x:v>
@@ -8348,7 +8227,7 @@
     </x:row>
     <x:row r="368" spans="1:3">
       <x:c r="A368" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="B368" s="0" t="s">
         <x:v>4</x:v>
@@ -8359,7 +8238,7 @@
     </x:row>
     <x:row r="369" spans="1:3">
       <x:c r="A369" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="B369" s="0" t="s">
         <x:v>4</x:v>
@@ -8370,7 +8249,7 @@
     </x:row>
     <x:row r="370" spans="1:3">
       <x:c r="A370" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B370" s="0" t="s">
         <x:v>4</x:v>
@@ -8381,7 +8260,7 @@
     </x:row>
     <x:row r="371" spans="1:3">
       <x:c r="A371" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B371" s="0" t="s">
         <x:v>4</x:v>
@@ -8392,7 +8271,7 @@
     </x:row>
     <x:row r="372" spans="1:3">
       <x:c r="A372" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B372" s="0" t="s">
         <x:v>4</x:v>
@@ -8403,7 +8282,7 @@
     </x:row>
     <x:row r="373" spans="1:3">
       <x:c r="A373" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B373" s="0" t="s">
         <x:v>4</x:v>
@@ -8414,7 +8293,7 @@
     </x:row>
     <x:row r="374" spans="1:3">
       <x:c r="A374" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="B374" s="0" t="s">
         <x:v>4</x:v>
@@ -8425,7 +8304,7 @@
     </x:row>
     <x:row r="375" spans="1:3">
       <x:c r="A375" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B375" s="0" t="s">
         <x:v>4</x:v>
@@ -8436,7 +8315,7 @@
     </x:row>
     <x:row r="376" spans="1:3">
       <x:c r="A376" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B376" s="0" t="s">
         <x:v>4</x:v>
@@ -8447,7 +8326,7 @@
     </x:row>
     <x:row r="377" spans="1:3">
       <x:c r="A377" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="B377" s="0" t="s">
         <x:v>4</x:v>
@@ -8458,7 +8337,7 @@
     </x:row>
     <x:row r="378" spans="1:3">
       <x:c r="A378" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B378" s="0" t="s">
         <x:v>4</x:v>
@@ -8469,7 +8348,7 @@
     </x:row>
     <x:row r="379" spans="1:3">
       <x:c r="A379" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B379" s="0" t="s">
         <x:v>4</x:v>
@@ -8480,7 +8359,7 @@
     </x:row>
     <x:row r="380" spans="1:3">
       <x:c r="A380" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="B380" s="0" t="s">
         <x:v>4</x:v>
@@ -8491,7 +8370,7 @@
     </x:row>
     <x:row r="381" spans="1:3">
       <x:c r="A381" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="B381" s="0" t="s">
         <x:v>4</x:v>
@@ -8502,7 +8381,7 @@
     </x:row>
     <x:row r="382" spans="1:3">
       <x:c r="A382" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="B382" s="0" t="s">
         <x:v>4</x:v>
@@ -8513,7 +8392,7 @@
     </x:row>
     <x:row r="383" spans="1:3">
       <x:c r="A383" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B383" s="0" t="s">
         <x:v>4</x:v>
@@ -8524,7 +8403,7 @@
     </x:row>
     <x:row r="384" spans="1:3">
       <x:c r="A384" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="B384" s="0" t="s">
         <x:v>4</x:v>
@@ -8535,7 +8414,7 @@
     </x:row>
     <x:row r="385" spans="1:3">
       <x:c r="A385" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="B385" s="0" t="s">
         <x:v>4</x:v>
@@ -8546,7 +8425,7 @@
     </x:row>
     <x:row r="386" spans="1:3">
       <x:c r="A386" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B386" s="0" t="s">
         <x:v>4</x:v>
@@ -8557,7 +8436,7 @@
     </x:row>
     <x:row r="387" spans="1:3">
       <x:c r="A387" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B387" s="0" t="s">
         <x:v>4</x:v>
@@ -8568,7 +8447,7 @@
     </x:row>
     <x:row r="388" spans="1:3">
       <x:c r="A388" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="B388" s="0" t="s">
         <x:v>4</x:v>
@@ -8579,7 +8458,7 @@
     </x:row>
     <x:row r="389" spans="1:3">
       <x:c r="A389" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="B389" s="0" t="s">
         <x:v>4</x:v>
@@ -8590,7 +8469,7 @@
     </x:row>
     <x:row r="390" spans="1:3">
       <x:c r="A390" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="B390" s="0" t="s">
         <x:v>4</x:v>
@@ -8601,7 +8480,7 @@
     </x:row>
     <x:row r="391" spans="1:3">
       <x:c r="A391" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B391" s="0" t="s">
         <x:v>4</x:v>
@@ -8612,7 +8491,7 @@
     </x:row>
     <x:row r="392" spans="1:3">
       <x:c r="A392" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B392" s="0" t="s">
         <x:v>4</x:v>
@@ -8623,7 +8502,7 @@
     </x:row>
     <x:row r="393" spans="1:3">
       <x:c r="A393" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="B393" s="0" t="s">
         <x:v>4</x:v>
@@ -8634,7 +8513,7 @@
     </x:row>
     <x:row r="394" spans="1:3">
       <x:c r="A394" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B394" s="0" t="s">
         <x:v>4</x:v>
@@ -8645,7 +8524,7 @@
     </x:row>
     <x:row r="395" spans="1:3">
       <x:c r="A395" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B395" s="0" t="s">
         <x:v>4</x:v>
@@ -8656,7 +8535,7 @@
     </x:row>
     <x:row r="396" spans="1:3">
       <x:c r="A396" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="B396" s="0" t="s">
         <x:v>4</x:v>
@@ -8667,7 +8546,7 @@
     </x:row>
     <x:row r="397" spans="1:3">
       <x:c r="A397" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B397" s="0" t="s">
         <x:v>4</x:v>
@@ -8678,7 +8557,7 @@
     </x:row>
     <x:row r="398" spans="1:3">
       <x:c r="A398" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="B398" s="0" t="s">
         <x:v>4</x:v>
@@ -8689,7 +8568,7 @@
     </x:row>
     <x:row r="399" spans="1:3">
       <x:c r="A399" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B399" s="0" t="s">
         <x:v>4</x:v>
@@ -8700,7 +8579,7 @@
     </x:row>
     <x:row r="400" spans="1:3">
       <x:c r="A400" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="B400" s="0" t="s">
         <x:v>4</x:v>
@@ -8711,7 +8590,7 @@
     </x:row>
     <x:row r="401" spans="1:3">
       <x:c r="A401" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="B401" s="0" t="s">
         <x:v>4</x:v>
@@ -8722,7 +8601,7 @@
     </x:row>
     <x:row r="402" spans="1:3">
       <x:c r="A402" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B402" s="0" t="s">
         <x:v>4</x:v>
@@ -8733,7 +8612,7 @@
     </x:row>
     <x:row r="403" spans="1:3">
       <x:c r="A403" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B403" s="0" t="s">
         <x:v>4</x:v>
@@ -8744,7 +8623,7 @@
     </x:row>
     <x:row r="404" spans="1:3">
       <x:c r="A404" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="B404" s="0" t="s">
         <x:v>4</x:v>
@@ -8755,7 +8634,7 @@
     </x:row>
     <x:row r="405" spans="1:3">
       <x:c r="A405" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="B405" s="0" t="s">
         <x:v>4</x:v>
@@ -8766,7 +8645,7 @@
     </x:row>
     <x:row r="406" spans="1:3">
       <x:c r="A406" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="B406" s="0" t="s">
         <x:v>4</x:v>
@@ -8777,7 +8656,7 @@
     </x:row>
     <x:row r="407" spans="1:3">
       <x:c r="A407" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B407" s="0" t="s">
         <x:v>4</x:v>
@@ -8788,7 +8667,7 @@
     </x:row>
     <x:row r="408" spans="1:3">
       <x:c r="A408" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="B408" s="0" t="s">
         <x:v>4</x:v>
@@ -8799,7 +8678,7 @@
     </x:row>
     <x:row r="409" spans="1:3">
       <x:c r="A409" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="B409" s="0" t="s">
         <x:v>4</x:v>
@@ -8810,7 +8689,7 @@
     </x:row>
     <x:row r="410" spans="1:3">
       <x:c r="A410" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B410" s="0" t="s">
         <x:v>4</x:v>
@@ -8821,7 +8700,7 @@
     </x:row>
     <x:row r="411" spans="1:3">
       <x:c r="A411" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B411" s="0" t="s">
         <x:v>4</x:v>
@@ -8832,7 +8711,7 @@
     </x:row>
     <x:row r="412" spans="1:3">
       <x:c r="A412" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="B412" s="0" t="s">
         <x:v>4</x:v>
@@ -8843,7 +8722,7 @@
     </x:row>
     <x:row r="413" spans="1:3">
       <x:c r="A413" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="B413" s="0" t="s">
         <x:v>4</x:v>
@@ -8854,7 +8733,7 @@
     </x:row>
     <x:row r="414" spans="1:3">
       <x:c r="A414" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B414" s="0" t="s">
         <x:v>4</x:v>
@@ -8865,7 +8744,7 @@
     </x:row>
     <x:row r="415" spans="1:3">
       <x:c r="A415" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B415" s="0" t="s">
         <x:v>4</x:v>
@@ -8876,7 +8755,7 @@
     </x:row>
     <x:row r="416" spans="1:3">
       <x:c r="A416" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B416" s="0" t="s">
         <x:v>4</x:v>
@@ -8887,7 +8766,7 @@
     </x:row>
     <x:row r="417" spans="1:3">
       <x:c r="A417" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B417" s="0" t="s">
         <x:v>4</x:v>
@@ -8898,7 +8777,7 @@
     </x:row>
     <x:row r="418" spans="1:3">
       <x:c r="A418" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B418" s="0" t="s">
         <x:v>4</x:v>
@@ -8909,7 +8788,7 @@
     </x:row>
     <x:row r="419" spans="1:3">
       <x:c r="A419" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="B419" s="0" t="s">
         <x:v>4</x:v>
@@ -8920,7 +8799,7 @@
     </x:row>
     <x:row r="420" spans="1:3">
       <x:c r="A420" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B420" s="0" t="s">
         <x:v>4</x:v>
@@ -8931,7 +8810,7 @@
     </x:row>
     <x:row r="421" spans="1:3">
       <x:c r="A421" s="0" t="s">
-        <x:v>612</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="B421" s="0" t="s">
         <x:v>4</x:v>
@@ -8942,7 +8821,7 @@
     </x:row>
     <x:row r="422" spans="1:3">
       <x:c r="A422" s="0" t="s">
-        <x:v>613</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B422" s="0" t="s">
         <x:v>4</x:v>
@@ -8953,12 +8832,133 @@
     </x:row>
     <x:row r="423" spans="1:3">
       <x:c r="A423" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B423" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C423" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" spans="1:3">
+      <x:c r="A424" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B424" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C424" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" spans="1:3">
+      <x:c r="A425" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="B425" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C425" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" spans="1:3">
+      <x:c r="A426" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B426" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C426" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" spans="1:3">
+      <x:c r="A427" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="B427" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C427" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" spans="1:3">
+      <x:c r="A428" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B428" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C428" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" spans="1:3">
+      <x:c r="A429" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B429" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C429" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" spans="1:3">
+      <x:c r="A430" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="B430" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C430" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" spans="1:3">
+      <x:c r="A431" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="B431" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C431" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" spans="1:3">
+      <x:c r="A432" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B432" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C432" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" spans="1:3">
+      <x:c r="A433" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B433" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C433" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" spans="1:3">
+      <x:c r="A434" s="0" t="s">
         <x:v>614</x:v>
       </x:c>
-      <x:c r="B423" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C423" s="0" t="s">
+      <x:c r="B434" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C434" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>

--- a/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
+++ b/app/borsa/gosterge-taramalari/data/Yükselis-trendi.xlsx
@@ -44,6 +44,9 @@
     <x:t>AEFES</x:t>
   </x:si>
   <x:si>
+    <x:t>AGESA</x:t>
+  </x:si>
+  <x:si>
     <x:t>AGYO</x:t>
   </x:si>
   <x:si>
@@ -98,1657 +101,1654 @@
     <x:t>AVGYO</x:t>
   </x:si>
   <x:si>
+    <x:t>AYGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEYAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BSOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURCE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BYDNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CATES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CCOLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMZY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CGCAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CIMSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CVKMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CWENE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMRGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFRB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DSTKF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EBEBK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECZYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGGUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGPRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENJSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENKAI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EREGL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUKYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUPWR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FONET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRNYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUBRF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUNDG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GWIND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HDFGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEDEF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOROZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HURGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBCT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICUGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IEYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHAAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISDMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZINV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAPLM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KBORU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRPLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRVGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTLEV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KTSKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LMKDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MANAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>METRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ODINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONCSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZATD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZRDN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNSUT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRDGS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRZMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RALYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RGYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUZYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELEC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYLP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SURGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TABGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCKRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEZOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TKFEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOASO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TUPRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURGG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ULUUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VANGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YEOTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YUNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZEDUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1CAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AAGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADESE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFYON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AGROT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHGAZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHSGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKBNK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKENR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKFGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKGRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKHAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKMGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALCTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALFAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALKLC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANHYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARCLK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARENA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARFYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARMGD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARZUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATAKP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATATR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATEKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATSYH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVOD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVPGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVTUR</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYCES</x:t>
   </x:si>
   <x:si>
+    <x:t>AYDEM</x:t>
+  </x:si>
+  <x:si>
     <x:t>AYEN</x:t>
   </x:si>
   <x:si>
-    <x:t>AYGAZ</x:t>
+    <x:t>AYES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAGFS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAHKM</x:t>
   </x:si>
   <x:si>
     <x:t>BAKAB</x:t>
   </x:si>
   <x:si>
-    <x:t>BARMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEYAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKO</x:t>
+    <x:t>BALAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BALSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANVT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BASGZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAYRK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESLR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BESTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BFREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIENY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIGTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINBN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIOEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BJKAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLCYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BLUME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BMSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BNTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOBET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BORLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOSSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRKVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRLSM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRSAN</x:t>
   </x:si>
   <x:si>
     <x:t>BRYAT</x:t>
   </x:si>
   <x:si>
-    <x:t>BSOKE</x:t>
+    <x:t>BTCIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCIM</x:t>
   </x:si>
   <x:si>
     <x:t>BULGS</x:t>
   </x:si>
   <x:si>
-    <x:t>BURCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CATES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CCOLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMZY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CGCAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CIMSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CWENE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMRGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFRB</x:t>
+    <x:t>CANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEMTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEOEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLEBI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMBTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COSMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRFSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CUSAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAGI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAPGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DARDL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DCTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DERIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESPC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DGNMO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIRIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMSAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DNISI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOFER</x:t>
   </x:si>
   <x:si>
     <x:t>DOGUB</x:t>
   </x:si>
   <x:si>
-    <x:t>DOHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DSTKF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURDO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EBEBK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECZYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGGUB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGPRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENJSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENKAI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EREGL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUKYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUPWR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FLAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FONET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARFA</x:t>
+    <x:t>DOKTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DURKN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DYOBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ECOGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGEGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EKSUN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELITE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMKEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMNIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMPAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENDAE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENERY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENPRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENSRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENTRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EPLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERBOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERCB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESCAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ESEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETILR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ETYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EYGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FADE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FENER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FMIZP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRMPL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FROTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FZLGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARAN</x:t>
   </x:si>
   <x:si>
     <x:t>GATEG</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEREL</x:t>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GENTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GESAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GIPTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLBMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLCVY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLRMK</x:t>
   </x:si>
   <x:si>
     <x:t>GLRYH</x:t>
   </x:si>
   <x:si>
-    <x:t>GMTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRNYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUBRF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GUNDG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GWIND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HDFGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEDEF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOROZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBCT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICUGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IEYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHAAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INDES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISDMR</x:t>
+    <x:t>GLYHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOKNR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOZDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRSEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRTHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GSRAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GZNMI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HATSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEKTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HKTM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HRKET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HTTBT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUBVC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUNER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHEVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHGZT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHLGM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IHYAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IMASM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INGRM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBIR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISCTR</x:t>
   </x:si>
   <x:si>
     <x:t>ISFIN</x:t>
   </x:si>
   <x:si>
-    <x:t>ISKPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZINV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAPLM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KBORU</x:t>
+    <x:t>ISGSY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISKUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISSEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IZMDC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JANTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAREL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KARTN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KATMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KAYSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KCAER</x:t>
   </x:si>
   <x:si>
     <x:t>KCHOL</x:t>
   </x:si>
   <x:si>
-    <x:t>KGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRPLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRVGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTLEV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTSKR</x:t>
+    <x:t>KENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KERVN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KFEIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIMMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLNMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLRHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLSER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KLYPV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KMPUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNFRT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOCMT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KONYA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KORDS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRDMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRONT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRSTL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KSTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUTPO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVVA</x:t>
   </x:si>
   <x:si>
     <x:t>KUYAS</x:t>
   </x:si>
   <x:si>
-    <x:t>LMKDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MACKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MANAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>METRO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBASE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ODINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONCSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZATD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZRDN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZSUB</x:t>
+    <x:t>KZBGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KZGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIDFA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LILAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LINK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LKMNH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LRSHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUKSK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LXGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LYDYE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAKTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARKA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARMR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARTI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAVI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEGAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKAG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEPET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERCN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEYSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGROS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MHRGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIATK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MMCAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDRS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MNDTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOPAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPARK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MRSHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRKS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTRYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MZHLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NETCD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NIBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NTHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NUHCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBAMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OFSYM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONRYT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORCAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSTIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTKAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OTTO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAKC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYLUM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYYAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OZKGY</x:t>
   </x:si>
   <x:si>
     <x:t>OZYSR</x:t>
   </x:si>
   <x:si>
-    <x:t>PAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNSUT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRDGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRZMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RALYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RGYAS</x:t>
+    <x:t>PAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAMEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASEU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCILT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PENTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PGSUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PINSU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PKENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PLTUR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PNLSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRKAB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSDTC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBFK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNBTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QUAGR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAYSG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REEDR</x:t>
   </x:si>
   <x:si>
     <x:t>RNPOL</x:t>
   </x:si>
   <x:si>
-    <x:t>RUZYE</x:t>
+    <x:t>RODRG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RTALB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RUBNS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RYGYO</x:t>
   </x:si>
   <x:si>
     <x:t>RYSAS</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELEC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYLP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SURGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TABGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCKRC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEZOL</x:t>
+    <x:t>SAFKR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAHOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANFM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SANKO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SARKY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SASA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAYAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SDTTR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGMN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SERNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEYKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SILVR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKTAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKYMD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRTG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMRVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SNPAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SODSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SONME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SRVGY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUNTK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUWEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TARKM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TATEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TAVHL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TBORG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TCELL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TDGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEKTU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TGSAS</x:t>
   </x:si>
   <x:si>
     <x:t>THYAO</x:t>
   </x:si>
   <x:si>
-    <x:t>TKFEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TOASO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRHOL</x:t>
+    <x:t>TKNSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMPOL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TMSN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TNZTP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRALT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRENJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRILC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRMET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSGYO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSKB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TSPOR</x:t>
   </x:si>
   <x:si>
     <x:t>TTKOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TUPRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURGG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ULUUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VANGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YEOTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YUNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZEDUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1CAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AAGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ADESE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGESA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AGROT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHGAZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHSGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKBNK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKENR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKFGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKGRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKHAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKMGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AKYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALBRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALCTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALFAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALKLC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANHYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARCLK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARENA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARFYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARMGD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARZUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATAKP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATATR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATEKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATSYH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVOD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVPGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYDEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AYES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAGFS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAHKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BALSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANVT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BASGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAYRK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESLR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BESTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BFREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIENY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIGTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINBN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BINHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIOEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BJKAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLCYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BMSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BNTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOBET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BORLS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOSSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRISA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRKVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRLSM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUCIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BYDNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CANTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CELHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEMTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CEOEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLEBI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMBTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COSMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRFSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CUSAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CVKMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAGI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAPGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DARDL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DCTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DERIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESPC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DGNMO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIRIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DITAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DNISI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOCO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DOKTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DURKN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DYOBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ECOGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EFOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGEGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EKSUN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELITE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMKEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMNIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMPAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENDAE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENERY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENPRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENSRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ENTRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EPLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERBOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ERCB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESCAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ESEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETILR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ETYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FADE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FENER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FMIZP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRMPL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FROTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FZLGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GENTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GESAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIPTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLBMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLCVY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLRMK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLYHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOKNR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOZDE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRSEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRTHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GSRAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GZNMI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HATSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HEKTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HKTM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HRKET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HTTBT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUBVC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUNER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HURGZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHEVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHGZT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHLGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IHYAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IMASM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INGRM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBIR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISCTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGSY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISKUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISSEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IZMDC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JANTS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAREL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KARTN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KATMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KAYSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KCAER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KERVN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KFEIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIMMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLNMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLRHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLSER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KLYPV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KMPUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNFRT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOCMT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KONYA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KORDS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRDMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRONT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRSTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KRTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KSTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUTPO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZBGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KZGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIDFA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LILAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LKMNH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LRSHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUKSK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LXGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LYDYE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAKTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARKA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARMR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARTI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAVI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEGAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKAG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEPET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERCN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MERKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEYSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGROS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MHRGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIATK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MMCAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDRS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MNDTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOBTL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOPAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MPARK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MRSHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRKS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTRYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MZHLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NETCD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NIBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NTHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NUHCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBAMS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OFSYM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ONRYT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORCAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORMA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSTIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTKAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OTTO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAKC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYLUM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYYAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OZKGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAMEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PASEU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCILT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PENTA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PGSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PINSU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PKENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PLTUR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PNLSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POLTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRKAB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSDTC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBFK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNBTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QUAGR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RAYSG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REEDR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RODRG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RTALB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RUBNS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RYGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAFKR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANFM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SANKO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SARKY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SASA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAYAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SDTTR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGMN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SERNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEYKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SILVR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKTAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKYMD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRTG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMRVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SNPAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SODSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SONME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SRVGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUMAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUNTK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUWEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TARKM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TATEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TAVHL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TBORG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TCELL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TDGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEHOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEKTU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TGSAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TKNSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TLMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMPOL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TMSN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TNZTP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRALT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRENJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRILC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRMET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSGYO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSKB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TSPOR</x:t>
   </x:si>
   <x:si>
     <x:t>TTRAK</x:t>
@@ -2210,7 +2210,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C178"/>
+  <x:dimension ref="A1:C173"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4113,61 +4113,6 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C173" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" spans="1:3">
-      <x:c r="A174" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="B174" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C174" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" spans="1:3">
-      <x:c r="A175" s="0" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="B175" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C175" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" spans="1:3">
-      <x:c r="A176" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="B176" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C176" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" spans="1:3">
-      <x:c r="A177" s="0" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="B177" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C177" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" spans="1:3">
-      <x:c r="A178" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="B178" s="0" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C178" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -4185,7 +4130,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C434"/>
+  <x:dimension ref="A1:C439"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
@@ -4201,7 +4146,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
@@ -4212,7 +4157,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
         <x:v>4</x:v>
@@ -4223,7 +4168,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
         <x:v>4</x:v>
@@ -4234,7 +4179,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>4</x:v>
@@ -4245,7 +4190,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>4</x:v>
@@ -4256,7 +4201,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>4</x:v>
@@ -4267,7 +4212,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
         <x:v>4</x:v>
@@ -4278,7 +4223,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>4</x:v>
@@ -4289,7 +4234,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>4</x:v>
@@ -4300,7 +4245,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>4</x:v>
@@ -4311,7 +4256,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>4</x:v>
@@ -4322,7 +4267,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>4</x:v>
@@ -4333,7 +4278,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>4</x:v>
@@ -4344,7 +4289,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>4</x:v>
@@ -4355,7 +4300,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
         <x:v>4</x:v>
@@ -4366,7 +4311,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
         <x:v>4</x:v>
@@ -4377,7 +4322,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
         <x:v>4</x:v>
@@ -4388,7 +4333,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
         <x:v>4</x:v>
@@ -4399,7 +4344,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
         <x:v>4</x:v>
@@ -4410,7 +4355,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
         <x:v>4</x:v>
@@ -4421,7 +4366,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
         <x:v>4</x:v>
@@ -4432,7 +4377,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
         <x:v>4</x:v>
@@ -4443,7 +4388,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
         <x:v>4</x:v>
@@ -4454,7 +4399,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
         <x:v>4</x:v>
@@ -4465,7 +4410,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
         <x:v>4</x:v>
@@ -4476,7 +4421,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
         <x:v>4</x:v>
@@ -4487,7 +4432,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
         <x:v>4</x:v>
@@ -4498,7 +4443,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
         <x:v>4</x:v>
@@ -4509,7 +4454,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
         <x:v>4</x:v>
@@ -4520,7 +4465,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
         <x:v>4</x:v>
@@ -4531,7 +4476,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
         <x:v>4</x:v>
@@ -4542,7 +4487,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
         <x:v>4</x:v>
@@ -4553,7 +4498,7 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
         <x:v>4</x:v>
@@ -4564,7 +4509,7 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
         <x:v>4</x:v>
@@ -4575,7 +4520,7 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
         <x:v>4</x:v>
@@ -4586,7 +4531,7 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
         <x:v>4</x:v>
@@ -4597,7 +4542,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
         <x:v>4</x:v>
@@ -4608,7 +4553,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
         <x:v>4</x:v>
@@ -4619,7 +4564,7 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
         <x:v>4</x:v>
@@ -4630,7 +4575,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
         <x:v>4</x:v>
@@ -4641,7 +4586,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
         <x:v>4</x:v>
@@ -4652,7 +4597,7 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
         <x:v>4</x:v>
@@ -4663,7 +4608,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
         <x:v>4</x:v>
@@ -4674,7 +4619,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
         <x:v>4</x:v>
@@ -4685,7 +4630,7 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
         <x:v>4</x:v>
@@ -4696,7 +4641,7 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
         <x:v>4</x:v>
@@ -4707,7 +4652,7 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
         <x:v>4</x:v>
@@ -4718,7 +4663,7 @@
     </x:row>
     <x:row r="49" spans="1:3">
       <x:c r="A49" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
         <x:v>4</x:v>
@@ -4729,7 +4674,7 @@
     </x:row>
     <x:row r="50" spans="1:3">
       <x:c r="A50" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
         <x:v>4</x:v>
@@ -4740,7 +4685,7 @@
     </x:row>
     <x:row r="51" spans="1:3">
       <x:c r="A51" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
         <x:v>4</x:v>
@@ -4751,7 +4696,7 @@
     </x:row>
     <x:row r="52" spans="1:3">
       <x:c r="A52" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
         <x:v>4</x:v>
@@ -4762,7 +4707,7 @@
     </x:row>
     <x:row r="53" spans="1:3">
       <x:c r="A53" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
         <x:v>4</x:v>
@@ -4773,7 +4718,7 @@
     </x:row>
     <x:row r="54" spans="1:3">
       <x:c r="A54" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
         <x:v>4</x:v>
@@ -4784,7 +4729,7 @@
     </x:row>
     <x:row r="55" spans="1:3">
       <x:c r="A55" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
         <x:v>4</x:v>
@@ -4795,7 +4740,7 @@
     </x:row>
     <x:row r="56" spans="1:3">
       <x:c r="A56" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
         <x:v>4</x:v>
@@ -4806,7 +4751,7 @@
     </x:row>
     <x:row r="57" spans="1:3">
       <x:c r="A57" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
         <x:v>4</x:v>
@@ -4817,7 +4762,7 @@
     </x:row>
     <x:row r="58" spans="1:3">
       <x:c r="A58" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
         <x:v>4</x:v>
@@ -4828,7 +4773,7 @@
     </x:row>
     <x:row r="59" spans="1:3">
       <x:c r="A59" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>4</x:v>
@@ -4839,7 +4784,7 @@
     </x:row>
     <x:row r="60" spans="1:3">
       <x:c r="A60" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>4</x:v>
@@ -4850,7 +4795,7 @@
     </x:row>
     <x:row r="61" spans="1:3">
       <x:c r="A61" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>4</x:v>
@@ -4861,7 +4806,7 @@
     </x:row>
     <x:row r="62" spans="1:3">
       <x:c r="A62" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>4</x:v>
@@ -4872,7 +4817,7 @@
     </x:row>
     <x:row r="63" spans="1:3">
       <x:c r="A63" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>4</x:v>
@@ -4883,7 +4828,7 @@
     </x:row>
     <x:row r="64" spans="1:3">
       <x:c r="A64" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
         <x:v>4</x:v>
@@ -4894,7 +4839,7 @@
     </x:row>
     <x:row r="65" spans="1:3">
       <x:c r="A65" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>4</x:v>
@@ -4905,7 +4850,7 @@
     </x:row>
     <x:row r="66" spans="1:3">
       <x:c r="A66" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
         <x:v>4</x:v>
@@ -4916,7 +4861,7 @@
     </x:row>
     <x:row r="67" spans="1:3">
       <x:c r="A67" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
         <x:v>4</x:v>
@@ -4927,7 +4872,7 @@
     </x:row>
     <x:row r="68" spans="1:3">
       <x:c r="A68" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
         <x:v>4</x:v>
@@ -4938,7 +4883,7 @@
     </x:row>
     <x:row r="69" spans="1:3">
       <x:c r="A69" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
         <x:v>4</x:v>
@@ -4949,7 +4894,7 @@
     </x:row>
     <x:row r="70" spans="1:3">
       <x:c r="A70" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
         <x:v>4</x:v>
@@ -4960,7 +4905,7 @@
     </x:row>
     <x:row r="71" spans="1:3">
       <x:c r="A71" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
         <x:v>4</x:v>
@@ -4971,7 +4916,7 @@
     </x:row>
     <x:row r="72" spans="1:3">
       <x:c r="A72" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
         <x:v>4</x:v>
@@ -4982,7 +4927,7 @@
     </x:row>
     <x:row r="73" spans="1:3">
       <x:c r="A73" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
         <x:v>4</x:v>
@@ -4993,7 +4938,7 @@
     </x:row>
     <x:row r="74" spans="1:3">
       <x:c r="A74" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
         <x:v>4</x:v>
@@ -5004,7 +4949,7 @@
     </x:row>
     <x:row r="75" spans="1:3">
       <x:c r="A75" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
         <x:v>4</x:v>
@@ -5015,7 +4960,7 @@
     </x:row>
     <x:row r="76" spans="1:3">
       <x:c r="A76" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
         <x:v>4</x:v>
@@ -5026,7 +4971,7 @@
     </x:row>
     <x:row r="77" spans="1:3">
       <x:c r="A77" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
         <x:v>4</x:v>
@@ -5037,7 +4982,7 @@
     </x:row>
     <x:row r="78" spans="1:3">
       <x:c r="A78" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
         <x:v>4</x:v>
@@ -5048,7 +4993,7 @@
     </x:row>
     <x:row r="79" spans="1:3">
       <x:c r="A79" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
         <x:v>4</x:v>
@@ -5059,7 +5004,7 @@
     </x:row>
     <x:row r="80" spans="1:3">
       <x:c r="A80" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
         <x:v>4</x:v>
@@ -5070,7 +5015,7 @@
     </x:row>
     <x:row r="81" spans="1:3">
       <x:c r="A81" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
         <x:v>4</x:v>
@@ -5081,7 +5026,7 @@
     </x:row>
     <x:row r="82" spans="1:3">
       <x:c r="A82" s="0" t="s">
-      